--- a/requirements/rm_diagram/db_rm_testdaten.xlsx
+++ b/requirements/rm_diagram/db_rm_testdaten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/administrator/Documents/fh-projects/fh-sem2-db-project/requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philippreisinger/Documents/Hochschule/S02/FOGL/fh-sem2-db-project/requirements/rm_diagram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0FDAA6E-FD33-344C-9E07-95C02F4FE2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7890BE42-7DB4-FC4C-BC3E-15933FB5F7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20380" yWindow="5400" windowWidth="28040" windowHeight="17440" xr2:uid="{F1193D4A-DC4B-D649-9F00-C53722C965C8}"/>
+    <workbookView xWindow="4440" yWindow="2640" windowWidth="37980" windowHeight="21740" xr2:uid="{F1193D4A-DC4B-D649-9F00-C53722C965C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,374 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="119">
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>author_name</t>
+  </si>
+  <si>
+    <t>Stephen King</t>
+  </si>
+  <si>
+    <t>Author_book_map</t>
+  </si>
+  <si>
+    <t>book</t>
+  </si>
+  <si>
+    <t>book_isbn</t>
+  </si>
+  <si>
+    <t>author_id</t>
+  </si>
+  <si>
+    <t>isbn</t>
+  </si>
+  <si>
+    <t>book_genre_id</t>
+  </si>
+  <si>
+    <t>publisher_id</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>book_circulation_log</t>
+  </si>
+  <si>
+    <t>Carrie</t>
+  </si>
+  <si>
+    <t>loan_starts_at_date</t>
+  </si>
+  <si>
+    <t>loan_ends_at_date</t>
+  </si>
+  <si>
+    <t>book_returned_at_date</t>
+  </si>
+  <si>
+    <t>customerid</t>
+  </si>
+  <si>
+    <t>fk_stockid</t>
+  </si>
+  <si>
+    <t>Salem's Lot</t>
+  </si>
+  <si>
+    <t>The Shining</t>
+  </si>
+  <si>
+    <t>The Stand</t>
+  </si>
+  <si>
+    <t>The Dead Zone</t>
+  </si>
+  <si>
+    <t>book_genre</t>
+  </si>
+  <si>
+    <t>Firestarter</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Cujo</t>
+  </si>
+  <si>
+    <t>Horror</t>
+  </si>
+  <si>
+    <t>Pet Sematary</t>
+  </si>
+  <si>
+    <t>Thriller</t>
+  </si>
+  <si>
+    <t>Christine</t>
+  </si>
+  <si>
+    <t>Fantasy</t>
+  </si>
+  <si>
+    <t>The Eyes of the Dragon</t>
+  </si>
+  <si>
+    <t>Science Fiction</t>
+  </si>
+  <si>
+    <t>The Talisman</t>
+  </si>
+  <si>
+    <t>Suspense</t>
+  </si>
+  <si>
+    <t>It</t>
+  </si>
+  <si>
+    <t>Nonfiction</t>
+  </si>
+  <si>
+    <t>Misery</t>
+  </si>
+  <si>
+    <t>The Tommyknockers</t>
+  </si>
+  <si>
+    <t>book_location</t>
+  </si>
+  <si>
+    <t>The Dark Half</t>
+  </si>
+  <si>
+    <t>book_location_floor_id</t>
+  </si>
+  <si>
+    <t>book_location_shelf_id</t>
+  </si>
+  <si>
+    <t>Needful Things</t>
+  </si>
+  <si>
+    <t>Gerald's Game</t>
+  </si>
+  <si>
+    <t>Dolores Claiborne</t>
+  </si>
+  <si>
+    <t>Insomnia</t>
+  </si>
+  <si>
+    <t>Rose Madder</t>
+  </si>
+  <si>
+    <t>The Green Mile</t>
+  </si>
+  <si>
+    <t>Desperation</t>
+  </si>
+  <si>
+    <t>Bag of Bones</t>
+  </si>
+  <si>
+    <t>book_location_floor</t>
+  </si>
+  <si>
+    <t>The Girl Who Loved Tom Gordon</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>Dreamcatcher</t>
+  </si>
+  <si>
+    <t>From a Buick 8</t>
+  </si>
+  <si>
+    <t>Lisey's Story</t>
+  </si>
+  <si>
+    <t>Duma Key</t>
+  </si>
+  <si>
+    <t>Under the Dome</t>
+  </si>
+  <si>
+    <t>book_location_shelf</t>
+  </si>
+  <si>
+    <t>Mr. Mercedes</t>
+  </si>
+  <si>
+    <t>Finders Keepers</t>
+  </si>
+  <si>
+    <t>End of Watch</t>
+  </si>
+  <si>
+    <t>Joyland</t>
+  </si>
+  <si>
+    <t>The Outsider</t>
+  </si>
+  <si>
+    <t>Elevation</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>Later</t>
+  </si>
+  <si>
+    <t>country_name</t>
+  </si>
+  <si>
+    <t>Billy Summers</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Holly</t>
+  </si>
+  <si>
+    <t>Fairy Tale</t>
+  </si>
+  <si>
+    <t>Never Flinch</t>
+  </si>
+  <si>
+    <t>book_stock_log</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>book_location_id</t>
+  </si>
+  <si>
+    <t>is_in_stock</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>country_id</t>
+  </si>
+  <si>
+    <t>zip_id</t>
+  </si>
+  <si>
+    <t>town_id</t>
+  </si>
+  <si>
+    <t>street_id</t>
+  </si>
+  <si>
+    <t>streetnumber</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Mustermann</t>
+  </si>
+  <si>
+    <t>Alexander</t>
+  </si>
+  <si>
+    <t>Maier</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>event_type_id</t>
+  </si>
+  <si>
+    <t>event_start_at_dt</t>
+  </si>
+  <si>
+    <t>Stephen King signiert</t>
+  </si>
+  <si>
+    <t>event_type</t>
+  </si>
+  <si>
+    <t>zip</t>
+  </si>
+  <si>
+    <t>zip_code</t>
+  </si>
+  <si>
+    <t>customer_event_map</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>event_id</t>
+  </si>
+  <si>
+    <t>Signing</t>
+  </si>
+  <si>
+    <t>publisher</t>
+  </si>
+  <si>
+    <t>event_book_map</t>
+  </si>
+  <si>
+    <t>Doubleday</t>
+  </si>
+  <si>
+    <t>Scribner</t>
+  </si>
+  <si>
+    <t>Viking Press</t>
+  </si>
+  <si>
+    <t>Signet</t>
+  </si>
+  <si>
+    <t>New American Library</t>
+  </si>
+  <si>
+    <t>street</t>
+  </si>
+  <si>
+    <t>Herrnberg</t>
+  </si>
+  <si>
+    <t>Grazer Straße</t>
+  </si>
+  <si>
+    <t>Fürstenfeld</t>
+  </si>
+  <si>
+    <t>town</t>
+  </si>
+  <si>
+    <t>town_name</t>
+  </si>
+  <si>
+    <t>Graz</t>
+  </si>
+  <si>
+    <t>Wien</t>
+  </si>
+  <si>
+    <t>Großwilfersdorf</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="00000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -48,16 +413,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,17 +456,158 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="29" formatCode="mm:ss.0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="00000"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -86,6 +618,233 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}" name="Table1" displayName="Table1" ref="E5:F6" totalsRowShown="0">
+  <autoFilter ref="E5:F6" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{4CA8222C-E02B-3947-87F8-83F881B4CD46}" name="id"/>
+    <tableColumn id="2" xr3:uid="{E0E55DC1-F22B-7F48-A870-6CF35C2E7C76}" name="author_name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}" name="Table11" displayName="Table11" ref="O47:P48" totalsRowShown="0">
+  <autoFilter ref="O47:P48" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{6EC00463-AD68-3A4E-88D2-79816B3C1B9D}" name="id"/>
+    <tableColumn id="2" xr3:uid="{E086A4A2-2C9C-A84B-9AC0-52176BF11D98}" name="country_name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}" name="Table12" displayName="Table12" ref="J54:Q56" totalsRowShown="0">
+  <autoFilter ref="J54:Q56" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{E73135F5-C2F6-4D4B-884D-4470E95AC0A9}" name="id"/>
+    <tableColumn id="2" xr3:uid="{89AD4D6A-6E80-F84D-BC1C-F0BC9AB56A2A}" name="first_name"/>
+    <tableColumn id="3" xr3:uid="{D5B6CC10-DD47-CF4F-97FC-CF3CB26AC93D}" name="last_name"/>
+    <tableColumn id="4" xr3:uid="{228DB8C2-005E-F44A-9144-29D84EA1CDCD}" name="country_id"/>
+    <tableColumn id="5" xr3:uid="{F311F8A6-D073-364D-AB8C-3D81F088519F}" name="zip_id"/>
+    <tableColumn id="6" xr3:uid="{B085B83B-E563-5747-92AE-F02F325D2365}" name="town_id"/>
+    <tableColumn id="7" xr3:uid="{469FF72E-F569-5149-AAA6-FAE3DFD7884E}" name="street_id"/>
+    <tableColumn id="8" xr3:uid="{E9A49622-D15A-F048-A7F1-ED4F84228EE8}" name="streetnumber"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}" name="Table13" displayName="Table13" ref="J59:M60" totalsRowShown="0">
+  <autoFilter ref="J59:M60" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{47A5031E-499A-004E-B300-55435FDF6C2C}" name="id" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{9FADB436-039C-5246-BE80-643E467F92EE}" name="event_type_id"/>
+    <tableColumn id="3" xr3:uid="{5C025943-87BA-0A4A-9FBA-C1B0DF57EB85}" name="event_start_at_dt" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{5457FAB7-6DE8-8A44-884C-825D5762F6B4}" name="name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}" name="Table14" displayName="Table14" ref="J63:K66" totalsRowShown="0">
+  <autoFilter ref="J63:K66" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{C4630465-2BEF-F04C-9706-9ECAD5A63900}" name="id"/>
+    <tableColumn id="2" xr3:uid="{3DED103F-D0D6-FB4A-BF71-8281276D9E61}" name="name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}" name="Table15" displayName="Table15" ref="J69:K74" totalsRowShown="0">
+  <autoFilter ref="J69:K74" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{7F823BF2-5D4F-5646-A492-44D3E4F6B911}" name="id"/>
+    <tableColumn id="2" xr3:uid="{DF0F7948-576E-8649-8C5A-04EB28891E87}" name="name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}" name="Table16" displayName="Table16" ref="J77:K80" totalsRowShown="0">
+  <autoFilter ref="J77:K80" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{61F45889-5DB7-B84F-B548-EC91EF25CFE0}" name="id"/>
+    <tableColumn id="2" xr3:uid="{26F1151E-3796-634A-A382-F1364220BD49}" name="street"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}" name="Table17" displayName="Table17" ref="J83:K86" totalsRowShown="0">
+  <autoFilter ref="J83:K86" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{98617ACD-5B89-6942-9465-1BB31F03AED3}" name="id"/>
+    <tableColumn id="2" xr3:uid="{AEE42774-BADF-C948-B5B5-784A9108FA3C}" name="town_name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}" name="Table18" displayName="Table18" ref="M63:N66" totalsRowShown="0">
+  <autoFilter ref="M63:N66" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{07F9A468-865E-0A43-9EE2-245F124FBEFF}" name="id"/>
+    <tableColumn id="2" xr3:uid="{A7D14D91-1CDA-FB45-A260-0E20E6DC29BE}" name="zip_code"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}" name="Table19" displayName="Table19" ref="M69:N110" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="M69:N110" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{8E911F00-E0AD-E241-B46F-392E2B46174D}" name="event_id"/>
+    <tableColumn id="2" xr3:uid="{0B1666A1-D5FB-6648-AEFB-95B5325AE797}" name="book_isbn" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}" name="Table20" displayName="Table20" ref="P64:Q65" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="P64:Q65" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{DE2D07D2-ADAE-264C-8DCD-F0CBE007E888}" name="customer_id"/>
+    <tableColumn id="2" xr3:uid="{A21AA7ED-F1FA-D540-B965-8F8EEC8690D4}" name="event_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}" name="Table2" displayName="Table2" ref="E10:F51" totalsRowShown="0">
+  <autoFilter ref="E10:F51" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{1B46E4BC-5557-7848-A9B7-5BB850BF8539}" name="book_isbn" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{A9C101D5-0497-2F45-A36B-EA046D7840FD}" name="author_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}" name="Table3" displayName="Table3" ref="I10:M51" totalsRowShown="0">
+  <autoFilter ref="I10:M51" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{38CAD5D1-EBB5-C247-B45E-AEE98024CD77}" name="isbn" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{60F11968-00C8-6F4A-9CC4-55D26BA9ED3D}" name="book_genre_id"/>
+    <tableColumn id="3" xr3:uid="{9E8F79E7-43C5-AF41-B8EF-1A9332BF14EA}" name="publisher_id"/>
+    <tableColumn id="4" xr3:uid="{1053F528-7EBD-174A-871B-D0618032220F}" name="title"/>
+    <tableColumn id="5" xr3:uid="{864CACD1-75A9-024C-BE64-135C41FF4E7C}" name="year"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}" name="Table4" displayName="Table4" ref="O11:T13" totalsRowShown="0">
+  <autoFilter ref="O11:T13" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{CE43687C-859D-1F40-BDA4-99499EB16E72}" name="id"/>
+    <tableColumn id="2" xr3:uid="{6970F839-29D6-AF48-9ED9-F80AEA8EBDB8}" name="loan_starts_at_date" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{2A5A1D14-65E8-8741-9C1C-5D6CEC0EAC51}" name="loan_ends_at_date" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{97CCF238-494E-9D41-8539-ABC80CEB0F33}" name="book_returned_at_date"/>
+    <tableColumn id="5" xr3:uid="{DAFFE0E3-462C-F744-A240-14A8F0635450}" name="customerid"/>
+    <tableColumn id="6" xr3:uid="{EB8E3328-793F-564A-877C-326817474CA3}" name="fk_stockid"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}" name="Table6" displayName="Table6" ref="O16:P22" totalsRowShown="0">
+  <autoFilter ref="O16:P22" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{38EBFB47-42CE-4249-A9CD-4AEC31A85951}" name="id"/>
+    <tableColumn id="2" xr3:uid="{D7B8AC5E-2E4C-E944-A81B-AAECE5723F44}" name="name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}" name="Table7" displayName="Table7" ref="O25:Q31" totalsRowShown="0">
+  <autoFilter ref="O25:Q31" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{C98E57F8-CF5A-B04C-9AE6-4326E12BF111}" name="id"/>
+    <tableColumn id="2" xr3:uid="{2B878DF3-03FC-7E45-8203-B9092C488BC3}" name="book_location_floor_id"/>
+    <tableColumn id="3" xr3:uid="{7E6E67C0-8A4A-4348-B9CE-17C91B56993F}" name="book_location_shelf_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}" name="Table8" displayName="Table8" ref="O34:P38" totalsRowShown="0">
+  <autoFilter ref="O34:P38" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{ED3B7FB1-4AD6-3148-A8C5-AD0D54AB86D5}" name="id"/>
+    <tableColumn id="2" xr3:uid="{5CFA8D92-95F5-D848-ACFF-964046FA5E4A}" name="number"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}" name="Table9" displayName="Table9" ref="O41:P44" totalsRowShown="0">
+  <autoFilter ref="O41:P44" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{34593F39-F4A6-074E-A6EC-EC7E7E8422BE}" name="id"/>
+    <tableColumn id="2" xr3:uid="{E3B4CF1C-A9B2-1C4A-A8F1-45940E10B2C5}" name="number"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}" name="Table10" displayName="Table10" ref="E54:H95" totalsRowShown="0">
+  <autoFilter ref="E54:H95" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0E733531-21AD-F946-9111-F766797F96D0}" name="id"/>
+    <tableColumn id="2" xr3:uid="{85903ED5-BC1F-D147-A8EA-8491727CFFC9}" name="book_location_id"/>
+    <tableColumn id="3" xr3:uid="{0A1011E6-FFDE-254C-9381-CF62A47EE8F3}" name="is_in_stock"/>
+    <tableColumn id="4" xr3:uid="{260DA1AD-9E16-104E-A144-7275FF29087D}" name="book_isbn" dataDxfId="5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -405,9 +1164,2416 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5DA9CCF-71D1-7F40-ABE4-A9F4E589BDAC}">
-  <dimension ref="A1"/>
+  <dimension ref="E4:T110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" customWidth="1"/>
+    <col min="12" max="12" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="14" max="14" width="17.83203125" customWidth="1"/>
+    <col min="15" max="15" width="9.83203125" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" customWidth="1"/>
+    <col min="17" max="17" width="21.83203125" customWidth="1"/>
+    <col min="18" max="18" width="22.1640625" customWidth="1"/>
+    <col min="19" max="19" width="12.6640625" customWidth="1"/>
+    <col min="20" max="20" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" t="s">
+        <v>12</v>
+      </c>
+      <c r="O10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E11" s="1">
+        <v>9780385086952</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>9780385086952</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11">
+        <v>1974</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>16</v>
+      </c>
+      <c r="R11" t="s">
+        <v>17</v>
+      </c>
+      <c r="S11" t="s">
+        <v>18</v>
+      </c>
+      <c r="T11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E12" s="1">
+        <v>9780307743657</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>9780307743657</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12">
+        <v>1975</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12" s="2">
+        <v>46082</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>46090</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E13" s="1">
+        <v>9780307743664</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1">
+        <v>9780307743664</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13">
+        <v>1977</v>
+      </c>
+      <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13" s="2">
+        <v>46082</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>46090</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E14" s="1">
+        <v>9780670813025</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>9780670813025</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>5</v>
+      </c>
+      <c r="L14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="15" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E15" s="1">
+        <v>9780345418864</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
+        <v>9780345418864</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15">
+        <v>1983</v>
+      </c>
+      <c r="O15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E16" s="1">
+        <v>9780670813032</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
+        <v>9780670813032</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16">
+        <v>1980</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E17" s="1">
+        <v>9780670813049</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <v>9780670813049</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17">
+        <v>1981</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E18" s="1">
+        <v>9780670813056</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>9780670813056</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18">
+        <v>1983</v>
+      </c>
+      <c r="O18">
+        <v>2</v>
+      </c>
+      <c r="P18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E19" s="1">
+        <v>9780670813063</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1">
+        <v>9780670813063</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19">
+        <v>1983</v>
+      </c>
+      <c r="O19">
+        <v>3</v>
+      </c>
+      <c r="P19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E20" s="1">
+        <v>9780670813070</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <v>9780670813070</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20" t="s">
+        <v>33</v>
+      </c>
+      <c r="M20">
+        <v>1984</v>
+      </c>
+      <c r="O20">
+        <v>4</v>
+      </c>
+      <c r="P20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E21" s="1">
+        <v>9780670813087</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <v>9780670813087</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+      <c r="L21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M21">
+        <v>1984</v>
+      </c>
+      <c r="O21">
+        <v>5</v>
+      </c>
+      <c r="P21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E22" s="1">
+        <v>9780670813094</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <v>9780670813094</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22" t="s">
+        <v>37</v>
+      </c>
+      <c r="M22">
+        <v>1986</v>
+      </c>
+      <c r="O22">
+        <v>6</v>
+      </c>
+      <c r="P22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E23" s="1">
+        <v>9780670813100</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
+        <v>9780670813100</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>2</v>
+      </c>
+      <c r="L23" t="s">
+        <v>39</v>
+      </c>
+      <c r="M23">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="24" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E24" s="1">
+        <v>9780670813117</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>9780670813117</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>2</v>
+      </c>
+      <c r="L24" t="s">
+        <v>40</v>
+      </c>
+      <c r="M24">
+        <v>1987</v>
+      </c>
+      <c r="O24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E25" s="1">
+        <v>9780670813124</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1">
+        <v>9780670813124</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25" t="s">
+        <v>42</v>
+      </c>
+      <c r="M25">
+        <v>1989</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P25" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E26" s="1">
+        <v>9780670813131</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <v>9780670813131</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>3</v>
+      </c>
+      <c r="L26" t="s">
+        <v>45</v>
+      </c>
+      <c r="M26">
+        <v>1991</v>
+      </c>
+      <c r="O26">
+        <v>6</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E27" s="1">
+        <v>9780670813148</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
+        <v>9780670813148</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27" t="s">
+        <v>46</v>
+      </c>
+      <c r="M27">
+        <v>1992</v>
+      </c>
+      <c r="O27">
+        <v>7</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E28" s="1">
+        <v>9780670813155</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <v>9780670813155</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28" t="s">
+        <v>47</v>
+      </c>
+      <c r="M28">
+        <v>1992</v>
+      </c>
+      <c r="O28">
+        <v>8</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E29" s="1">
+        <v>9780670813162</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1">
+        <v>9780670813162</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>2</v>
+      </c>
+      <c r="L29" t="s">
+        <v>48</v>
+      </c>
+      <c r="M29">
+        <v>1994</v>
+      </c>
+      <c r="O29">
+        <v>9</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E30" s="1">
+        <v>9780670813179</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
+        <v>9780670813179</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>2</v>
+      </c>
+      <c r="L30" t="s">
+        <v>49</v>
+      </c>
+      <c r="M30">
+        <v>1995</v>
+      </c>
+      <c r="O30">
+        <v>10</v>
+      </c>
+      <c r="P30">
+        <v>2</v>
+      </c>
+      <c r="Q30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E31" s="1">
+        <v>9780670813186</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1">
+        <v>9780670813186</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31">
+        <v>1996</v>
+      </c>
+      <c r="O31">
+        <v>11</v>
+      </c>
+      <c r="P31">
+        <v>2</v>
+      </c>
+      <c r="Q31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E32" s="1">
+        <v>9780670813193</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1">
+        <v>9780670813193</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32" t="s">
+        <v>51</v>
+      </c>
+      <c r="M32">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="33" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E33" s="1">
+        <v>9780670813209</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1">
+        <v>9780670813209</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33" t="s">
+        <v>52</v>
+      </c>
+      <c r="M33">
+        <v>1998</v>
+      </c>
+      <c r="O33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E34" s="1">
+        <v>9780670813216</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1">
+        <v>9780670813216</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>2</v>
+      </c>
+      <c r="L34" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34">
+        <v>1999</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E35" s="1">
+        <v>9780670813223</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>9780670813223</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+      <c r="L35" t="s">
+        <v>56</v>
+      </c>
+      <c r="M35">
+        <v>2001</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E36" s="1">
+        <v>9780670813230</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>9780670813230</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36">
+        <v>2002</v>
+      </c>
+      <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E37" s="1">
+        <v>9780670813247</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1">
+        <v>9780670813247</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>2</v>
+      </c>
+      <c r="L37" t="s">
+        <v>58</v>
+      </c>
+      <c r="M37">
+        <v>2006</v>
+      </c>
+      <c r="O37">
+        <v>3</v>
+      </c>
+      <c r="P37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E38" s="1">
+        <v>9780670813254</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
+        <v>9780670813254</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+      <c r="L38" t="s">
+        <v>59</v>
+      </c>
+      <c r="M38">
+        <v>2008</v>
+      </c>
+      <c r="O38">
+        <v>4</v>
+      </c>
+      <c r="P38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E39" s="1">
+        <v>9780670813261</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1">
+        <v>9780670813261</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>2</v>
+      </c>
+      <c r="L39" t="s">
+        <v>60</v>
+      </c>
+      <c r="M39">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="40" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E40" s="1">
+        <v>9780670813278</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1">
+        <v>9780670813278</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <v>2</v>
+      </c>
+      <c r="L40" s="2">
+        <v>23337</v>
+      </c>
+      <c r="M40">
+        <v>2011</v>
+      </c>
+      <c r="O40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E41" s="1">
+        <v>9780670813285</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
+        <v>9780670813285</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <v>2</v>
+      </c>
+      <c r="L41" t="s">
+        <v>62</v>
+      </c>
+      <c r="M41">
+        <v>2014</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="P41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E42" s="1">
+        <v>9780670813292</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1">
+        <v>9780670813292</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>2</v>
+      </c>
+      <c r="L42" t="s">
+        <v>63</v>
+      </c>
+      <c r="M42">
+        <v>2015</v>
+      </c>
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E43" s="1">
+        <v>9780670813308</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1">
+        <v>9780670813308</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <v>2</v>
+      </c>
+      <c r="L43" t="s">
+        <v>64</v>
+      </c>
+      <c r="M43">
+        <v>2016</v>
+      </c>
+      <c r="O43">
+        <v>2</v>
+      </c>
+      <c r="P43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E44" s="1">
+        <v>9780670813315</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1">
+        <v>9780670813315</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>2</v>
+      </c>
+      <c r="L44" t="s">
+        <v>65</v>
+      </c>
+      <c r="M44">
+        <v>2013</v>
+      </c>
+      <c r="O44">
+        <v>3</v>
+      </c>
+      <c r="P44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E45" s="1">
+        <v>9780670813322</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1">
+        <v>9780670813322</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>2</v>
+      </c>
+      <c r="L45" t="s">
+        <v>66</v>
+      </c>
+      <c r="M45">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="46" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E46" s="1">
+        <v>9780670813339</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1">
+        <v>9780670813339</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <v>2</v>
+      </c>
+      <c r="L46" t="s">
+        <v>67</v>
+      </c>
+      <c r="M46">
+        <v>2018</v>
+      </c>
+      <c r="O46" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E47" s="1">
+        <v>9780670813346</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1">
+        <v>9780670813346</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>2</v>
+      </c>
+      <c r="L47" t="s">
+        <v>69</v>
+      </c>
+      <c r="M47">
+        <v>2021</v>
+      </c>
+      <c r="O47" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="P47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="5:16" x14ac:dyDescent="0.2">
+      <c r="E48" s="1">
+        <v>9780670813353</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1">
+        <v>9780670813353</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>2</v>
+      </c>
+      <c r="L48" t="s">
+        <v>71</v>
+      </c>
+      <c r="M48">
+        <v>2021</v>
+      </c>
+      <c r="O48">
+        <v>1</v>
+      </c>
+      <c r="P48" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E49" s="1">
+        <v>9780670813360</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="I49" s="1">
+        <v>9780670813360</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>2</v>
+      </c>
+      <c r="L49" t="s">
+        <v>73</v>
+      </c>
+      <c r="M49">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="50" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E50" s="1">
+        <v>9780670813377</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1">
+        <v>9780670813377</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>2</v>
+      </c>
+      <c r="L50" t="s">
+        <v>74</v>
+      </c>
+      <c r="M50">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="51" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E51" s="1">
+        <v>9780670813384</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="I51" s="1">
+        <v>9780670813384</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>2</v>
+      </c>
+      <c r="L51" t="s">
+        <v>75</v>
+      </c>
+      <c r="M51">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="53" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E53" t="s">
+        <v>76</v>
+      </c>
+      <c r="J53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E54" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s">
+        <v>79</v>
+      </c>
+      <c r="H54" t="s">
+        <v>6</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K54" t="s">
+        <v>80</v>
+      </c>
+      <c r="L54" t="s">
+        <v>81</v>
+      </c>
+      <c r="M54" t="s">
+        <v>82</v>
+      </c>
+      <c r="N54" t="s">
+        <v>83</v>
+      </c>
+      <c r="O54" t="s">
+        <v>84</v>
+      </c>
+      <c r="P54" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>6</v>
+      </c>
+      <c r="G55" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" s="3">
+        <v>9780385086952</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55" t="s">
+        <v>87</v>
+      </c>
+      <c r="L55" t="s">
+        <v>88</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>3</v>
+      </c>
+      <c r="O55">
+        <v>3</v>
+      </c>
+      <c r="P55">
+        <v>1</v>
+      </c>
+      <c r="Q55">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="56" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>6</v>
+      </c>
+      <c r="G56" t="b">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4">
+        <v>9780307743657</v>
+      </c>
+      <c r="J56">
+        <v>2</v>
+      </c>
+      <c r="K56" t="s">
+        <v>89</v>
+      </c>
+      <c r="L56" t="s">
+        <v>90</v>
+      </c>
+      <c r="M56">
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <v>3</v>
+      </c>
+      <c r="O56">
+        <v>3</v>
+      </c>
+      <c r="P56">
+        <v>1</v>
+      </c>
+      <c r="Q56">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E57">
+        <v>3</v>
+      </c>
+      <c r="F57">
+        <v>6</v>
+      </c>
+      <c r="G57" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" s="3">
+        <v>9780307743664</v>
+      </c>
+    </row>
+    <row r="58" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E58">
+        <v>4</v>
+      </c>
+      <c r="F58">
+        <v>7</v>
+      </c>
+      <c r="G58" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4">
+        <v>9780670813025</v>
+      </c>
+      <c r="J58" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E59">
+        <v>5</v>
+      </c>
+      <c r="F59">
+        <v>7</v>
+      </c>
+      <c r="G59" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" s="3">
+        <v>9780345418864</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K59" t="s">
+        <v>92</v>
+      </c>
+      <c r="L59" t="s">
+        <v>93</v>
+      </c>
+      <c r="M59" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E60">
+        <v>6</v>
+      </c>
+      <c r="F60">
+        <v>6</v>
+      </c>
+      <c r="G60" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4">
+        <v>9780670813032</v>
+      </c>
+      <c r="J60" s="7">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60" s="5">
+        <v>46142.371099537035</v>
+      </c>
+      <c r="M60" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="61" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E61">
+        <v>7</v>
+      </c>
+      <c r="F61">
+        <v>6</v>
+      </c>
+      <c r="G61" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" s="3">
+        <v>9780670813049</v>
+      </c>
+    </row>
+    <row r="62" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E62">
+        <v>8</v>
+      </c>
+      <c r="F62">
+        <v>8</v>
+      </c>
+      <c r="G62" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4">
+        <v>9780670813056</v>
+      </c>
+      <c r="J62" t="s">
+        <v>95</v>
+      </c>
+      <c r="M62" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="63" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E63">
+        <v>9</v>
+      </c>
+      <c r="F63">
+        <v>8</v>
+      </c>
+      <c r="G63" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" s="3">
+        <v>9780670813063</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K63" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N63" t="s">
+        <v>97</v>
+      </c>
+      <c r="P63" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E64">
+        <v>10</v>
+      </c>
+      <c r="F64">
+        <v>8</v>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4">
+        <v>9780670813070</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64" t="s">
+        <v>99</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="N64">
+        <v>1010</v>
+      </c>
+      <c r="P64" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q64" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E65">
+        <v>11</v>
+      </c>
+      <c r="F65">
+        <v>8</v>
+      </c>
+      <c r="G65" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="3">
+        <v>9780670813087</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="K65" t="s">
+        <v>102</v>
+      </c>
+      <c r="M65">
+        <v>2</v>
+      </c>
+      <c r="N65">
+        <v>8010</v>
+      </c>
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="Q65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E66">
+        <v>12</v>
+      </c>
+      <c r="F66">
+        <v>6</v>
+      </c>
+      <c r="G66" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4">
+        <v>9780670813094</v>
+      </c>
+      <c r="M66">
+        <v>3</v>
+      </c>
+      <c r="N66">
+        <v>8263</v>
+      </c>
+    </row>
+    <row r="67" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E67">
+        <v>13</v>
+      </c>
+      <c r="F67">
+        <v>6</v>
+      </c>
+      <c r="G67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3">
+        <v>9780670813100</v>
+      </c>
+    </row>
+    <row r="68" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E68">
+        <v>14</v>
+      </c>
+      <c r="F68">
+        <v>6</v>
+      </c>
+      <c r="G68" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4">
+        <v>9780670813117</v>
+      </c>
+      <c r="J68" t="s">
+        <v>103</v>
+      </c>
+      <c r="M68" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="69" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E69">
+        <v>15</v>
+      </c>
+      <c r="F69">
+        <v>6</v>
+      </c>
+      <c r="G69" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" s="3">
+        <v>9780670813124</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K69" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E70">
+        <v>16</v>
+      </c>
+      <c r="F70">
+        <v>6</v>
+      </c>
+      <c r="G70" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4">
+        <v>9780670813131</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70" t="s">
+        <v>105</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70" s="3">
+        <v>9780385086952</v>
+      </c>
+    </row>
+    <row r="71" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E71">
+        <v>17</v>
+      </c>
+      <c r="F71">
+        <v>6</v>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" s="3">
+        <v>9780670813148</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
+      <c r="K71" t="s">
+        <v>106</v>
+      </c>
+      <c r="M71">
+        <v>1</v>
+      </c>
+      <c r="N71" s="4">
+        <v>9780307743657</v>
+      </c>
+    </row>
+    <row r="72" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E72">
+        <v>18</v>
+      </c>
+      <c r="F72">
+        <v>6</v>
+      </c>
+      <c r="G72" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4">
+        <v>9780670813155</v>
+      </c>
+      <c r="J72">
+        <v>3</v>
+      </c>
+      <c r="K72" t="s">
+        <v>107</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72" s="3">
+        <v>9780307743664</v>
+      </c>
+    </row>
+    <row r="73" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E73">
+        <v>19</v>
+      </c>
+      <c r="F73">
+        <v>6</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" s="3">
+        <v>9780670813162</v>
+      </c>
+      <c r="J73">
+        <v>4</v>
+      </c>
+      <c r="K73" t="s">
+        <v>108</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="N73" s="4">
+        <v>9780670813025</v>
+      </c>
+    </row>
+    <row r="74" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E74">
+        <v>20</v>
+      </c>
+      <c r="F74">
+        <v>6</v>
+      </c>
+      <c r="G74" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4">
+        <v>9780670813179</v>
+      </c>
+      <c r="J74">
+        <v>5</v>
+      </c>
+      <c r="K74" t="s">
+        <v>109</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+      <c r="N74" s="3">
+        <v>9780345418864</v>
+      </c>
+    </row>
+    <row r="75" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E75">
+        <v>21</v>
+      </c>
+      <c r="F75">
+        <v>6</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" s="3">
+        <v>9780670813186</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75" s="4">
+        <v>9780670813032</v>
+      </c>
+    </row>
+    <row r="76" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E76">
+        <v>22</v>
+      </c>
+      <c r="F76">
+        <v>6</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4">
+        <v>9780670813193</v>
+      </c>
+      <c r="J76" t="s">
+        <v>110</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76" s="3">
+        <v>9780670813049</v>
+      </c>
+    </row>
+    <row r="77" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E77">
+        <v>23</v>
+      </c>
+      <c r="F77">
+        <v>6</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" s="3">
+        <v>9780670813209</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K77" t="s">
+        <v>110</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77" s="4">
+        <v>9780670813056</v>
+      </c>
+    </row>
+    <row r="78" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E78">
+        <v>24</v>
+      </c>
+      <c r="F78">
+        <v>6</v>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4">
+        <v>9780670813216</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78" t="s">
+        <v>111</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78" s="3">
+        <v>9780670813063</v>
+      </c>
+    </row>
+    <row r="79" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E79">
+        <v>25</v>
+      </c>
+      <c r="F79">
+        <v>6</v>
+      </c>
+      <c r="G79" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" s="3">
+        <v>9780670813223</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="K79" t="s">
+        <v>112</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79" s="4">
+        <v>9780670813070</v>
+      </c>
+    </row>
+    <row r="80" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="E80">
+        <v>26</v>
+      </c>
+      <c r="F80">
+        <v>6</v>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4">
+        <v>9780670813230</v>
+      </c>
+      <c r="J80">
+        <v>3</v>
+      </c>
+      <c r="K80" t="s">
+        <v>113</v>
+      </c>
+      <c r="M80">
+        <v>1</v>
+      </c>
+      <c r="N80" s="3">
+        <v>9780670813087</v>
+      </c>
+    </row>
+    <row r="81" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E81">
+        <v>27</v>
+      </c>
+      <c r="F81">
+        <v>6</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" s="3">
+        <v>9780670813247</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81" s="4">
+        <v>9780670813094</v>
+      </c>
+    </row>
+    <row r="82" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E82">
+        <v>28</v>
+      </c>
+      <c r="F82">
+        <v>6</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4">
+        <v>9780670813254</v>
+      </c>
+      <c r="J82" t="s">
+        <v>114</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82" s="3">
+        <v>9780670813100</v>
+      </c>
+    </row>
+    <row r="83" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E83">
+        <v>29</v>
+      </c>
+      <c r="F83">
+        <v>6</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" s="3">
+        <v>9780670813261</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K83" t="s">
+        <v>115</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83" s="4">
+        <v>9780670813117</v>
+      </c>
+    </row>
+    <row r="84" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E84">
+        <v>30</v>
+      </c>
+      <c r="F84">
+        <v>6</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" s="4">
+        <v>9780670813278</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84" t="s">
+        <v>116</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
+      </c>
+      <c r="N84" s="3">
+        <v>9780670813124</v>
+      </c>
+    </row>
+    <row r="85" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E85">
+        <v>31</v>
+      </c>
+      <c r="F85">
+        <v>6</v>
+      </c>
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" s="3">
+        <v>9780670813285</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85" t="s">
+        <v>117</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85" s="4">
+        <v>9780670813131</v>
+      </c>
+    </row>
+    <row r="86" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E86">
+        <v>32</v>
+      </c>
+      <c r="F86">
+        <v>6</v>
+      </c>
+      <c r="G86" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4">
+        <v>9780670813292</v>
+      </c>
+      <c r="J86">
+        <v>3</v>
+      </c>
+      <c r="K86" t="s">
+        <v>118</v>
+      </c>
+      <c r="M86">
+        <v>1</v>
+      </c>
+      <c r="N86" s="3">
+        <v>9780670813148</v>
+      </c>
+    </row>
+    <row r="87" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E87">
+        <v>33</v>
+      </c>
+      <c r="F87">
+        <v>6</v>
+      </c>
+      <c r="G87" t="b">
+        <v>1</v>
+      </c>
+      <c r="H87" s="3">
+        <v>9780670813308</v>
+      </c>
+      <c r="M87">
+        <v>1</v>
+      </c>
+      <c r="N87" s="4">
+        <v>9780670813155</v>
+      </c>
+    </row>
+    <row r="88" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E88">
+        <v>34</v>
+      </c>
+      <c r="F88">
+        <v>6</v>
+      </c>
+      <c r="G88" t="b">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4">
+        <v>9780670813315</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88" s="3">
+        <v>9780670813162</v>
+      </c>
+    </row>
+    <row r="89" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E89">
+        <v>35</v>
+      </c>
+      <c r="F89">
+        <v>6</v>
+      </c>
+      <c r="G89" t="b">
+        <v>1</v>
+      </c>
+      <c r="H89" s="3">
+        <v>9780670813322</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89" s="4">
+        <v>9780670813179</v>
+      </c>
+    </row>
+    <row r="90" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E90">
+        <v>36</v>
+      </c>
+      <c r="F90">
+        <v>6</v>
+      </c>
+      <c r="G90" t="b">
+        <v>1</v>
+      </c>
+      <c r="H90" s="4">
+        <v>9780670813339</v>
+      </c>
+      <c r="M90">
+        <v>1</v>
+      </c>
+      <c r="N90" s="3">
+        <v>9780670813186</v>
+      </c>
+    </row>
+    <row r="91" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E91">
+        <v>37</v>
+      </c>
+      <c r="F91">
+        <v>6</v>
+      </c>
+      <c r="G91" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" s="3">
+        <v>9780670813346</v>
+      </c>
+      <c r="M91">
+        <v>1</v>
+      </c>
+      <c r="N91" s="4">
+        <v>9780670813193</v>
+      </c>
+    </row>
+    <row r="92" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E92">
+        <v>38</v>
+      </c>
+      <c r="F92">
+        <v>6</v>
+      </c>
+      <c r="G92" t="b">
+        <v>1</v>
+      </c>
+      <c r="H92" s="4">
+        <v>9780670813353</v>
+      </c>
+      <c r="M92">
+        <v>1</v>
+      </c>
+      <c r="N92" s="3">
+        <v>9780670813209</v>
+      </c>
+    </row>
+    <row r="93" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E93">
+        <v>39</v>
+      </c>
+      <c r="F93">
+        <v>6</v>
+      </c>
+      <c r="G93" t="b">
+        <v>1</v>
+      </c>
+      <c r="H93" s="3">
+        <v>9780670813360</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93" s="4">
+        <v>9780670813216</v>
+      </c>
+    </row>
+    <row r="94" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E94">
+        <v>40</v>
+      </c>
+      <c r="F94">
+        <v>6</v>
+      </c>
+      <c r="G94" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4">
+        <v>9780670813377</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94" s="3">
+        <v>9780670813223</v>
+      </c>
+    </row>
+    <row r="95" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E95">
+        <v>41</v>
+      </c>
+      <c r="F95">
+        <v>6</v>
+      </c>
+      <c r="G95" t="b">
+        <v>1</v>
+      </c>
+      <c r="H95" s="3">
+        <v>9780670813384</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95" s="4">
+        <v>9780670813230</v>
+      </c>
+    </row>
+    <row r="96" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96" s="3">
+        <v>9780670813247</v>
+      </c>
+    </row>
+    <row r="97" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97" s="4">
+        <v>9780670813254</v>
+      </c>
+    </row>
+    <row r="98" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98" s="3">
+        <v>9780670813261</v>
+      </c>
+    </row>
+    <row r="99" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99" s="4">
+        <v>9780670813278</v>
+      </c>
+    </row>
+    <row r="100" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100" s="3">
+        <v>9780670813285</v>
+      </c>
+    </row>
+    <row r="101" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101" s="4">
+        <v>9780670813292</v>
+      </c>
+    </row>
+    <row r="102" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M102">
+        <v>1</v>
+      </c>
+      <c r="N102" s="3">
+        <v>9780670813308</v>
+      </c>
+    </row>
+    <row r="103" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103" s="4">
+        <v>9780670813315</v>
+      </c>
+    </row>
+    <row r="104" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104" s="3">
+        <v>9780670813322</v>
+      </c>
+    </row>
+    <row r="105" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105" s="4">
+        <v>9780670813339</v>
+      </c>
+    </row>
+    <row r="106" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="N106" s="3">
+        <v>9780670813346</v>
+      </c>
+    </row>
+    <row r="107" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107" s="4">
+        <v>9780670813353</v>
+      </c>
+    </row>
+    <row r="108" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108" s="3">
+        <v>9780670813360</v>
+      </c>
+    </row>
+    <row r="109" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109" s="4">
+        <v>9780670813377</v>
+      </c>
+    </row>
+    <row r="110" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110" s="3">
+        <v>9780670813384</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="19">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId12"/>
+    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId17"/>
+    <tablePart r:id="rId18"/>
+    <tablePart r:id="rId19"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/requirements/rm_diagram/db_rm_testdaten.xlsx
+++ b/requirements/rm_diagram/db_rm_testdaten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philippreisinger/Documents/Hochschule/S02/FOGL/fh-sem2-db-project/requirements/rm_diagram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7890BE42-7DB4-FC4C-BC3E-15933FB5F7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FA48ED-F2F7-B041-A946-736B78A5CEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="2640" windowWidth="37980" windowHeight="21740" xr2:uid="{F1193D4A-DC4B-D649-9F00-C53722C965C8}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="50040" windowHeight="28200" xr2:uid="{F1193D4A-DC4B-D649-9F00-C53722C965C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="120">
   <si>
     <t>Author</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>Großwilfersdorf</t>
+  </si>
+  <si>
+    <t>"4/30/2026  8:54:23 AM"</t>
   </si>
 </sst>
 </file>
@@ -448,7 +451,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -465,25 +468,590 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color theme="5" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color theme="5" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color theme="5" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color theme="5" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="5" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right style="medium">
+        <color theme="5"/>
+      </right>
+      <top style="medium">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right style="medium">
+        <color theme="5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right style="medium">
+        <color theme="5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="3" tint="0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color theme="4"/>
+      </right>
+      <top style="medium">
+        <color theme="3" tint="0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="3" tint="0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color theme="4"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="3" tint="0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color theme="4"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="3" tint="0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="3" tint="0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </left>
+      <right style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </right>
+      <top style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </left>
+      <right style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </left>
+      <right style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </left>
+      <right style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </right>
+      <top style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </left>
+      <right style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </right>
+      <top style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </left>
+      <right style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </left>
+      <right style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </left>
+        <right style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </left>
+        <right style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="medium">
+          <color theme="4"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="5"/>
+        </left>
+        <right style="medium">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="5" tint="-0.249977111117893"/>
+        </left>
+        <right style="medium">
+          <color theme="5" tint="-0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -511,6 +1079,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="29" formatCode="mm:ss.0"/>
     </dxf>
     <dxf>
       <font>
@@ -552,60 +1123,26 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="29" formatCode="mm:ss.0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="00000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yy"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="00000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -620,11 +1157,916 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>441739</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>11043</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>441739</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>209826</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="Straight Connector 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC01A454-775B-AF0A-972C-8C87D9D638AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5378174" y="1247913"/>
+          <a:ext cx="0" cy="596348"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>586154</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>8881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>586154</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="Straight Connector 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D466AF4-5ABC-DE82-5E66-9E81D69DC5E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2877483" y="10488601"/>
+          <a:ext cx="0" cy="195385"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>577272</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>606985</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="36" name="Straight Connector 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1E7D974-4D87-0A76-0420-B28D95FB4A4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2868601" y="10683986"/>
+          <a:ext cx="6113279" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>588308</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>37353</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>597647</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>18677</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="Straight Connector 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA430E8A-D308-9BDC-3471-22915A2E99BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8787279" y="10552206"/>
+          <a:ext cx="9339" cy="186765"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>719044</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>46691</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>719044</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>177427</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="44" name="Straight Connector 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75CDDB71-3BFC-85D4-5602-78D2951DFBEE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8918015" y="10561544"/>
+          <a:ext cx="0" cy="336177"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1288676</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>177427</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1288676</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>196103</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="46" name="Straight Connector 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C55F8B8C-4E80-2DFC-6857-62D4FAC80520}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4575735" y="10897721"/>
+          <a:ext cx="0" cy="224117"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1270000</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>149412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>709705</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>177427</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="47" name="Straight Connector 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CE2496C-C787-6D4F-8206-88D78472245E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4557059" y="10869706"/>
+          <a:ext cx="4351617" cy="28015"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>961838</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>65368</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>971176</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>168089</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="Straight Connector 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E4EBC66-5B65-B346-B34C-28A2ACE38C10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="9160809" y="10580221"/>
+          <a:ext cx="9338" cy="513603"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>541618</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>177427</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>943161</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>177427</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="53" name="Straight Connector 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0131D967-6E05-FA27-4F66-481AC175D92E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7405221" y="11103162"/>
+          <a:ext cx="1736911" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>532279</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>177427</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>532279</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>18676</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="55" name="Straight Connector 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46B06519-EBDA-4F6D-3FDF-08FF8E2A22DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7395882" y="11103162"/>
+          <a:ext cx="0" cy="252132"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>523986</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>8881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>523986</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>204265</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="57" name="Straight Connector 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{353E130C-98B4-0478-F2DD-B3495A690CCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2175874" y="19618391"/>
+          <a:ext cx="0" cy="808182"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>417413</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>195385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>417413</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>133217</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="59" name="Straight Connector 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD1DB88D-B1A2-14D8-935D-2FC4BBBDFB1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2895245" y="21883077"/>
+          <a:ext cx="0" cy="346364"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>454358</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>99113</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>454358</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>196806</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="60" name="Straight Connector 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9D3EE73-6C1E-DE40-8FCA-F386F722F481}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2106246" y="22159812"/>
+          <a:ext cx="0" cy="301959"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>426294</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>115454</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>417413</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>115454</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="Straight Connector 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0495440C-6770-954F-859B-2D7957758614}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2078182" y="22211678"/>
+          <a:ext cx="817063" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>772658</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>10302</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>774079</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>62168</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="65" name="Straight Connector 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1297BBC-C609-6D4C-849F-BE6EF57ED209}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4076434" y="21902260"/>
+          <a:ext cx="1421" cy="256132"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>408532</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>35524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>408532</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>204265</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="66" name="Straight Connector 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11CA2E8B-4C2D-A848-8937-1B0609E2FED5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5497413" y="22096223"/>
+          <a:ext cx="0" cy="373007"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>772658</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>44405</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>399650</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>53286</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="70" name="Straight Connector 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED457B58-A3D5-E648-B3AB-299DE43A990D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4076434" y="22140629"/>
+          <a:ext cx="1252237" cy="8881"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>737133</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>26643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>737133</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>204266</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="76" name="Straight Connector 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C39238E-7F88-5F66-84AA-C5276BF9A501}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10231049" y="1678531"/>
+          <a:ext cx="0" cy="177623"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}" name="Table1" displayName="Table1" ref="E5:F6" totalsRowShown="0">
   <autoFilter ref="E5:F6" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4CA8222C-E02B-3947-87F8-83F881B4CD46}" name="id"/>
+    <tableColumn id="1" xr3:uid="{4CA8222C-E02B-3947-87F8-83F881B4CD46}" name="id" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{E0E55DC1-F22B-7F48-A870-6CF35C2E7C76}" name="author_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -643,8 +2085,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}" name="Table12" displayName="Table12" ref="J54:Q56" totalsRowShown="0">
-  <autoFilter ref="J54:Q56" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}" name="Table12" displayName="Table12" ref="M76:T78" totalsRowShown="0">
+  <autoFilter ref="M76:T78" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E73135F5-C2F6-4D4B-884D-4470E95AC0A9}" name="id"/>
     <tableColumn id="2" xr3:uid="{89AD4D6A-6E80-F84D-BC1C-F0BC9AB56A2A}" name="first_name"/>
@@ -660,12 +2102,12 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}" name="Table13" displayName="Table13" ref="J59:M60" totalsRowShown="0">
-  <autoFilter ref="J59:M60" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}" name="Table13" displayName="Table13" ref="G101:J102" totalsRowShown="0">
+  <autoFilter ref="G101:J102" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{47A5031E-499A-004E-B300-55435FDF6C2C}" name="id" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{47A5031E-499A-004E-B300-55435FDF6C2C}" name="id" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{9FADB436-039C-5246-BE80-643E467F92EE}" name="event_type_id"/>
-    <tableColumn id="3" xr3:uid="{5C025943-87BA-0A4A-9FBA-C1B0DF57EB85}" name="event_start_at_dt" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{5C025943-87BA-0A4A-9FBA-C1B0DF57EB85}" name="event_start_at_dt" dataDxfId="15"/>
     <tableColumn id="4" xr3:uid="{5457FAB7-6DE8-8A44-884C-825D5762F6B4}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -673,8 +2115,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}" name="Table14" displayName="Table14" ref="J63:K66" totalsRowShown="0">
-  <autoFilter ref="J63:K66" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}" name="Table14" displayName="Table14" ref="L106:M109" totalsRowShown="0">
+  <autoFilter ref="L106:M109" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{C4630465-2BEF-F04C-9706-9ECAD5A63900}" name="id"/>
     <tableColumn id="2" xr3:uid="{3DED103F-D0D6-FB4A-BF71-8281276D9E61}" name="name"/>
@@ -684,8 +2126,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}" name="Table15" displayName="Table15" ref="J69:K74" totalsRowShown="0">
-  <autoFilter ref="J69:K74" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}" name="Table15" displayName="Table15" ref="K56:L61" totalsRowShown="0">
+  <autoFilter ref="K56:L61" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{7F823BF2-5D4F-5646-A492-44D3E4F6B911}" name="id"/>
     <tableColumn id="2" xr3:uid="{DF0F7948-576E-8649-8C5A-04EB28891E87}" name="name"/>
@@ -728,18 +2170,18 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}" name="Table19" displayName="Table19" ref="M69:N110" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="M69:N110" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}" name="Table19" displayName="Table19" ref="G56:H97" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="G56:H97" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{8E911F00-E0AD-E241-B46F-392E2B46174D}" name="event_id"/>
-    <tableColumn id="2" xr3:uid="{0B1666A1-D5FB-6648-AEFB-95B5325AE797}" name="book_isbn" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{0B1666A1-D5FB-6648-AEFB-95B5325AE797}" name="book_isbn" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}" name="Table20" displayName="Table20" ref="P64:Q65" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}" name="Table20" displayName="Table20" ref="P64:Q65" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="P64:Q65" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{DE2D07D2-ADAE-264C-8DCD-F0CBE007E888}" name="customer_id"/>
@@ -750,11 +2192,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}" name="Table2" displayName="Table2" ref="E10:F51" totalsRowShown="0">
-  <autoFilter ref="E10:F51" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}" name="Table2" displayName="Table2" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="20">
+  <autoFilter ref="D10:E51" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1B46E4BC-5557-7848-A9B7-5BB850BF8539}" name="book_isbn" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{A9C101D5-0497-2F45-A36B-EA046D7840FD}" name="author_id"/>
+    <tableColumn id="1" xr3:uid="{1B46E4BC-5557-7848-A9B7-5BB850BF8539}" name="book_isbn" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{A9C101D5-0497-2F45-A36B-EA046D7840FD}" name="author_id" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -764,7 +2206,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}" name="Table3" displayName="Table3" ref="I10:M51" totalsRowShown="0">
   <autoFilter ref="I10:M51" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{38CAD5D1-EBB5-C247-B45E-AEE98024CD77}" name="isbn" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{38CAD5D1-EBB5-C247-B45E-AEE98024CD77}" name="isbn" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{60F11968-00C8-6F4A-9CC4-55D26BA9ED3D}" name="book_genre_id"/>
     <tableColumn id="3" xr3:uid="{9E8F79E7-43C5-AF41-B8EF-1A9332BF14EA}" name="publisher_id"/>
     <tableColumn id="4" xr3:uid="{1053F528-7EBD-174A-871B-D0618032220F}" name="title"/>
@@ -779,8 +2221,8 @@
   <autoFilter ref="O11:T13" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CE43687C-859D-1F40-BDA4-99499EB16E72}" name="id"/>
-    <tableColumn id="2" xr3:uid="{6970F839-29D6-AF48-9ED9-F80AEA8EBDB8}" name="loan_starts_at_date" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{2A5A1D14-65E8-8741-9C1C-5D6CEC0EAC51}" name="loan_ends_at_date" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{6970F839-29D6-AF48-9ED9-F80AEA8EBDB8}" name="loan_starts_at_date" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{2A5A1D14-65E8-8741-9C1C-5D6CEC0EAC51}" name="loan_ends_at_date" dataDxfId="18"/>
     <tableColumn id="4" xr3:uid="{97CCF238-494E-9D41-8539-ABC80CEB0F33}" name="book_returned_at_date"/>
     <tableColumn id="5" xr3:uid="{DAFFE0E3-462C-F744-A240-14A8F0635450}" name="customerid"/>
     <tableColumn id="6" xr3:uid="{EB8E3328-793F-564A-877C-326817474CA3}" name="fk_stockid"/>
@@ -790,8 +2232,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}" name="Table6" displayName="Table6" ref="O16:P22" totalsRowShown="0">
-  <autoFilter ref="O16:P22" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}" name="Table6" displayName="Table6" ref="J2:K8" totalsRowShown="0">
+  <autoFilter ref="J2:K8" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{38EBFB47-42CE-4249-A9CD-4AEC31A85951}" name="id"/>
     <tableColumn id="2" xr3:uid="{D7B8AC5E-2E4C-E944-A81B-AAECE5723F44}" name="name"/>
@@ -801,47 +2243,47 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}" name="Table7" displayName="Table7" ref="O25:Q31" totalsRowShown="0">
-  <autoFilter ref="O25:Q31" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}" name="Table7" displayName="Table7" ref="C101:E107" totalsRowShown="0">
+  <autoFilter ref="C101:E107" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C98E57F8-CF5A-B04C-9AE6-4326E12BF111}" name="id"/>
-    <tableColumn id="2" xr3:uid="{2B878DF3-03FC-7E45-8203-B9092C488BC3}" name="book_location_floor_id"/>
-    <tableColumn id="3" xr3:uid="{7E6E67C0-8A4A-4348-B9CE-17C91B56993F}" name="book_location_shelf_id"/>
+    <tableColumn id="1" xr3:uid="{C98E57F8-CF5A-B04C-9AE6-4326E12BF111}" name="id" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{2B878DF3-03FC-7E45-8203-B9092C488BC3}" name="book_location_floor_id" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{7E6E67C0-8A4A-4348-B9CE-17C91B56993F}" name="book_location_shelf_id" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}" name="Table8" displayName="Table8" ref="O34:P38" totalsRowShown="0">
-  <autoFilter ref="O34:P38" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}" name="Table8" displayName="Table8" ref="C111:D115" totalsRowShown="0">
+  <autoFilter ref="C111:D115" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{ED3B7FB1-4AD6-3148-A8C5-AD0D54AB86D5}" name="id"/>
-    <tableColumn id="2" xr3:uid="{5CFA8D92-95F5-D848-ACFF-964046FA5E4A}" name="number"/>
+    <tableColumn id="1" xr3:uid="{ED3B7FB1-4AD6-3148-A8C5-AD0D54AB86D5}" name="id" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{5CFA8D92-95F5-D848-ACFF-964046FA5E4A}" name="number" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}" name="Table9" displayName="Table9" ref="O41:P44" totalsRowShown="0">
-  <autoFilter ref="O41:P44" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}" name="Table9" displayName="Table9" ref="F111:G114" totalsRowShown="0">
+  <autoFilter ref="F111:G114" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{34593F39-F4A6-074E-A6EC-EC7E7E8422BE}" name="id"/>
-    <tableColumn id="2" xr3:uid="{E3B4CF1C-A9B2-1C4A-A8F1-45940E10B2C5}" name="number"/>
+    <tableColumn id="1" xr3:uid="{34593F39-F4A6-074E-A6EC-EC7E7E8422BE}" name="id" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{E3B4CF1C-A9B2-1C4A-A8F1-45940E10B2C5}" name="number" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}" name="Table10" displayName="Table10" ref="E54:H95" totalsRowShown="0">
-  <autoFilter ref="E54:H95" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}" name="Table10" displayName="Table10" ref="B55:E96" totalsRowShown="0">
+  <autoFilter ref="B55:E96" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{0E733531-21AD-F946-9111-F766797F96D0}" name="id"/>
-    <tableColumn id="2" xr3:uid="{85903ED5-BC1F-D147-A8EA-8491727CFFC9}" name="book_location_id"/>
+    <tableColumn id="2" xr3:uid="{85903ED5-BC1F-D147-A8EA-8491727CFFC9}" name="book_location_id" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{0A1011E6-FFDE-254C-9381-CF62A47EE8F3}" name="is_in_stock"/>
-    <tableColumn id="4" xr3:uid="{260DA1AD-9E16-104E-A144-7275FF29087D}" name="book_isbn" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{260DA1AD-9E16-104E-A144-7275FF29087D}" name="book_isbn" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1164,11 +2606,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5DA9CCF-71D1-7F40-ABE4-A9F4E589BDAC}">
-  <dimension ref="E4:T110"/>
+  <dimension ref="B1:T115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="8.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="21.33203125" customWidth="1"/>
-    <col min="6" max="6" width="14.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" customWidth="1"/>
     <col min="8" max="8" width="17.5" customWidth="1"/>
     <col min="9" max="9" width="16.83203125" customWidth="1"/>
     <col min="10" max="10" width="17.1640625" customWidth="1"/>
@@ -1184,43 +2629,98 @@
     <col min="20" max="20" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="5:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="J1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="J2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="4:20" x14ac:dyDescent="0.2">
       <c r="E4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="E5" s="7" t="s">
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="E5" s="14" t="s">
         <v>1</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="E6">
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="E6" s="13">
         <v>1</v>
       </c>
       <c r="F6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="E9" t="s">
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="J8">
+        <v>6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="4:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
         <v>4</v>
       </c>
       <c r="I9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="E10" s="6" t="s">
+    <row r="10" spans="4:20" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="F10" t="s">
+      <c r="E10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="32" t="s">
         <v>8</v>
       </c>
       <c r="J10" t="s">
@@ -1239,14 +2739,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="E11" s="1">
+    <row r="11" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D11" s="33">
         <v>9780385086952</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="E11" s="35">
+        <v>1</v>
+      </c>
+      <c r="I11" s="33">
         <v>9780385086952</v>
       </c>
       <c r="J11">
@@ -1261,7 +2761,7 @@
       <c r="M11">
         <v>1974</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="O11" s="5" t="s">
         <v>1</v>
       </c>
       <c r="P11" t="s">
@@ -1280,14 +2780,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="E12" s="1">
+    <row r="12" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D12" s="33">
         <v>9780307743657</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="E12" s="7">
+        <v>1</v>
+      </c>
+      <c r="I12" s="33">
         <v>9780307743657</v>
       </c>
       <c r="J12">
@@ -1305,10 +2805,10 @@
       <c r="O12">
         <v>1</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>46082</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>46090</v>
       </c>
       <c r="S12">
@@ -1318,14 +2818,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="E13" s="1">
+    <row r="13" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D13" s="33">
         <v>9780307743664</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1">
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="I13" s="33">
         <v>9780307743664</v>
       </c>
       <c r="J13">
@@ -1343,10 +2843,10 @@
       <c r="O13">
         <v>2</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>46082</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>46090</v>
       </c>
       <c r="S13">
@@ -1356,14 +2856,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="E14" s="1">
+    <row r="14" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D14" s="33">
         <v>9780670813025</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1">
+      <c r="E14" s="8">
+        <v>1</v>
+      </c>
+      <c r="I14" s="33">
         <v>9780670813025</v>
       </c>
       <c r="J14">
@@ -1379,14 +2879,14 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="15" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="E15" s="1">
+    <row r="15" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D15" s="33">
         <v>9780345418864</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="I15" s="1">
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="I15" s="33">
         <v>9780345418864</v>
       </c>
       <c r="J15">
@@ -1401,18 +2901,15 @@
       <c r="M15">
         <v>1983</v>
       </c>
-      <c r="O15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="E16" s="1">
+    </row>
+    <row r="16" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D16" s="33">
         <v>9780670813032</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="1">
+      <c r="E16" s="8">
+        <v>1</v>
+      </c>
+      <c r="I16" s="33">
         <v>9780670813032</v>
       </c>
       <c r="J16">
@@ -1427,21 +2924,15 @@
       <c r="M16">
         <v>1980</v>
       </c>
-      <c r="O16" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="P16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E17" s="1">
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D17" s="33">
         <v>9780670813049</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="I17" s="1">
+      <c r="E17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="33">
         <v>9780670813049</v>
       </c>
       <c r="J17">
@@ -1456,21 +2947,15 @@
       <c r="M17">
         <v>1981</v>
       </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="P17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E18" s="1">
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D18" s="33">
         <v>9780670813056</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1">
+      <c r="E18" s="8">
+        <v>1</v>
+      </c>
+      <c r="I18" s="33">
         <v>9780670813056</v>
       </c>
       <c r="J18">
@@ -1485,21 +2970,15 @@
       <c r="M18">
         <v>1983</v>
       </c>
-      <c r="O18">
-        <v>2</v>
-      </c>
-      <c r="P18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E19" s="1">
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D19" s="33">
         <v>9780670813063</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="I19" s="1">
+      <c r="E19" s="8">
+        <v>1</v>
+      </c>
+      <c r="I19" s="33">
         <v>9780670813063</v>
       </c>
       <c r="J19">
@@ -1514,21 +2993,15 @@
       <c r="M19">
         <v>1983</v>
       </c>
-      <c r="O19">
-        <v>3</v>
-      </c>
-      <c r="P19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E20" s="1">
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D20" s="33">
         <v>9780670813070</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="I20" s="1">
+      <c r="E20" s="8">
+        <v>1</v>
+      </c>
+      <c r="I20" s="33">
         <v>9780670813070</v>
       </c>
       <c r="J20">
@@ -1543,21 +3016,15 @@
       <c r="M20">
         <v>1984</v>
       </c>
-      <c r="O20">
-        <v>4</v>
-      </c>
-      <c r="P20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E21" s="1">
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D21" s="33">
         <v>9780670813087</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="I21" s="1">
+      <c r="E21" s="8">
+        <v>1</v>
+      </c>
+      <c r="I21" s="33">
         <v>9780670813087</v>
       </c>
       <c r="J21">
@@ -1572,21 +3039,15 @@
       <c r="M21">
         <v>1984</v>
       </c>
-      <c r="O21">
-        <v>5</v>
-      </c>
-      <c r="P21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E22" s="1">
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D22" s="33">
         <v>9780670813094</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="I22" s="1">
+      <c r="E22" s="8">
+        <v>1</v>
+      </c>
+      <c r="I22" s="33">
         <v>9780670813094</v>
       </c>
       <c r="J22">
@@ -1601,21 +3062,15 @@
       <c r="M22">
         <v>1986</v>
       </c>
-      <c r="O22">
-        <v>6</v>
-      </c>
-      <c r="P22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E23" s="1">
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D23" s="33">
         <v>9780670813100</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="I23" s="1">
+      <c r="E23" s="8">
+        <v>1</v>
+      </c>
+      <c r="I23" s="33">
         <v>9780670813100</v>
       </c>
       <c r="J23">
@@ -1631,14 +3086,14 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="24" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E24" s="1">
+    <row r="24" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D24" s="33">
         <v>9780670813117</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="I24" s="1">
+      <c r="E24" s="8">
+        <v>1</v>
+      </c>
+      <c r="I24" s="33">
         <v>9780670813117</v>
       </c>
       <c r="J24">
@@ -1653,18 +3108,15 @@
       <c r="M24">
         <v>1987</v>
       </c>
-      <c r="O24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E25" s="1">
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D25" s="33">
         <v>9780670813124</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="I25" s="1">
+      <c r="E25" s="8">
+        <v>1</v>
+      </c>
+      <c r="I25" s="33">
         <v>9780670813124</v>
       </c>
       <c r="J25">
@@ -1679,24 +3131,15 @@
       <c r="M25">
         <v>1989</v>
       </c>
-      <c r="O25" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="P25" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E26" s="1">
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D26" s="33">
         <v>9780670813131</v>
       </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1">
+      <c r="E26" s="8">
+        <v>1</v>
+      </c>
+      <c r="I26" s="33">
         <v>9780670813131</v>
       </c>
       <c r="J26">
@@ -1711,24 +3154,15 @@
       <c r="M26">
         <v>1991</v>
       </c>
-      <c r="O26">
-        <v>6</v>
-      </c>
-      <c r="P26">
-        <v>1</v>
-      </c>
-      <c r="Q26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E27" s="1">
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D27" s="33">
         <v>9780670813148</v>
       </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="I27" s="1">
+      <c r="E27" s="8">
+        <v>1</v>
+      </c>
+      <c r="I27" s="33">
         <v>9780670813148</v>
       </c>
       <c r="J27">
@@ -1743,24 +3177,15 @@
       <c r="M27">
         <v>1992</v>
       </c>
-      <c r="O27">
-        <v>7</v>
-      </c>
-      <c r="P27">
-        <v>1</v>
-      </c>
-      <c r="Q27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E28" s="1">
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D28" s="33">
         <v>9780670813155</v>
       </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="I28" s="1">
+      <c r="E28" s="8">
+        <v>1</v>
+      </c>
+      <c r="I28" s="33">
         <v>9780670813155</v>
       </c>
       <c r="J28">
@@ -1775,24 +3200,15 @@
       <c r="M28">
         <v>1992</v>
       </c>
-      <c r="O28">
-        <v>8</v>
-      </c>
-      <c r="P28">
-        <v>1</v>
-      </c>
-      <c r="Q28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E29" s="1">
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D29" s="33">
         <v>9780670813162</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="I29" s="1">
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="I29" s="33">
         <v>9780670813162</v>
       </c>
       <c r="J29">
@@ -1807,24 +3223,15 @@
       <c r="M29">
         <v>1994</v>
       </c>
-      <c r="O29">
-        <v>9</v>
-      </c>
-      <c r="P29">
-        <v>2</v>
-      </c>
-      <c r="Q29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E30" s="1">
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D30" s="33">
         <v>9780670813179</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="I30" s="1">
+      <c r="E30" s="8">
+        <v>1</v>
+      </c>
+      <c r="I30" s="33">
         <v>9780670813179</v>
       </c>
       <c r="J30">
@@ -1839,24 +3246,15 @@
       <c r="M30">
         <v>1995</v>
       </c>
-      <c r="O30">
-        <v>10</v>
-      </c>
-      <c r="P30">
-        <v>2</v>
-      </c>
-      <c r="Q30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E31" s="1">
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D31" s="33">
         <v>9780670813186</v>
       </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="I31" s="1">
+      <c r="E31" s="8">
+        <v>1</v>
+      </c>
+      <c r="I31" s="33">
         <v>9780670813186</v>
       </c>
       <c r="J31">
@@ -1871,24 +3269,15 @@
       <c r="M31">
         <v>1996</v>
       </c>
-      <c r="O31">
-        <v>11</v>
-      </c>
-      <c r="P31">
-        <v>2</v>
-      </c>
-      <c r="Q31">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E32" s="1">
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="D32" s="33">
         <v>9780670813193</v>
       </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
+      <c r="E32" s="8">
+        <v>1</v>
+      </c>
+      <c r="I32" s="33">
         <v>9780670813193</v>
       </c>
       <c r="J32">
@@ -1904,14 +3293,14 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E33" s="1">
+    <row r="33" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D33" s="33">
         <v>9780670813209</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="I33" s="1">
+      <c r="E33" s="8">
+        <v>1</v>
+      </c>
+      <c r="I33" s="33">
         <v>9780670813209</v>
       </c>
       <c r="J33">
@@ -1926,18 +3315,15 @@
       <c r="M33">
         <v>1998</v>
       </c>
-      <c r="O33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E34" s="1">
+    </row>
+    <row r="34" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D34" s="33">
         <v>9780670813216</v>
       </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="I34" s="1">
+      <c r="E34" s="8">
+        <v>1</v>
+      </c>
+      <c r="I34" s="33">
         <v>9780670813216</v>
       </c>
       <c r="J34">
@@ -1952,21 +3338,15 @@
       <c r="M34">
         <v>1999</v>
       </c>
-      <c r="O34" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="P34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E35" s="1">
+    </row>
+    <row r="35" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D35" s="33">
         <v>9780670813223</v>
       </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
+      <c r="E35" s="9">
+        <v>1</v>
+      </c>
+      <c r="I35" s="33">
         <v>9780670813223</v>
       </c>
       <c r="J35">
@@ -1981,21 +3361,15 @@
       <c r="M35">
         <v>2001</v>
       </c>
-      <c r="O35">
-        <v>1</v>
-      </c>
-      <c r="P35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E36" s="1">
+    </row>
+    <row r="36" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D36" s="33">
         <v>9780670813230</v>
       </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
+      <c r="E36" s="9">
+        <v>1</v>
+      </c>
+      <c r="I36" s="33">
         <v>9780670813230</v>
       </c>
       <c r="J36">
@@ -2010,21 +3384,15 @@
       <c r="M36">
         <v>2002</v>
       </c>
-      <c r="O36">
-        <v>2</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E37" s="1">
+    </row>
+    <row r="37" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D37" s="33">
         <v>9780670813247</v>
       </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="I37" s="1">
+      <c r="E37" s="8">
+        <v>1</v>
+      </c>
+      <c r="I37" s="33">
         <v>9780670813247</v>
       </c>
       <c r="J37">
@@ -2039,21 +3407,15 @@
       <c r="M37">
         <v>2006</v>
       </c>
-      <c r="O37">
-        <v>3</v>
-      </c>
-      <c r="P37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E38" s="1">
+    </row>
+    <row r="38" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D38" s="33">
         <v>9780670813254</v>
       </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="I38" s="1">
+      <c r="E38" s="9">
+        <v>1</v>
+      </c>
+      <c r="I38" s="33">
         <v>9780670813254</v>
       </c>
       <c r="J38">
@@ -2068,21 +3430,15 @@
       <c r="M38">
         <v>2008</v>
       </c>
-      <c r="O38">
-        <v>4</v>
-      </c>
-      <c r="P38">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E39" s="1">
+    </row>
+    <row r="39" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D39" s="33">
         <v>9780670813261</v>
       </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="I39" s="1">
+      <c r="E39" s="8">
+        <v>1</v>
+      </c>
+      <c r="I39" s="33">
         <v>9780670813261</v>
       </c>
       <c r="J39">
@@ -2098,14 +3454,14 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="40" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E40" s="1">
+    <row r="40" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D40" s="33">
         <v>9780670813278</v>
       </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="I40" s="1">
+      <c r="E40" s="8">
+        <v>1</v>
+      </c>
+      <c r="I40" s="33">
         <v>9780670813278</v>
       </c>
       <c r="J40">
@@ -2114,24 +3470,21 @@
       <c r="K40">
         <v>2</v>
       </c>
-      <c r="L40" s="2">
+      <c r="L40" s="1">
         <v>23337</v>
       </c>
       <c r="M40">
         <v>2011</v>
       </c>
-      <c r="O40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E41" s="1">
+    </row>
+    <row r="41" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D41" s="33">
         <v>9780670813285</v>
       </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="I41" s="1">
+      <c r="E41" s="8">
+        <v>1</v>
+      </c>
+      <c r="I41" s="33">
         <v>9780670813285</v>
       </c>
       <c r="J41">
@@ -2146,21 +3499,15 @@
       <c r="M41">
         <v>2014</v>
       </c>
-      <c r="O41" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="P41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E42" s="1">
+    </row>
+    <row r="42" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D42" s="33">
         <v>9780670813292</v>
       </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="I42" s="1">
+      <c r="E42" s="8">
+        <v>1</v>
+      </c>
+      <c r="I42" s="33">
         <v>9780670813292</v>
       </c>
       <c r="J42">
@@ -2175,21 +3522,15 @@
       <c r="M42">
         <v>2015</v>
       </c>
-      <c r="O42">
-        <v>1</v>
-      </c>
-      <c r="P42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E43" s="1">
+    </row>
+    <row r="43" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D43" s="33">
         <v>9780670813308</v>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="I43" s="1">
+      <c r="E43" s="8">
+        <v>1</v>
+      </c>
+      <c r="I43" s="33">
         <v>9780670813308</v>
       </c>
       <c r="J43">
@@ -2204,21 +3545,15 @@
       <c r="M43">
         <v>2016</v>
       </c>
-      <c r="O43">
-        <v>2</v>
-      </c>
-      <c r="P43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E44" s="1">
+    </row>
+    <row r="44" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D44" s="33">
         <v>9780670813315</v>
       </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="I44" s="1">
+      <c r="E44" s="8">
+        <v>1</v>
+      </c>
+      <c r="I44" s="33">
         <v>9780670813315</v>
       </c>
       <c r="J44">
@@ -2233,21 +3568,15 @@
       <c r="M44">
         <v>2013</v>
       </c>
-      <c r="O44">
-        <v>3</v>
-      </c>
-      <c r="P44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E45" s="1">
+    </row>
+    <row r="45" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D45" s="33">
         <v>9780670813322</v>
       </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="I45" s="1">
+      <c r="E45" s="8">
+        <v>1</v>
+      </c>
+      <c r="I45" s="33">
         <v>9780670813322</v>
       </c>
       <c r="J45">
@@ -2263,14 +3592,14 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="46" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E46" s="1">
+    <row r="46" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D46" s="33">
         <v>9780670813339</v>
       </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="I46" s="1">
+      <c r="E46" s="8">
+        <v>1</v>
+      </c>
+      <c r="I46" s="33">
         <v>9780670813339</v>
       </c>
       <c r="J46">
@@ -2289,14 +3618,14 @@
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E47" s="1">
+    <row r="47" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D47" s="33">
         <v>9780670813346</v>
       </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="I47" s="1">
+      <c r="E47" s="8">
+        <v>1</v>
+      </c>
+      <c r="I47" s="33">
         <v>9780670813346</v>
       </c>
       <c r="J47">
@@ -2311,21 +3640,21 @@
       <c r="M47">
         <v>2021</v>
       </c>
-      <c r="O47" s="7" t="s">
+      <c r="O47" s="5" t="s">
         <v>1</v>
       </c>
       <c r="P47" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="5:16" x14ac:dyDescent="0.2">
-      <c r="E48" s="1">
+    <row r="48" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D48" s="33">
         <v>9780670813353</v>
       </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="I48" s="1">
+      <c r="E48" s="8">
+        <v>1</v>
+      </c>
+      <c r="I48" s="33">
         <v>9780670813353</v>
       </c>
       <c r="J48">
@@ -2347,14 +3676,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E49" s="1">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D49" s="33">
         <v>9780670813360</v>
       </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="I49" s="1">
+      <c r="E49" s="8">
+        <v>1</v>
+      </c>
+      <c r="I49" s="33">
         <v>9780670813360</v>
       </c>
       <c r="J49">
@@ -2370,14 +3699,14 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="50" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E50" s="1">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D50" s="33">
         <v>9780670813377</v>
       </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="I50" s="1">
+      <c r="E50" s="8">
+        <v>1</v>
+      </c>
+      <c r="I50" s="33">
         <v>9780670813377</v>
       </c>
       <c r="J50">
@@ -2393,14 +3722,14 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="51" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E51" s="1">
+    <row r="51" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D51" s="34">
         <v>9780670813384</v>
       </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="I51" s="1">
+      <c r="E51" s="9">
+        <v>1</v>
+      </c>
+      <c r="I51" s="34">
         <v>9780670813384</v>
       </c>
       <c r="J51">
@@ -2416,265 +3745,231 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="53" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E53" t="s">
+    <row r="52" spans="2:17" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>76</v>
       </c>
-      <c r="J53" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="54" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E54" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" t="s">
+    </row>
+    <row r="55" spans="2:17" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="G54" t="s">
+      <c r="D55" t="s">
         <v>79</v>
       </c>
-      <c r="H54" t="s">
+      <c r="E55" t="s">
         <v>6</v>
       </c>
-      <c r="J54" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K54" t="s">
-        <v>80</v>
-      </c>
-      <c r="L54" t="s">
-        <v>81</v>
-      </c>
-      <c r="M54" t="s">
-        <v>82</v>
-      </c>
-      <c r="N54" t="s">
-        <v>83</v>
-      </c>
-      <c r="O54" t="s">
-        <v>84</v>
-      </c>
-      <c r="P54" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55">
+      <c r="G55" t="s">
+        <v>104</v>
+      </c>
+      <c r="K55" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" s="29">
         <v>6</v>
       </c>
-      <c r="G55" t="b">
-        <v>1</v>
-      </c>
-      <c r="H55" s="3">
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2">
         <v>9780385086952</v>
       </c>
-      <c r="J55">
-        <v>1</v>
-      </c>
-      <c r="K55" t="s">
-        <v>87</v>
-      </c>
-      <c r="L55" t="s">
-        <v>88</v>
-      </c>
-      <c r="M55">
-        <v>1</v>
-      </c>
-      <c r="N55">
+      <c r="G56" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H56" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L56" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57" s="29">
+        <v>6</v>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9780307743657</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57" s="37">
+        <v>9780385086952</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B58">
         <v>3</v>
       </c>
-      <c r="O55">
+      <c r="C58" s="29">
+        <v>6</v>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="2">
+        <v>9780307743664</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" s="38">
+        <v>9780307743657</v>
+      </c>
+      <c r="K58">
+        <v>2</v>
+      </c>
+      <c r="L58" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B59">
+        <v>4</v>
+      </c>
+      <c r="C59" s="29">
+        <v>7</v>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="3">
+        <v>9780670813025</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59" s="37">
+        <v>9780307743664</v>
+      </c>
+      <c r="K59">
         <v>3</v>
       </c>
-      <c r="P55">
-        <v>1</v>
-      </c>
-      <c r="Q55">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="56" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E56">
-        <v>2</v>
-      </c>
-      <c r="F56">
+      <c r="L59" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B60">
+        <v>5</v>
+      </c>
+      <c r="C60" s="29">
+        <v>7</v>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="2">
+        <v>9780345418864</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60" s="38">
+        <v>9780670813025</v>
+      </c>
+      <c r="K60">
+        <v>4</v>
+      </c>
+      <c r="L60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B61">
         <v>6</v>
       </c>
-      <c r="G56" t="b">
-        <v>1</v>
-      </c>
-      <c r="H56" s="4">
-        <v>9780307743657</v>
-      </c>
-      <c r="J56">
-        <v>2</v>
-      </c>
-      <c r="K56" t="s">
-        <v>89</v>
-      </c>
-      <c r="L56" t="s">
-        <v>90</v>
-      </c>
-      <c r="M56">
-        <v>1</v>
-      </c>
-      <c r="N56">
-        <v>3</v>
-      </c>
-      <c r="O56">
-        <v>3</v>
-      </c>
-      <c r="P56">
-        <v>1</v>
-      </c>
-      <c r="Q56">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="57" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E57">
-        <v>3</v>
-      </c>
-      <c r="F57">
+      <c r="C61" s="29">
         <v>6</v>
       </c>
-      <c r="G57" t="b">
-        <v>1</v>
-      </c>
-      <c r="H57" s="3">
-        <v>9780307743664</v>
-      </c>
-    </row>
-    <row r="58" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E58">
-        <v>4</v>
-      </c>
-      <c r="F58">
+      <c r="D61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9780670813032</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61" s="37">
+        <v>9780345418864</v>
+      </c>
+      <c r="K61">
+        <v>5</v>
+      </c>
+      <c r="L61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B62">
         <v>7</v>
       </c>
-      <c r="G58" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58" s="4">
-        <v>9780670813025</v>
-      </c>
-      <c r="J58" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="59" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E59">
-        <v>5</v>
-      </c>
-      <c r="F59">
-        <v>7</v>
-      </c>
-      <c r="G59" t="b">
-        <v>1</v>
-      </c>
-      <c r="H59" s="3">
-        <v>9780345418864</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K59" t="s">
-        <v>92</v>
-      </c>
-      <c r="L59" t="s">
-        <v>93</v>
-      </c>
-      <c r="M59" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="60" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E60">
+      <c r="C62" s="29">
         <v>6</v>
       </c>
-      <c r="F60">
-        <v>6</v>
-      </c>
-      <c r="G60" t="b">
-        <v>1</v>
-      </c>
-      <c r="H60" s="4">
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="2">
+        <v>9780670813049</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62" s="38">
         <v>9780670813032</v>
-      </c>
-      <c r="J60" s="7">
-        <v>1</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="L60" s="5">
-        <v>46142.371099537035</v>
-      </c>
-      <c r="M60" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="61" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E61">
-        <v>7</v>
-      </c>
-      <c r="F61">
-        <v>6</v>
-      </c>
-      <c r="G61" t="b">
-        <v>1</v>
-      </c>
-      <c r="H61" s="3">
-        <v>9780670813049</v>
-      </c>
-    </row>
-    <row r="62" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E62">
-        <v>8</v>
-      </c>
-      <c r="F62">
-        <v>8</v>
-      </c>
-      <c r="G62" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62" s="4">
-        <v>9780670813056</v>
-      </c>
-      <c r="J62" t="s">
-        <v>95</v>
       </c>
       <c r="M62" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="63" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E63">
-        <v>9</v>
-      </c>
-      <c r="F63">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B63">
         <v>8</v>
       </c>
-      <c r="G63" t="b">
-        <v>1</v>
-      </c>
-      <c r="H63" s="3">
-        <v>9780670813063</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K63" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" s="7" t="s">
+      <c r="C63" s="29">
+        <v>8</v>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="3">
+        <v>9780670813056</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63" s="37">
+        <v>9780670813049</v>
+      </c>
+      <c r="M63" s="5" t="s">
         <v>1</v>
       </c>
       <c r="N63" t="s">
@@ -2684,24 +3979,24 @@
         <v>98</v>
       </c>
     </row>
-    <row r="64" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E64">
-        <v>10</v>
-      </c>
-      <c r="F64">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B64">
+        <v>9</v>
+      </c>
+      <c r="C64" s="29">
         <v>8</v>
       </c>
-      <c r="G64" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" s="4">
-        <v>9780670813070</v>
-      </c>
-      <c r="J64">
-        <v>1</v>
-      </c>
-      <c r="K64" t="s">
-        <v>99</v>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="2">
+        <v>9780670813063</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" s="38">
+        <v>9780670813056</v>
       </c>
       <c r="M64">
         <v>1</v>
@@ -2709,31 +4004,31 @@
       <c r="N64">
         <v>1010</v>
       </c>
-      <c r="P64" s="7" t="s">
+      <c r="P64" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="Q64" s="7" t="s">
+      <c r="Q64" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E65">
-        <v>11</v>
-      </c>
-      <c r="F65">
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B65">
+        <v>10</v>
+      </c>
+      <c r="C65" s="29">
         <v>8</v>
       </c>
-      <c r="G65" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" s="3">
-        <v>9780670813087</v>
-      </c>
-      <c r="J65">
-        <v>2</v>
-      </c>
-      <c r="K65" t="s">
-        <v>102</v>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3">
+        <v>9780670813070</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" s="37">
+        <v>9780670813063</v>
       </c>
       <c r="M65">
         <v>2</v>
@@ -2748,18 +4043,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E66">
-        <v>12</v>
-      </c>
-      <c r="F66">
-        <v>6</v>
-      </c>
-      <c r="G66" t="b">
-        <v>1</v>
-      </c>
-      <c r="H66" s="4">
-        <v>9780670813094</v>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B66">
+        <v>11</v>
+      </c>
+      <c r="C66" s="29">
+        <v>8</v>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="2">
+        <v>9780670813087</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" s="38">
+        <v>9780670813070</v>
       </c>
       <c r="M66">
         <v>3</v>
@@ -2768,253 +4069,256 @@
         <v>8263</v>
       </c>
     </row>
-    <row r="67" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E67">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B67">
+        <v>12</v>
+      </c>
+      <c r="C67" s="29">
+        <v>6</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3">
+        <v>9780670813094</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67" s="37">
+        <v>9780670813087</v>
+      </c>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B68">
         <v>13</v>
       </c>
-      <c r="F67">
+      <c r="C68" s="29">
         <v>6</v>
       </c>
-      <c r="G67" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" s="3">
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="2">
         <v>9780670813100</v>
       </c>
-    </row>
-    <row r="68" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E68">
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68" s="38">
+        <v>9780670813094</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B69">
         <v>14</v>
       </c>
-      <c r="F68">
+      <c r="C69" s="29">
         <v>6</v>
       </c>
-      <c r="G68" t="b">
-        <v>1</v>
-      </c>
-      <c r="H68" s="4">
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="3">
         <v>9780670813117</v>
       </c>
-      <c r="J68" t="s">
-        <v>103</v>
-      </c>
-      <c r="M68" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="69" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E69">
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69" s="37">
+        <v>9780670813100</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B70">
         <v>15</v>
       </c>
-      <c r="F69">
+      <c r="C70" s="29">
         <v>6</v>
       </c>
-      <c r="G69" t="b">
-        <v>1</v>
-      </c>
-      <c r="H69" s="3">
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="2">
         <v>9780670813124</v>
       </c>
-      <c r="J69" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K69" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="N69" s="7" t="s">
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70" s="38">
+        <v>9780670813117</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B71">
+        <v>16</v>
+      </c>
+      <c r="C71" s="29">
         <v>6</v>
       </c>
-    </row>
-    <row r="70" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E70">
-        <v>16</v>
-      </c>
-      <c r="F70">
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="3">
+        <v>9780670813131</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71" s="37">
+        <v>9780670813124</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B72">
+        <v>17</v>
+      </c>
+      <c r="C72" s="29">
         <v>6</v>
       </c>
-      <c r="G70" t="b">
-        <v>1</v>
-      </c>
-      <c r="H70" s="4">
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="2">
+        <v>9780670813148</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72" s="38">
         <v>9780670813131</v>
       </c>
-      <c r="J70">
-        <v>1</v>
-      </c>
-      <c r="K70" t="s">
-        <v>105</v>
-      </c>
-      <c r="M70">
-        <v>1</v>
-      </c>
-      <c r="N70" s="3">
-        <v>9780385086952</v>
-      </c>
-    </row>
-    <row r="71" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E71">
-        <v>17</v>
-      </c>
-      <c r="F71">
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B73">
+        <v>18</v>
+      </c>
+      <c r="C73" s="29">
         <v>6</v>
       </c>
-      <c r="G71" t="b">
-        <v>1</v>
-      </c>
-      <c r="H71" s="3">
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="3">
+        <v>9780670813155</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73" s="37">
         <v>9780670813148</v>
       </c>
-      <c r="J71">
-        <v>2</v>
-      </c>
-      <c r="K71" t="s">
-        <v>106</v>
-      </c>
-      <c r="M71">
-        <v>1</v>
-      </c>
-      <c r="N71" s="4">
-        <v>9780307743657</v>
-      </c>
-    </row>
-    <row r="72" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E72">
-        <v>18</v>
-      </c>
-      <c r="F72">
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B74">
+        <v>19</v>
+      </c>
+      <c r="C74" s="29">
         <v>6</v>
       </c>
-      <c r="G72" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72" s="4">
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="2">
+        <v>9780670813162</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74" s="38">
         <v>9780670813155</v>
       </c>
-      <c r="J72">
-        <v>3</v>
-      </c>
-      <c r="K72" t="s">
-        <v>107</v>
-      </c>
-      <c r="M72">
-        <v>1</v>
-      </c>
-      <c r="N72" s="3">
-        <v>9780307743664</v>
-      </c>
-    </row>
-    <row r="73" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E73">
-        <v>19</v>
-      </c>
-      <c r="F73">
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B75">
+        <v>20</v>
+      </c>
+      <c r="C75" s="29">
         <v>6</v>
       </c>
-      <c r="G73" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73" s="3">
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="3">
+        <v>9780670813179</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75" s="37">
         <v>9780670813162</v>
       </c>
-      <c r="J73">
-        <v>4</v>
-      </c>
-      <c r="K73" t="s">
-        <v>108</v>
-      </c>
-      <c r="M73">
-        <v>1</v>
-      </c>
-      <c r="N73" s="4">
-        <v>9780670813025</v>
-      </c>
-    </row>
-    <row r="74" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E74">
-        <v>20</v>
-      </c>
-      <c r="F74">
+      <c r="M75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B76">
+        <v>21</v>
+      </c>
+      <c r="C76" s="29">
         <v>6</v>
       </c>
-      <c r="G74" t="b">
-        <v>1</v>
-      </c>
-      <c r="H74" s="4">
+      <c r="D76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" s="2">
+        <v>9780670813186</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76" s="38">
         <v>9780670813179</v>
-      </c>
-      <c r="J74">
-        <v>5</v>
-      </c>
-      <c r="K74" t="s">
-        <v>109</v>
-      </c>
-      <c r="M74">
-        <v>1</v>
-      </c>
-      <c r="N74" s="3">
-        <v>9780345418864</v>
-      </c>
-    </row>
-    <row r="75" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E75">
-        <v>21</v>
-      </c>
-      <c r="F75">
-        <v>6</v>
-      </c>
-      <c r="G75" t="b">
-        <v>1</v>
-      </c>
-      <c r="H75" s="3">
-        <v>9780670813186</v>
-      </c>
-      <c r="M75">
-        <v>1</v>
-      </c>
-      <c r="N75" s="4">
-        <v>9780670813032</v>
-      </c>
-    </row>
-    <row r="76" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E76">
-        <v>22</v>
-      </c>
-      <c r="F76">
-        <v>6</v>
-      </c>
-      <c r="G76" t="b">
-        <v>1</v>
-      </c>
-      <c r="H76" s="4">
-        <v>9780670813193</v>
       </c>
       <c r="J76" t="s">
         <v>110</v>
       </c>
-      <c r="M76">
-        <v>1</v>
-      </c>
-      <c r="N76" s="3">
-        <v>9780670813049</v>
-      </c>
-    </row>
-    <row r="77" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E77">
-        <v>23</v>
-      </c>
-      <c r="F77">
+      <c r="M76" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N76" t="s">
+        <v>80</v>
+      </c>
+      <c r="O76" t="s">
+        <v>81</v>
+      </c>
+      <c r="P76" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>83</v>
+      </c>
+      <c r="R76" t="s">
+        <v>84</v>
+      </c>
+      <c r="S76" t="s">
+        <v>85</v>
+      </c>
+      <c r="T76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B77">
+        <v>22</v>
+      </c>
+      <c r="C77" s="29">
         <v>6</v>
       </c>
-      <c r="G77" t="b">
-        <v>1</v>
-      </c>
-      <c r="H77" s="3">
-        <v>9780670813209</v>
-      </c>
-      <c r="J77" s="7" t="s">
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="3">
+        <v>9780670813193</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77" s="37">
+        <v>9780670813186</v>
+      </c>
+      <c r="J77" s="5" t="s">
         <v>1</v>
       </c>
       <c r="K77" t="s">
@@ -3023,22 +4327,46 @@
       <c r="M77">
         <v>1</v>
       </c>
-      <c r="N77" s="4">
-        <v>9780670813056</v>
-      </c>
-    </row>
-    <row r="78" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E78">
-        <v>24</v>
-      </c>
-      <c r="F78">
+      <c r="N77" t="s">
+        <v>87</v>
+      </c>
+      <c r="O77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P77">
+        <v>1</v>
+      </c>
+      <c r="Q77">
+        <v>3</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>1</v>
+      </c>
+      <c r="T77">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="78" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B78">
+        <v>23</v>
+      </c>
+      <c r="C78" s="29">
         <v>6</v>
       </c>
-      <c r="G78" t="b">
-        <v>1</v>
-      </c>
-      <c r="H78" s="4">
-        <v>9780670813216</v>
+      <c r="D78" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="2">
+        <v>9780670813209</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78" s="38">
+        <v>9780670813193</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -3047,24 +4375,48 @@
         <v>111</v>
       </c>
       <c r="M78">
-        <v>1</v>
-      </c>
-      <c r="N78" s="3">
-        <v>9780670813063</v>
-      </c>
-    </row>
-    <row r="79" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E79">
-        <v>25</v>
-      </c>
-      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="N78" t="s">
+        <v>89</v>
+      </c>
+      <c r="O78" t="s">
+        <v>90</v>
+      </c>
+      <c r="P78">
+        <v>1</v>
+      </c>
+      <c r="Q78">
+        <v>3</v>
+      </c>
+      <c r="R78">
+        <v>3</v>
+      </c>
+      <c r="S78">
+        <v>1</v>
+      </c>
+      <c r="T78">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B79">
+        <v>24</v>
+      </c>
+      <c r="C79" s="29">
         <v>6</v>
       </c>
-      <c r="G79" t="b">
-        <v>1</v>
-      </c>
-      <c r="H79" s="3">
-        <v>9780670813223</v>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="3">
+        <v>9780670813216</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79" s="37">
+        <v>9780670813209</v>
       </c>
       <c r="J79">
         <v>2</v>
@@ -3072,25 +4424,25 @@
       <c r="K79" t="s">
         <v>112</v>
       </c>
-      <c r="M79">
-        <v>1</v>
-      </c>
-      <c r="N79" s="4">
-        <v>9780670813070</v>
-      </c>
-    </row>
-    <row r="80" spans="5:17" x14ac:dyDescent="0.2">
-      <c r="E80">
-        <v>26</v>
-      </c>
-      <c r="F80">
+    </row>
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B80">
+        <v>25</v>
+      </c>
+      <c r="C80" s="29">
         <v>6</v>
       </c>
-      <c r="G80" t="b">
-        <v>1</v>
-      </c>
-      <c r="H80" s="4">
-        <v>9780670813230</v>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" s="2">
+        <v>9780670813223</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80" s="38">
+        <v>9780670813216</v>
       </c>
       <c r="J80">
         <v>3</v>
@@ -3098,94 +4450,94 @@
       <c r="K80" t="s">
         <v>113</v>
       </c>
-      <c r="M80">
-        <v>1</v>
-      </c>
-      <c r="N80" s="3">
-        <v>9780670813087</v>
-      </c>
-    </row>
-    <row r="81" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E81">
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B81">
+        <v>26</v>
+      </c>
+      <c r="C81" s="29">
+        <v>6</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="3">
+        <v>9780670813230</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81" s="37">
+        <v>9780670813223</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B82">
         <v>27</v>
       </c>
-      <c r="F81">
+      <c r="C82" s="29">
         <v>6</v>
       </c>
-      <c r="G81" t="b">
-        <v>1</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="D82" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="2">
         <v>9780670813247</v>
       </c>
-      <c r="M81">
-        <v>1</v>
-      </c>
-      <c r="N81" s="4">
-        <v>9780670813094</v>
-      </c>
-    </row>
-    <row r="82" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E82">
-        <v>28</v>
-      </c>
-      <c r="F82">
-        <v>6</v>
-      </c>
-      <c r="G82" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82" s="4">
-        <v>9780670813254</v>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82" s="38">
+        <v>9780670813230</v>
       </c>
       <c r="J82" t="s">
         <v>114</v>
       </c>
-      <c r="M82">
-        <v>1</v>
-      </c>
-      <c r="N82" s="3">
-        <v>9780670813100</v>
-      </c>
-    </row>
-    <row r="83" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E83">
-        <v>29</v>
-      </c>
-      <c r="F83">
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B83">
+        <v>28</v>
+      </c>
+      <c r="C83" s="29">
         <v>6</v>
       </c>
-      <c r="G83" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83" s="3">
-        <v>9780670813261</v>
-      </c>
-      <c r="J83" s="7" t="s">
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="3">
+        <v>9780670813254</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83" s="37">
+        <v>9780670813247</v>
+      </c>
+      <c r="J83" s="5" t="s">
         <v>1</v>
       </c>
       <c r="K83" t="s">
         <v>115</v>
       </c>
-      <c r="M83">
-        <v>1</v>
-      </c>
-      <c r="N83" s="4">
-        <v>9780670813117</v>
-      </c>
-    </row>
-    <row r="84" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E84">
-        <v>30</v>
-      </c>
-      <c r="F84">
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B84">
+        <v>29</v>
+      </c>
+      <c r="C84" s="29">
         <v>6</v>
       </c>
-      <c r="G84" t="b">
-        <v>1</v>
-      </c>
-      <c r="H84" s="4">
-        <v>9780670813278</v>
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="2">
+        <v>9780670813261</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84" s="38">
+        <v>9780670813254</v>
       </c>
       <c r="J84">
         <v>1</v>
@@ -3193,25 +4545,25 @@
       <c r="K84" t="s">
         <v>116</v>
       </c>
-      <c r="M84">
-        <v>1</v>
-      </c>
-      <c r="N84" s="3">
-        <v>9780670813124</v>
-      </c>
-    </row>
-    <row r="85" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E85">
-        <v>31</v>
-      </c>
-      <c r="F85">
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B85">
+        <v>30</v>
+      </c>
+      <c r="C85" s="29">
         <v>6</v>
       </c>
-      <c r="G85" t="b">
-        <v>1</v>
-      </c>
-      <c r="H85" s="3">
-        <v>9780670813285</v>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="3">
+        <v>9780670813278</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85" s="37">
+        <v>9780670813261</v>
       </c>
       <c r="J85">
         <v>2</v>
@@ -3219,25 +4571,25 @@
       <c r="K85" t="s">
         <v>117</v>
       </c>
-      <c r="M85">
-        <v>1</v>
-      </c>
-      <c r="N85" s="4">
-        <v>9780670813131</v>
-      </c>
-    </row>
-    <row r="86" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E86">
-        <v>32</v>
-      </c>
-      <c r="F86">
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B86">
+        <v>31</v>
+      </c>
+      <c r="C86" s="29">
         <v>6</v>
       </c>
-      <c r="G86" t="b">
-        <v>1</v>
-      </c>
-      <c r="H86" s="4">
-        <v>9780670813292</v>
+      <c r="D86" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="2">
+        <v>9780670813285</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86" s="38">
+        <v>9780670813278</v>
       </c>
       <c r="J86">
         <v>3</v>
@@ -3245,317 +4597,425 @@
       <c r="K86" t="s">
         <v>118</v>
       </c>
-      <c r="M86">
-        <v>1</v>
-      </c>
-      <c r="N86" s="3">
-        <v>9780670813148</v>
-      </c>
-    </row>
-    <row r="87" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E87">
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B87">
+        <v>32</v>
+      </c>
+      <c r="C87" s="29">
+        <v>6</v>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="3">
+        <v>9780670813292</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87" s="37">
+        <v>9780670813285</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B88">
         <v>33</v>
       </c>
-      <c r="F87">
+      <c r="C88" s="29">
         <v>6</v>
       </c>
-      <c r="G87" t="b">
-        <v>1</v>
-      </c>
-      <c r="H87" s="3">
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="2">
         <v>9780670813308</v>
       </c>
-      <c r="M87">
-        <v>1</v>
-      </c>
-      <c r="N87" s="4">
-        <v>9780670813155</v>
-      </c>
-    </row>
-    <row r="88" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E88">
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88" s="38">
+        <v>9780670813292</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B89">
         <v>34</v>
       </c>
-      <c r="F88">
+      <c r="C89" s="29">
         <v>6</v>
       </c>
-      <c r="G88" t="b">
-        <v>1</v>
-      </c>
-      <c r="H88" s="4">
+      <c r="D89" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="3">
         <v>9780670813315</v>
       </c>
-      <c r="M88">
-        <v>1</v>
-      </c>
-      <c r="N88" s="3">
-        <v>9780670813162</v>
-      </c>
-    </row>
-    <row r="89" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E89">
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89" s="37">
+        <v>9780670813308</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B90">
         <v>35</v>
       </c>
-      <c r="F89">
+      <c r="C90" s="29">
         <v>6</v>
       </c>
-      <c r="G89" t="b">
-        <v>1</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="D90" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="2">
         <v>9780670813322</v>
       </c>
-      <c r="M89">
-        <v>1</v>
-      </c>
-      <c r="N89" s="4">
-        <v>9780670813179</v>
-      </c>
-    </row>
-    <row r="90" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E90">
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90" s="38">
+        <v>9780670813315</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B91">
         <v>36</v>
       </c>
-      <c r="F90">
+      <c r="C91" s="29">
         <v>6</v>
       </c>
-      <c r="G90" t="b">
-        <v>1</v>
-      </c>
-      <c r="H90" s="4">
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="3">
         <v>9780670813339</v>
       </c>
-      <c r="M90">
-        <v>1</v>
-      </c>
-      <c r="N90" s="3">
-        <v>9780670813186</v>
-      </c>
-    </row>
-    <row r="91" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E91">
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91" s="37">
+        <v>9780670813322</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B92">
         <v>37</v>
       </c>
-      <c r="F91">
+      <c r="C92" s="29">
         <v>6</v>
       </c>
-      <c r="G91" t="b">
-        <v>1</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="D92" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2">
         <v>9780670813346</v>
       </c>
-      <c r="M91">
-        <v>1</v>
-      </c>
-      <c r="N91" s="4">
-        <v>9780670813193</v>
-      </c>
-    </row>
-    <row r="92" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E92">
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92" s="38">
+        <v>9780670813339</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B93">
         <v>38</v>
       </c>
-      <c r="F92">
+      <c r="C93" s="29">
         <v>6</v>
       </c>
-      <c r="G92" t="b">
-        <v>1</v>
-      </c>
-      <c r="H92" s="4">
+      <c r="D93" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="3">
         <v>9780670813353</v>
       </c>
-      <c r="M92">
-        <v>1</v>
-      </c>
-      <c r="N92" s="3">
-        <v>9780670813209</v>
-      </c>
-    </row>
-    <row r="93" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E93">
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93" s="37">
+        <v>9780670813346</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B94">
         <v>39</v>
       </c>
-      <c r="F93">
+      <c r="C94" s="29">
         <v>6</v>
       </c>
-      <c r="G93" t="b">
-        <v>1</v>
-      </c>
-      <c r="H93" s="3">
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="2">
         <v>9780670813360</v>
       </c>
-      <c r="M93">
-        <v>1</v>
-      </c>
-      <c r="N93" s="4">
-        <v>9780670813216</v>
-      </c>
-    </row>
-    <row r="94" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E94">
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94" s="38">
+        <v>9780670813353</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B95">
         <v>40</v>
       </c>
-      <c r="F94">
+      <c r="C95" s="29">
         <v>6</v>
       </c>
-      <c r="G94" t="b">
-        <v>1</v>
-      </c>
-      <c r="H94" s="4">
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="3">
         <v>9780670813377</v>
       </c>
-      <c r="M94">
-        <v>1</v>
-      </c>
-      <c r="N94" s="3">
-        <v>9780670813223</v>
-      </c>
-    </row>
-    <row r="95" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E95">
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95" s="37">
+        <v>9780670813360</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B96">
         <v>41</v>
       </c>
-      <c r="F95">
+      <c r="C96" s="30">
         <v>6</v>
       </c>
-      <c r="G95" t="b">
-        <v>1</v>
-      </c>
-      <c r="H95" s="3">
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" s="2">
         <v>9780670813384</v>
       </c>
-      <c r="M95">
-        <v>1</v>
-      </c>
-      <c r="N95" s="4">
-        <v>9780670813230</v>
-      </c>
-    </row>
-    <row r="96" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="M96">
-        <v>1</v>
-      </c>
-      <c r="N96" s="3">
-        <v>9780670813247</v>
-      </c>
-    </row>
-    <row r="97" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M97">
-        <v>1</v>
-      </c>
-      <c r="N97" s="4">
-        <v>9780670813254</v>
-      </c>
-    </row>
-    <row r="98" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M98">
-        <v>1</v>
-      </c>
-      <c r="N98" s="3">
-        <v>9780670813261</v>
-      </c>
-    </row>
-    <row r="99" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M99">
-        <v>1</v>
-      </c>
-      <c r="N99" s="4">
-        <v>9780670813278</v>
-      </c>
-    </row>
-    <row r="100" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M100">
-        <v>1</v>
-      </c>
-      <c r="N100" s="3">
-        <v>9780670813285</v>
-      </c>
-    </row>
-    <row r="101" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M101">
-        <v>1</v>
-      </c>
-      <c r="N101" s="4">
-        <v>9780670813292</v>
-      </c>
-    </row>
-    <row r="102" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M102">
-        <v>1</v>
-      </c>
-      <c r="N102" s="3">
-        <v>9780670813308</v>
-      </c>
-    </row>
-    <row r="103" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M103">
-        <v>1</v>
-      </c>
-      <c r="N103" s="4">
-        <v>9780670813315</v>
-      </c>
-    </row>
-    <row r="104" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M104">
-        <v>1</v>
-      </c>
-      <c r="N104" s="3">
-        <v>9780670813322</v>
-      </c>
-    </row>
-    <row r="105" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M105">
-        <v>1</v>
-      </c>
-      <c r="N105" s="4">
-        <v>9780670813339</v>
-      </c>
-    </row>
-    <row r="106" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M106">
-        <v>1</v>
-      </c>
-      <c r="N106" s="3">
-        <v>9780670813346</v>
-      </c>
-    </row>
-    <row r="107" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M107">
-        <v>1</v>
-      </c>
-      <c r="N107" s="4">
-        <v>9780670813353</v>
-      </c>
-    </row>
-    <row r="108" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M108">
-        <v>1</v>
-      </c>
-      <c r="N108" s="3">
-        <v>9780670813360</v>
-      </c>
-    </row>
-    <row r="109" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M109">
-        <v>1</v>
-      </c>
-      <c r="N109" s="4">
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96" s="38">
         <v>9780670813377</v>
       </c>
     </row>
-    <row r="110" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M110">
-        <v>1</v>
-      </c>
-      <c r="N110" s="3">
+    <row r="97" spans="3:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97" s="39">
         <v>9780670813384</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="100" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>41</v>
+      </c>
+      <c r="G100" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C101" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="D101" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E101" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" t="s">
+        <v>92</v>
+      </c>
+      <c r="I101" t="s">
+        <v>93</v>
+      </c>
+      <c r="J101" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C102" s="29">
+        <v>6</v>
+      </c>
+      <c r="D102" s="26">
+        <v>1</v>
+      </c>
+      <c r="E102" s="16">
+        <v>1</v>
+      </c>
+      <c r="G102" s="5">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J102" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="103" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C103" s="29">
+        <v>7</v>
+      </c>
+      <c r="D103" s="26">
+        <v>1</v>
+      </c>
+      <c r="E103" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C104" s="29">
+        <v>8</v>
+      </c>
+      <c r="D104" s="26">
+        <v>1</v>
+      </c>
+      <c r="E104" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C105" s="29">
+        <v>9</v>
+      </c>
+      <c r="D105" s="26">
+        <v>2</v>
+      </c>
+      <c r="E105" s="16">
+        <v>1</v>
+      </c>
+      <c r="L105" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="106" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C106" s="29">
+        <v>10</v>
+      </c>
+      <c r="D106" s="26">
+        <v>2</v>
+      </c>
+      <c r="E106" s="16">
+        <v>2</v>
+      </c>
+      <c r="L106" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M106" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="107" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C107" s="30">
+        <v>11</v>
+      </c>
+      <c r="D107" s="27">
+        <v>2</v>
+      </c>
+      <c r="E107" s="17">
+        <v>3</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="108" spans="3:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="L108">
+        <v>2</v>
+      </c>
+      <c r="M108" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="110" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>53</v>
+      </c>
+      <c r="E110" s="18"/>
+      <c r="G110" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C111" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F111" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="G111" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="112" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C112" s="23">
+        <v>1</v>
+      </c>
+      <c r="D112" s="11">
+        <v>1</v>
+      </c>
+      <c r="F112" s="20">
+        <v>1</v>
+      </c>
+      <c r="G112" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C113" s="23">
+        <v>2</v>
+      </c>
+      <c r="D113" s="11">
+        <v>0</v>
+      </c>
+      <c r="F113" s="20">
+        <v>2</v>
+      </c>
+      <c r="G113" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="3:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C114" s="23">
+        <v>3</v>
+      </c>
+      <c r="D114" s="11">
+        <v>2</v>
+      </c>
+      <c r="F114" s="21">
+        <v>3</v>
+      </c>
+      <c r="G114" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="3:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C115" s="24">
+        <v>4</v>
+      </c>
+      <c r="D115" s="12">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="19">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -3574,6 +5034,7 @@
     <tablePart r:id="rId17"/>
     <tablePart r:id="rId18"/>
     <tablePart r:id="rId19"/>
+    <tablePart r:id="rId20"/>
   </tableParts>
 </worksheet>
 </file>
--- a/requirements/rm_diagram/db_rm_testdaten.xlsx
+++ b/requirements/rm_diagram/db_rm_testdaten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philippreisinger/Documents/Hochschule/S02/FOGL/fh-sem2-db-project/requirements/rm_diagram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FA48ED-F2F7-B041-A946-736B78A5CEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581A4E5D-C05B-2249-9516-DF62FC5F8544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="50040" windowHeight="28200" xr2:uid="{F1193D4A-DC4B-D649-9F00-C53722C965C8}"/>
   </bookViews>
@@ -451,52 +451,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="67">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -527,115 +487,6 @@
       <top/>
       <bottom style="medium">
         <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="5" tint="-0.249977111117893"/>
-      </left>
-      <right style="medium">
-        <color theme="5" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
-        <color theme="5" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="5" tint="-0.249977111117893"/>
-      </left>
-      <right style="medium">
-        <color theme="5" tint="-0.249977111117893"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="5" tint="-0.249977111117893"/>
-      </left>
-      <right style="medium">
-        <color theme="5" tint="-0.249977111117893"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color theme="5" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="5"/>
-      </left>
-      <right style="medium">
-        <color theme="5"/>
-      </right>
-      <top style="medium">
-        <color theme="5"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="5"/>
-      </left>
-      <right style="medium">
-        <color theme="5"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="5"/>
-      </left>
-      <right style="medium">
-        <color theme="5"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color theme="5"/>
       </bottom>
       <diagonal/>
     </border>
@@ -694,19 +545,6 @@
       <bottom style="medium">
         <color theme="3" tint="0.249977111117893"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="9" tint="-0.249977111117893"/>
-      </left>
-      <right style="thick">
-        <color theme="9" tint="-0.249977111117893"/>
-      </right>
-      <top style="thick">
-        <color theme="9" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -785,56 +623,801 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFF00"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFFFF00"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFFFF00"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFF00"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFFFF00"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </right>
+      <top style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFF00"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFFFF00"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5"/>
+      </left>
+      <right style="thick">
+        <color theme="5"/>
+      </right>
+      <top style="thick">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5"/>
+      </left>
+      <right style="thick">
+        <color theme="5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5"/>
+      </left>
+      <right style="thick">
+        <color theme="5"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right style="thick">
+        <color theme="5"/>
+      </right>
+      <top style="medium">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right style="thick">
+        <color theme="5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right style="thick">
+        <color theme="5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFF00"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FFFFFF00"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFF00"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </left>
+      <right style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </right>
+      <top style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </left>
+      <right style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </left>
+      <right style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="8" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="5" tint="0.59999389629810485"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8"/>
+      </left>
+      <right style="thick">
+        <color theme="8"/>
+      </right>
+      <top style="thick">
+        <color theme="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8"/>
+      </left>
+      <right style="thick">
+        <color theme="8"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8"/>
+      </left>
+      <right style="thick">
+        <color theme="8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8"/>
+      </left>
+      <right style="thick">
+        <color theme="8"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="8"/>
+      </left>
+      <right style="thick">
+        <color theme="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </left>
+      <right style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </right>
+      <top style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </left>
+      <right style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </left>
+      <right style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </right>
+      <top style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="9" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </right>
+      <top style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="6" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.39997558519241921"/>
+      </left>
+      <right style="thick">
+        <color theme="5" tint="0.39997558519241921"/>
+      </right>
+      <top style="thick">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.39997558519241921"/>
+      </left>
+      <right style="thick">
+        <color theme="5" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.39997558519241921"/>
+      </left>
+      <right style="thick">
+        <color theme="5" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFF00"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="41">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FF00B0F0"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF00B0F0"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="5" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="5" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFFFF00"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFFFF00"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFFFF00"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFFFF00"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -873,13 +1456,383 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="00000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFFFF00"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFFFF00"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thick">
           <color theme="8" tint="0.39997558519241921"/>
         </left>
         <right style="thick">
           <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="29" formatCode="mm:ss.0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFFFF00"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFFFF00"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FF00B0F0"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF00B0F0"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </left>
+        <right style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="6" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="6" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="medium">
+          <color theme="4"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </left>
+        <right style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5" tint="0.59999389629810485"/>
+        </left>
+        <right style="thick">
+          <color theme="5" tint="0.59999389629810485"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="6" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="6" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FF00B0F0"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF00B0F0"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yy"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFF0000"/>
         </right>
         <top/>
         <bottom/>
@@ -921,21 +1874,10 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
+          <color theme="8"/>
         </left>
         <right style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
-        </left>
-        <right style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
+          <color theme="8"/>
         </right>
         <top/>
         <bottom/>
@@ -944,79 +1886,13 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="00000"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="3" tint="0.249977111117893"/>
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
         </left>
-        <right style="medium">
-          <color theme="4"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="5"/>
-        </left>
-        <right style="medium">
-          <color theme="5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="5" tint="-0.249977111117893"/>
-        </left>
-        <right style="medium">
-          <color theme="5" tint="-0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="3" tint="0.249977111117893"/>
-        </left>
-        <right style="medium">
-          <color theme="3" tint="0.249977111117893"/>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
         </right>
         <top/>
         <bottom/>
@@ -1032,116 +1908,26 @@
         <right style="thin">
           <color theme="1"/>
         </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="29" formatCode="mm:ss.0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="00000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yy"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
         <top style="thin">
           <color theme="1"/>
         </top>
         <bottom style="thin">
           <color theme="1"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8"/>
+        </left>
+        <right style="thick">
+          <color theme="8"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
   </dxfs>
@@ -2059,6 +2845,1085 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1127902</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>35524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1127902</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>26644</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29CB3010-3550-887B-642B-BD8967DDECB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12264825" y="10479720"/>
+          <a:ext cx="0" cy="852588"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>452942</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>35524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>452942</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Straight Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73150A85-BC87-A7AF-60AD-E2BFC0A998D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7362452" y="20328881"/>
+          <a:ext cx="0" cy="595035"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>985804</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>35524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>985804</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>186503</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Straight Connector 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36A15257-C605-9E2F-01D3-A8C9D4B71CCD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8206154" y="21021608"/>
+          <a:ext cx="0" cy="568392"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>408532</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>44406</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>408532</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>106574</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A7EDFED-8768-8FAF-6901-A255BFB05F1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1234476" y="19840420"/>
+          <a:ext cx="0" cy="293077"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>408531</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>115455</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>737133</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>115455</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8DA21AC-487D-6BEA-C736-B90D386B2E7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1234475" y="20142378"/>
+          <a:ext cx="20000280" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>746014</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>115455</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>746014</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>204265</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Straight Connector 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22859EFC-BDF1-443C-93C3-47CFD5046D43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21243636" y="20142378"/>
+          <a:ext cx="0" cy="506223"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>639440</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>204266</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>639440</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>35525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="Straight Connector 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{045D93B8-253D-D32E-B97F-DAB7B107949D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11163566" y="18579301"/>
+          <a:ext cx="0" cy="1287762"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>639441</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>26644</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>683847</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>26644</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="Straight Connector 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF89BCF2-1786-C33E-10A0-C8A6CBEB85A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11163567" y="19858182"/>
+          <a:ext cx="8366014" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>683846</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>8882</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>683846</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>195385</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="Straight Connector 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09512E50-9E25-0B89-6444-6CDD243954EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19529580" y="19840420"/>
+          <a:ext cx="0" cy="834825"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>888112</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>8881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>888112</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>195385</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="Straight Connector 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5183D49-E5D7-9757-6C67-82DF139DEEF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16181399" y="18597063"/>
+          <a:ext cx="0" cy="603916"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>719370</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>44405</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>719370</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>26644</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="Straight Connector 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{087CDFD9-5718-1836-BFE3-7E41677C2D4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16012657" y="17202727"/>
+          <a:ext cx="0" cy="399651"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>692727</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>26644</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>692727</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>8881</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="Straight Connector 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{040F86FA-CEF6-5373-97F1-15576A8EA913}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="17433636" y="17602378"/>
+          <a:ext cx="0" cy="399650"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>719370</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>35525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>692727</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>35525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="39" name="Straight Connector 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED09C95A-FCBC-FB1F-7834-2DC22F308EE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16012657" y="17611259"/>
+          <a:ext cx="1420979" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>301958</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>17763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>301958</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>204266</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F8880E3-6D06-DB7F-98D5-9B5C01DE9A39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="18401678" y="15950490"/>
+          <a:ext cx="0" cy="2122587"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>754895</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>754895</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Connector 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E9D0497-9A2C-2C72-ADBA-42FBBFAAED08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="19600629" y="17451399"/>
+          <a:ext cx="0" cy="630559"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>879231</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>8881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>888112</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>8881</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FC78277-10D2-33E0-A40F-190A7297F659}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11403357" y="16199161"/>
+          <a:ext cx="8881" cy="1953846"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>772658</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>772658</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>44406</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Straight Connector 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69E3D864-F8A8-7123-E346-D0F989762FD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12602308" y="16190280"/>
+          <a:ext cx="0" cy="719371"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>674965</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>62168</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>674965</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>204266</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Straight Connector 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED93F5E6-9C0E-C85A-6D01-27A3BC538F58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="8588042" y="20568671"/>
+          <a:ext cx="0" cy="346364"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>657203</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>62168</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>683846</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>62168</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="Straight Connector 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F65877BB-A829-4113-9D5A-EFA31E55B68E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8570280" y="20568671"/>
+          <a:ext cx="1358811" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>692727</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>17762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>692727</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>71049</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="Straight Connector 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{194A036E-C1D6-DD08-DC3A-787EFF3AF6F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9937972" y="16883007"/>
+          <a:ext cx="0" cy="3694545"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>701608</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>17762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>772658</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>17762</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="Straight Connector 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BED36490-D0A4-6ECE-B24D-AB915DAD31DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9946853" y="16883007"/>
+          <a:ext cx="2655455" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2066,7 +3931,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}" name="Table1" displayName="Table1" ref="E5:F6" totalsRowShown="0">
   <autoFilter ref="E5:F6" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4CA8222C-E02B-3947-87F8-83F881B4CD46}" name="id" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{4CA8222C-E02B-3947-87F8-83F881B4CD46}" name="id" dataDxfId="40"/>
     <tableColumn id="2" xr3:uid="{E0E55DC1-F22B-7F48-A870-6CF35C2E7C76}" name="author_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2074,10 +3939,10 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}" name="Table11" displayName="Table11" ref="O47:P48" totalsRowShown="0">
-  <autoFilter ref="O47:P48" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}" name="Table11" displayName="Table11" ref="M94:N95" totalsRowShown="0">
+  <autoFilter ref="M94:N95" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6EC00463-AD68-3A4E-88D2-79816B3C1B9D}" name="id"/>
+    <tableColumn id="1" xr3:uid="{6EC00463-AD68-3A4E-88D2-79816B3C1B9D}" name="id" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{E086A4A2-2C9C-A84B-9AC0-52176BF11D98}" name="country_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2085,16 +3950,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}" name="Table12" displayName="Table12" ref="M76:T78" totalsRowShown="0">
-  <autoFilter ref="M76:T78" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}" name="Table12" displayName="Table12" ref="J88:Q90" totalsRowShown="0">
+  <autoFilter ref="J88:Q90" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E73135F5-C2F6-4D4B-884D-4470E95AC0A9}" name="id"/>
+    <tableColumn id="1" xr3:uid="{E73135F5-C2F6-4D4B-884D-4470E95AC0A9}" name="id" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{89AD4D6A-6E80-F84D-BC1C-F0BC9AB56A2A}" name="first_name"/>
     <tableColumn id="3" xr3:uid="{D5B6CC10-DD47-CF4F-97FC-CF3CB26AC93D}" name="last_name"/>
-    <tableColumn id="4" xr3:uid="{228DB8C2-005E-F44A-9144-29D84EA1CDCD}" name="country_id"/>
-    <tableColumn id="5" xr3:uid="{F311F8A6-D073-364D-AB8C-3D81F088519F}" name="zip_id"/>
-    <tableColumn id="6" xr3:uid="{B085B83B-E563-5747-92AE-F02F325D2365}" name="town_id"/>
-    <tableColumn id="7" xr3:uid="{469FF72E-F569-5149-AAA6-FAE3DFD7884E}" name="street_id"/>
+    <tableColumn id="4" xr3:uid="{228DB8C2-005E-F44A-9144-29D84EA1CDCD}" name="country_id" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{F311F8A6-D073-364D-AB8C-3D81F088519F}" name="zip_id" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{B085B83B-E563-5747-92AE-F02F325D2365}" name="town_id" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{469FF72E-F569-5149-AAA6-FAE3DFD7884E}" name="street_id" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{E9A49622-D15A-F048-A7F1-ED4F84228EE8}" name="streetnumber"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2105,9 +3970,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}" name="Table13" displayName="Table13" ref="G101:J102" totalsRowShown="0">
   <autoFilter ref="G101:J102" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{47A5031E-499A-004E-B300-55435FDF6C2C}" name="id" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{9FADB436-039C-5246-BE80-643E467F92EE}" name="event_type_id"/>
-    <tableColumn id="3" xr3:uid="{5C025943-87BA-0A4A-9FBA-C1B0DF57EB85}" name="event_start_at_dt" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{47A5031E-499A-004E-B300-55435FDF6C2C}" name="id" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{9FADB436-039C-5246-BE80-643E467F92EE}" name="event_type_id" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{5C025943-87BA-0A4A-9FBA-C1B0DF57EB85}" name="event_start_at_dt" dataDxfId="13"/>
     <tableColumn id="4" xr3:uid="{5457FAB7-6DE8-8A44-884C-825D5762F6B4}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2115,10 +3980,10 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}" name="Table14" displayName="Table14" ref="L106:M109" totalsRowShown="0">
-  <autoFilter ref="L106:M109" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}" name="Table14" displayName="Table14" ref="H106:I108" totalsRowShown="0">
+  <autoFilter ref="H106:I108" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C4630465-2BEF-F04C-9706-9ECAD5A63900}" name="id"/>
+    <tableColumn id="1" xr3:uid="{C4630465-2BEF-F04C-9706-9ECAD5A63900}" name="id" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{3DED103F-D0D6-FB4A-BF71-8281276D9E61}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2129,7 +3994,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}" name="Table15" displayName="Table15" ref="K56:L61" totalsRowShown="0">
   <autoFilter ref="K56:L61" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7F823BF2-5D4F-5646-A492-44D3E4F6B911}" name="id"/>
+    <tableColumn id="1" xr3:uid="{7F823BF2-5D4F-5646-A492-44D3E4F6B911}" name="id" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{DF0F7948-576E-8649-8C5A-04EB28891E87}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2137,10 +4002,10 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}" name="Table16" displayName="Table16" ref="J77:K80" totalsRowShown="0">
-  <autoFilter ref="J77:K80" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}" name="Table16" displayName="Table16" ref="P81:Q84" totalsRowShown="0">
+  <autoFilter ref="P81:Q84" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{61F45889-5DB7-B84F-B548-EC91EF25CFE0}" name="id"/>
+    <tableColumn id="1" xr3:uid="{61F45889-5DB7-B84F-B548-EC91EF25CFE0}" name="id" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{26F1151E-3796-634A-A382-F1364220BD49}" name="street"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2148,10 +4013,10 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}" name="Table17" displayName="Table17" ref="J83:K86" totalsRowShown="0">
-  <autoFilter ref="J83:K86" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}" name="Table17" displayName="Table17" ref="O74:P77" totalsRowShown="0">
+  <autoFilter ref="O74:P77" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{98617ACD-5B89-6942-9465-1BB31F03AED3}" name="id"/>
+    <tableColumn id="1" xr3:uid="{98617ACD-5B89-6942-9465-1BB31F03AED3}" name="id" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{AEE42774-BADF-C948-B5B5-784A9108FA3C}" name="town_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2159,10 +4024,10 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}" name="Table18" displayName="Table18" ref="M63:N66" totalsRowShown="0">
-  <autoFilter ref="M63:N66" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}" name="Table18" displayName="Table18" ref="M80:N83" totalsRowShown="0">
+  <autoFilter ref="M80:N83" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{07F9A468-865E-0A43-9EE2-245F124FBEFF}" name="id"/>
+    <tableColumn id="1" xr3:uid="{07F9A468-865E-0A43-9EE2-245F124FBEFF}" name="id" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{A7D14D91-1CDA-FB45-A260-0E20E6DC29BE}" name="zip_code"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2170,33 +4035,33 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}" name="Table19" displayName="Table19" ref="G56:H97" totalsRowShown="0" headerRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}" name="Table19" displayName="Table19" ref="G56:H97" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="G56:H97" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8E911F00-E0AD-E241-B46F-392E2B46174D}" name="event_id"/>
-    <tableColumn id="2" xr3:uid="{0B1666A1-D5FB-6648-AEFB-95B5325AE797}" name="book_isbn" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8E911F00-E0AD-E241-B46F-392E2B46174D}" name="event_id" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{0B1666A1-D5FB-6648-AEFB-95B5325AE797}" name="book_isbn" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}" name="Table20" displayName="Table20" ref="P64:Q65" totalsRowShown="0" headerRowDxfId="13">
-  <autoFilter ref="P64:Q65" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}" name="Table20" displayName="Table20" ref="J77:K78" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="J77:K78" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DE2D07D2-ADAE-264C-8DCD-F0CBE007E888}" name="customer_id"/>
-    <tableColumn id="2" xr3:uid="{A21AA7ED-F1FA-D540-B965-8F8EEC8690D4}" name="event_id"/>
+    <tableColumn id="1" xr3:uid="{DE2D07D2-ADAE-264C-8DCD-F0CBE007E888}" name="customer_id" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{A21AA7ED-F1FA-D540-B965-8F8EEC8690D4}" name="event_id" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}" name="Table2" displayName="Table2" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}" name="Table2" displayName="Table2" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="39">
   <autoFilter ref="D10:E51" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1B46E4BC-5557-7848-A9B7-5BB850BF8539}" name="book_isbn" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{A9C101D5-0497-2F45-A36B-EA046D7840FD}" name="author_id" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{1B46E4BC-5557-7848-A9B7-5BB850BF8539}" name="book_isbn" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{A9C101D5-0497-2F45-A36B-EA046D7840FD}" name="author_id" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2206,9 +4071,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}" name="Table3" displayName="Table3" ref="I10:M51" totalsRowShown="0">
   <autoFilter ref="I10:M51" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{38CAD5D1-EBB5-C247-B45E-AEE98024CD77}" name="isbn" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{38CAD5D1-EBB5-C247-B45E-AEE98024CD77}" name="isbn" dataDxfId="36"/>
     <tableColumn id="2" xr3:uid="{60F11968-00C8-6F4A-9CC4-55D26BA9ED3D}" name="book_genre_id"/>
-    <tableColumn id="3" xr3:uid="{9E8F79E7-43C5-AF41-B8EF-1A9332BF14EA}" name="publisher_id"/>
+    <tableColumn id="3" xr3:uid="{9E8F79E7-43C5-AF41-B8EF-1A9332BF14EA}" name="publisher_id" dataDxfId="35"/>
     <tableColumn id="4" xr3:uid="{1053F528-7EBD-174A-871B-D0618032220F}" name="title"/>
     <tableColumn id="5" xr3:uid="{864CACD1-75A9-024C-BE64-135C41FF4E7C}" name="year"/>
   </tableColumns>
@@ -2217,15 +4082,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}" name="Table4" displayName="Table4" ref="O11:T13" totalsRowShown="0">
-  <autoFilter ref="O11:T13" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}" name="Table4" displayName="Table4" ref="L101:Q103" totalsRowShown="0">
+  <autoFilter ref="L101:Q103" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CE43687C-859D-1F40-BDA4-99499EB16E72}" name="id"/>
-    <tableColumn id="2" xr3:uid="{6970F839-29D6-AF48-9ED9-F80AEA8EBDB8}" name="loan_starts_at_date" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{2A5A1D14-65E8-8741-9C1C-5D6CEC0EAC51}" name="loan_ends_at_date" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{6970F839-29D6-AF48-9ED9-F80AEA8EBDB8}" name="loan_starts_at_date" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{2A5A1D14-65E8-8741-9C1C-5D6CEC0EAC51}" name="loan_ends_at_date" dataDxfId="33"/>
     <tableColumn id="4" xr3:uid="{97CCF238-494E-9D41-8539-ABC80CEB0F33}" name="book_returned_at_date"/>
-    <tableColumn id="5" xr3:uid="{DAFFE0E3-462C-F744-A240-14A8F0635450}" name="customerid"/>
-    <tableColumn id="6" xr3:uid="{EB8E3328-793F-564A-877C-326817474CA3}" name="fk_stockid"/>
+    <tableColumn id="5" xr3:uid="{DAFFE0E3-462C-F744-A240-14A8F0635450}" name="customerid" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{EB8E3328-793F-564A-877C-326817474CA3}" name="fk_stockid" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2235,7 +4100,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}" name="Table6" displayName="Table6" ref="J2:K8" totalsRowShown="0">
   <autoFilter ref="J2:K8" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{38EBFB47-42CE-4249-A9CD-4AEC31A85951}" name="id"/>
+    <tableColumn id="1" xr3:uid="{38EBFB47-42CE-4249-A9CD-4AEC31A85951}" name="id" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{D7B8AC5E-2E4C-E944-A81B-AAECE5723F44}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2246,9 +4111,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}" name="Table7" displayName="Table7" ref="C101:E107" totalsRowShown="0">
   <autoFilter ref="C101:E107" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C98E57F8-CF5A-B04C-9AE6-4326E12BF111}" name="id" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{2B878DF3-03FC-7E45-8203-B9092C488BC3}" name="book_location_floor_id" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{7E6E67C0-8A4A-4348-B9CE-17C91B56993F}" name="book_location_shelf_id" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{C98E57F8-CF5A-B04C-9AE6-4326E12BF111}" name="id" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{2B878DF3-03FC-7E45-8203-B9092C488BC3}" name="book_location_floor_id" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{7E6E67C0-8A4A-4348-B9CE-17C91B56993F}" name="book_location_shelf_id" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2258,8 +4123,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}" name="Table8" displayName="Table8" ref="C111:D115" totalsRowShown="0">
   <autoFilter ref="C111:D115" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{ED3B7FB1-4AD6-3148-A8C5-AD0D54AB86D5}" name="id" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{5CFA8D92-95F5-D848-ACFF-964046FA5E4A}" name="number" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{ED3B7FB1-4AD6-3148-A8C5-AD0D54AB86D5}" name="id" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{5CFA8D92-95F5-D848-ACFF-964046FA5E4A}" name="number" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2269,8 +4134,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}" name="Table9" displayName="Table9" ref="F111:G114" totalsRowShown="0">
   <autoFilter ref="F111:G114" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{34593F39-F4A6-074E-A6EC-EC7E7E8422BE}" name="id" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{E3B4CF1C-A9B2-1C4A-A8F1-45940E10B2C5}" name="number" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{34593F39-F4A6-074E-A6EC-EC7E7E8422BE}" name="id" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{E3B4CF1C-A9B2-1C4A-A8F1-45940E10B2C5}" name="number" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2280,10 +4145,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}" name="Table10" displayName="Table10" ref="B55:E96" totalsRowShown="0">
   <autoFilter ref="B55:E96" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0E733531-21AD-F946-9111-F766797F96D0}" name="id"/>
-    <tableColumn id="2" xr3:uid="{85903ED5-BC1F-D147-A8EA-8491727CFFC9}" name="book_location_id" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{0E733531-21AD-F946-9111-F766797F96D0}" name="id" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{85903ED5-BC1F-D147-A8EA-8491727CFFC9}" name="book_location_id" dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{0A1011E6-FFDE-254C-9381-CF62A47EE8F3}" name="is_in_stock"/>
-    <tableColumn id="4" xr3:uid="{260DA1AD-9E16-104E-A144-7275FF29087D}" name="book_isbn" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{260DA1AD-9E16-104E-A144-7275FF29087D}" name="book_isbn" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2606,10 +4471,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5DA9CCF-71D1-7F40-ABE4-A9F4E589BDAC}">
-  <dimension ref="B1:T115"/>
+  <dimension ref="B1:Q115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="8.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="21.33203125" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
@@ -2629,83 +4494,83 @@
     <col min="20" max="20" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="J1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="J2" s="6" t="s">
+    <row r="2" spans="3:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="J2" s="37" t="s">
         <v>1</v>
       </c>
       <c r="K2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="J3">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="J3" s="38">
         <v>1</v>
       </c>
       <c r="K3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="4:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E4" t="s">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="38">
         <v>2</v>
       </c>
       <c r="K4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="E5" s="14" t="s">
+    <row r="5" spans="3:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="50" t="s">
         <v>1</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="38">
         <v>3</v>
       </c>
       <c r="K5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="E6" s="13">
+    <row r="6" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="51">
         <v>1</v>
       </c>
       <c r="F6" t="s">
         <v>3</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="38">
         <v>4</v>
       </c>
       <c r="K6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="J7">
+    <row r="7" spans="3:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="J7" s="38">
         <v>5</v>
       </c>
       <c r="K7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="J8">
+    <row r="8" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="39">
         <v>6</v>
       </c>
       <c r="K8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="4:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
         <v>4</v>
       </c>
@@ -2713,20 +4578,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="4:20" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="36" t="s">
+    <row r="10" spans="3:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="45" t="s">
         <v>10</v>
       </c>
       <c r="L10" t="s">
@@ -2735,24 +4600,22 @@
       <c r="M10" t="s">
         <v>12</v>
       </c>
-      <c r="O10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="D11" s="33">
+    </row>
+    <row r="11" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C11" s="27"/>
+      <c r="D11" s="40">
         <v>9780385086952</v>
       </c>
-      <c r="E11" s="35">
-        <v>1</v>
-      </c>
-      <c r="I11" s="33">
+      <c r="E11" s="54">
+        <v>1</v>
+      </c>
+      <c r="I11" s="40">
         <v>9780385086952</v>
       </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11">
+      <c r="J11" s="44">
+        <v>1</v>
+      </c>
+      <c r="K11" s="46">
         <v>1</v>
       </c>
       <c r="L11" t="s">
@@ -2761,39 +4624,22 @@
       <c r="M11">
         <v>1974</v>
       </c>
-      <c r="O11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="P11" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>16</v>
-      </c>
-      <c r="R11" t="s">
-        <v>17</v>
-      </c>
-      <c r="S11" t="s">
-        <v>18</v>
-      </c>
-      <c r="T11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="D12" s="33">
+    </row>
+    <row r="12" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C12" s="27"/>
+      <c r="D12" s="40">
         <v>9780307743657</v>
       </c>
-      <c r="E12" s="7">
-        <v>1</v>
-      </c>
-      <c r="I12" s="33">
+      <c r="E12" s="55">
+        <v>1</v>
+      </c>
+      <c r="I12" s="40">
         <v>9780307743657</v>
       </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
+      <c r="J12" s="44">
+        <v>1</v>
+      </c>
+      <c r="K12" s="46">
         <v>2</v>
       </c>
       <c r="L12" t="s">
@@ -2802,36 +4648,22 @@
       <c r="M12">
         <v>1975</v>
       </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12" s="1">
-        <v>46082</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>46090</v>
-      </c>
-      <c r="S12">
-        <v>1</v>
-      </c>
-      <c r="T12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="D13" s="33">
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C13" s="27"/>
+      <c r="D13" s="40">
         <v>9780307743664</v>
       </c>
-      <c r="E13" s="8">
-        <v>1</v>
-      </c>
-      <c r="I13" s="33">
+      <c r="E13" s="54">
+        <v>1</v>
+      </c>
+      <c r="I13" s="40">
         <v>9780307743664</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
+      <c r="J13" s="44">
+        <v>1</v>
+      </c>
+      <c r="K13" s="46">
         <v>2</v>
       </c>
       <c r="L13" t="s">
@@ -2840,36 +4672,22 @@
       <c r="M13">
         <v>1977</v>
       </c>
-      <c r="O13">
-        <v>2</v>
-      </c>
-      <c r="P13" s="1">
-        <v>46082</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>46090</v>
-      </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-      <c r="T13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="D14" s="33">
+    </row>
+    <row r="14" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C14" s="27"/>
+      <c r="D14" s="40">
         <v>9780670813025</v>
       </c>
-      <c r="E14" s="8">
-        <v>1</v>
-      </c>
-      <c r="I14" s="33">
+      <c r="E14" s="54">
+        <v>1</v>
+      </c>
+      <c r="I14" s="40">
         <v>9780670813025</v>
       </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
+      <c r="J14" s="44">
+        <v>1</v>
+      </c>
+      <c r="K14" s="46">
         <v>5</v>
       </c>
       <c r="L14" t="s">
@@ -2879,20 +4697,21 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="15" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="D15" s="33">
+    <row r="15" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C15" s="27"/>
+      <c r="D15" s="40">
         <v>9780345418864</v>
       </c>
-      <c r="E15" s="8">
-        <v>1</v>
-      </c>
-      <c r="I15" s="33">
+      <c r="E15" s="54">
+        <v>1</v>
+      </c>
+      <c r="I15" s="40">
         <v>9780345418864</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
+      <c r="J15" s="44">
+        <v>1</v>
+      </c>
+      <c r="K15" s="46">
         <v>2</v>
       </c>
       <c r="L15" t="s">
@@ -2902,20 +4721,21 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="16" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="D16" s="33">
+    <row r="16" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C16" s="27"/>
+      <c r="D16" s="40">
         <v>9780670813032</v>
       </c>
-      <c r="E16" s="8">
-        <v>1</v>
-      </c>
-      <c r="I16" s="33">
+      <c r="E16" s="54">
+        <v>1</v>
+      </c>
+      <c r="I16" s="40">
         <v>9780670813032</v>
       </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
+      <c r="J16" s="44">
+        <v>1</v>
+      </c>
+      <c r="K16" s="46">
         <v>2</v>
       </c>
       <c r="L16" t="s">
@@ -2925,20 +4745,21 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D17" s="33">
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C17" s="27"/>
+      <c r="D17" s="40">
         <v>9780670813049</v>
       </c>
-      <c r="E17" s="8">
-        <v>1</v>
-      </c>
-      <c r="I17" s="33">
+      <c r="E17" s="54">
+        <v>1</v>
+      </c>
+      <c r="I17" s="40">
         <v>9780670813049</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="46">
         <v>2</v>
       </c>
       <c r="L17" t="s">
@@ -2948,20 +4769,21 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="18" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D18" s="33">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C18" s="27"/>
+      <c r="D18" s="40">
         <v>9780670813056</v>
       </c>
-      <c r="E18" s="8">
-        <v>1</v>
-      </c>
-      <c r="I18" s="33">
+      <c r="E18" s="54">
+        <v>1</v>
+      </c>
+      <c r="I18" s="40">
         <v>9780670813056</v>
       </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
+      <c r="J18" s="44">
+        <v>1</v>
+      </c>
+      <c r="K18" s="46">
         <v>2</v>
       </c>
       <c r="L18" t="s">
@@ -2971,20 +4793,21 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="19" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D19" s="33">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C19" s="27"/>
+      <c r="D19" s="40">
         <v>9780670813063</v>
       </c>
-      <c r="E19" s="8">
-        <v>1</v>
-      </c>
-      <c r="I19" s="33">
+      <c r="E19" s="54">
+        <v>1</v>
+      </c>
+      <c r="I19" s="40">
         <v>9780670813063</v>
       </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
+      <c r="J19" s="44">
+        <v>1</v>
+      </c>
+      <c r="K19" s="46">
         <v>2</v>
       </c>
       <c r="L19" t="s">
@@ -2994,20 +4817,21 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D20" s="33">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C20" s="27"/>
+      <c r="D20" s="40">
         <v>9780670813070</v>
       </c>
-      <c r="E20" s="8">
-        <v>1</v>
-      </c>
-      <c r="I20" s="33">
+      <c r="E20" s="54">
+        <v>1</v>
+      </c>
+      <c r="I20" s="40">
         <v>9780670813070</v>
       </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
+      <c r="J20" s="44">
+        <v>1</v>
+      </c>
+      <c r="K20" s="46">
         <v>2</v>
       </c>
       <c r="L20" t="s">
@@ -3017,20 +4841,21 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D21" s="33">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C21" s="27"/>
+      <c r="D21" s="40">
         <v>9780670813087</v>
       </c>
-      <c r="E21" s="8">
-        <v>1</v>
-      </c>
-      <c r="I21" s="33">
+      <c r="E21" s="54">
+        <v>1</v>
+      </c>
+      <c r="I21" s="40">
         <v>9780670813087</v>
       </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
+      <c r="J21" s="44">
+        <v>1</v>
+      </c>
+      <c r="K21" s="46">
         <v>3</v>
       </c>
       <c r="L21" t="s">
@@ -3040,20 +4865,21 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D22" s="33">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C22" s="27"/>
+      <c r="D22" s="40">
         <v>9780670813094</v>
       </c>
-      <c r="E22" s="8">
-        <v>1</v>
-      </c>
-      <c r="I22" s="33">
+      <c r="E22" s="54">
+        <v>1</v>
+      </c>
+      <c r="I22" s="40">
         <v>9780670813094</v>
       </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
+      <c r="J22" s="44">
+        <v>1</v>
+      </c>
+      <c r="K22" s="46">
         <v>2</v>
       </c>
       <c r="L22" t="s">
@@ -3063,20 +4889,21 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D23" s="33">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C23" s="27"/>
+      <c r="D23" s="40">
         <v>9780670813100</v>
       </c>
-      <c r="E23" s="8">
-        <v>1</v>
-      </c>
-      <c r="I23" s="33">
+      <c r="E23" s="54">
+        <v>1</v>
+      </c>
+      <c r="I23" s="40">
         <v>9780670813100</v>
       </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
+      <c r="J23" s="44">
+        <v>1</v>
+      </c>
+      <c r="K23" s="46">
         <v>2</v>
       </c>
       <c r="L23" t="s">
@@ -3086,20 +4913,21 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="24" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D24" s="33">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C24" s="27"/>
+      <c r="D24" s="40">
         <v>9780670813117</v>
       </c>
-      <c r="E24" s="8">
-        <v>1</v>
-      </c>
-      <c r="I24" s="33">
+      <c r="E24" s="54">
+        <v>1</v>
+      </c>
+      <c r="I24" s="40">
         <v>9780670813117</v>
       </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
+      <c r="J24" s="44">
+        <v>1</v>
+      </c>
+      <c r="K24" s="46">
         <v>2</v>
       </c>
       <c r="L24" t="s">
@@ -3109,20 +4937,21 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="25" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D25" s="33">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C25" s="27"/>
+      <c r="D25" s="40">
         <v>9780670813124</v>
       </c>
-      <c r="E25" s="8">
-        <v>1</v>
-      </c>
-      <c r="I25" s="33">
+      <c r="E25" s="54">
+        <v>1</v>
+      </c>
+      <c r="I25" s="40">
         <v>9780670813124</v>
       </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25">
+      <c r="J25" s="44">
+        <v>1</v>
+      </c>
+      <c r="K25" s="46">
         <v>2</v>
       </c>
       <c r="L25" t="s">
@@ -3132,20 +4961,21 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="26" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D26" s="33">
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C26" s="27"/>
+      <c r="D26" s="40">
         <v>9780670813131</v>
       </c>
-      <c r="E26" s="8">
-        <v>1</v>
-      </c>
-      <c r="I26" s="33">
+      <c r="E26" s="54">
+        <v>1</v>
+      </c>
+      <c r="I26" s="40">
         <v>9780670813131</v>
       </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26">
+      <c r="J26" s="44">
+        <v>1</v>
+      </c>
+      <c r="K26" s="46">
         <v>3</v>
       </c>
       <c r="L26" t="s">
@@ -3155,20 +4985,21 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="27" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D27" s="33">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C27" s="27"/>
+      <c r="D27" s="40">
         <v>9780670813148</v>
       </c>
-      <c r="E27" s="8">
-        <v>1</v>
-      </c>
-      <c r="I27" s="33">
+      <c r="E27" s="54">
+        <v>1</v>
+      </c>
+      <c r="I27" s="40">
         <v>9780670813148</v>
       </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
+      <c r="J27" s="44">
+        <v>1</v>
+      </c>
+      <c r="K27" s="46">
         <v>2</v>
       </c>
       <c r="L27" t="s">
@@ -3178,20 +5009,21 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="28" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D28" s="33">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C28" s="27"/>
+      <c r="D28" s="40">
         <v>9780670813155</v>
       </c>
-      <c r="E28" s="8">
-        <v>1</v>
-      </c>
-      <c r="I28" s="33">
+      <c r="E28" s="54">
+        <v>1</v>
+      </c>
+      <c r="I28" s="40">
         <v>9780670813155</v>
       </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28">
+      <c r="J28" s="44">
+        <v>1</v>
+      </c>
+      <c r="K28" s="46">
         <v>2</v>
       </c>
       <c r="L28" t="s">
@@ -3201,20 +5033,21 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="29" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D29" s="33">
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C29" s="27"/>
+      <c r="D29" s="40">
         <v>9780670813162</v>
       </c>
-      <c r="E29" s="8">
-        <v>1</v>
-      </c>
-      <c r="I29" s="33">
+      <c r="E29" s="54">
+        <v>1</v>
+      </c>
+      <c r="I29" s="40">
         <v>9780670813162</v>
       </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29">
+      <c r="J29" s="44">
+        <v>1</v>
+      </c>
+      <c r="K29" s="46">
         <v>2</v>
       </c>
       <c r="L29" t="s">
@@ -3224,20 +5057,21 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="30" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D30" s="33">
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C30" s="27"/>
+      <c r="D30" s="40">
         <v>9780670813179</v>
       </c>
-      <c r="E30" s="8">
-        <v>1</v>
-      </c>
-      <c r="I30" s="33">
+      <c r="E30" s="54">
+        <v>1</v>
+      </c>
+      <c r="I30" s="40">
         <v>9780670813179</v>
       </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
+      <c r="J30" s="44">
+        <v>1</v>
+      </c>
+      <c r="K30" s="46">
         <v>2</v>
       </c>
       <c r="L30" t="s">
@@ -3247,20 +5081,21 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="31" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D31" s="33">
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C31" s="27"/>
+      <c r="D31" s="40">
         <v>9780670813186</v>
       </c>
-      <c r="E31" s="8">
-        <v>1</v>
-      </c>
-      <c r="I31" s="33">
+      <c r="E31" s="54">
+        <v>1</v>
+      </c>
+      <c r="I31" s="40">
         <v>9780670813186</v>
       </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
+      <c r="J31" s="44">
+        <v>1</v>
+      </c>
+      <c r="K31" s="46">
         <v>1</v>
       </c>
       <c r="L31" t="s">
@@ -3270,20 +5105,21 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="32" spans="4:13" x14ac:dyDescent="0.2">
-      <c r="D32" s="33">
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C32" s="27"/>
+      <c r="D32" s="40">
         <v>9780670813193</v>
       </c>
-      <c r="E32" s="8">
-        <v>1</v>
-      </c>
-      <c r="I32" s="33">
+      <c r="E32" s="54">
+        <v>1</v>
+      </c>
+      <c r="I32" s="40">
         <v>9780670813193</v>
       </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-      <c r="K32">
+      <c r="J32" s="44">
+        <v>1</v>
+      </c>
+      <c r="K32" s="46">
         <v>2</v>
       </c>
       <c r="L32" t="s">
@@ -3293,20 +5129,21 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="33" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D33" s="33">
+    <row r="33" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C33" s="27"/>
+      <c r="D33" s="40">
         <v>9780670813209</v>
       </c>
-      <c r="E33" s="8">
-        <v>1</v>
-      </c>
-      <c r="I33" s="33">
+      <c r="E33" s="54">
+        <v>1</v>
+      </c>
+      <c r="I33" s="40">
         <v>9780670813209</v>
       </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-      <c r="K33">
+      <c r="J33" s="44">
+        <v>1</v>
+      </c>
+      <c r="K33" s="46">
         <v>2</v>
       </c>
       <c r="L33" t="s">
@@ -3316,20 +5153,21 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="34" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D34" s="33">
+    <row r="34" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C34" s="27"/>
+      <c r="D34" s="40">
         <v>9780670813216</v>
       </c>
-      <c r="E34" s="8">
-        <v>1</v>
-      </c>
-      <c r="I34" s="33">
+      <c r="E34" s="54">
+        <v>1</v>
+      </c>
+      <c r="I34" s="40">
         <v>9780670813216</v>
       </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-      <c r="K34">
+      <c r="J34" s="44">
+        <v>1</v>
+      </c>
+      <c r="K34" s="46">
         <v>2</v>
       </c>
       <c r="L34" t="s">
@@ -3339,20 +5177,21 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="35" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D35" s="33">
+    <row r="35" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C35" s="27"/>
+      <c r="D35" s="40">
         <v>9780670813223</v>
       </c>
-      <c r="E35" s="9">
-        <v>1</v>
-      </c>
-      <c r="I35" s="33">
+      <c r="E35" s="56">
+        <v>1</v>
+      </c>
+      <c r="I35" s="40">
         <v>9780670813223</v>
       </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35">
+      <c r="J35" s="44">
+        <v>1</v>
+      </c>
+      <c r="K35" s="46">
         <v>2</v>
       </c>
       <c r="L35" t="s">
@@ -3362,20 +5201,21 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="36" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D36" s="33">
+    <row r="36" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C36" s="27"/>
+      <c r="D36" s="40">
         <v>9780670813230</v>
       </c>
-      <c r="E36" s="9">
-        <v>1</v>
-      </c>
-      <c r="I36" s="33">
+      <c r="E36" s="56">
+        <v>1</v>
+      </c>
+      <c r="I36" s="40">
         <v>9780670813230</v>
       </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-      <c r="K36">
+      <c r="J36" s="44">
+        <v>1</v>
+      </c>
+      <c r="K36" s="46">
         <v>2</v>
       </c>
       <c r="L36" t="s">
@@ -3385,20 +5225,21 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="37" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D37" s="33">
+    <row r="37" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C37" s="27"/>
+      <c r="D37" s="40">
         <v>9780670813247</v>
       </c>
-      <c r="E37" s="8">
-        <v>1</v>
-      </c>
-      <c r="I37" s="33">
+      <c r="E37" s="54">
+        <v>1</v>
+      </c>
+      <c r="I37" s="40">
         <v>9780670813247</v>
       </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
-      <c r="K37">
+      <c r="J37" s="44">
+        <v>1</v>
+      </c>
+      <c r="K37" s="46">
         <v>2</v>
       </c>
       <c r="L37" t="s">
@@ -3408,20 +5249,21 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="38" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D38" s="33">
+    <row r="38" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C38" s="27"/>
+      <c r="D38" s="40">
         <v>9780670813254</v>
       </c>
-      <c r="E38" s="9">
-        <v>1</v>
-      </c>
-      <c r="I38" s="33">
+      <c r="E38" s="56">
+        <v>1</v>
+      </c>
+      <c r="I38" s="40">
         <v>9780670813254</v>
       </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-      <c r="K38">
+      <c r="J38" s="44">
+        <v>1</v>
+      </c>
+      <c r="K38" s="46">
         <v>2</v>
       </c>
       <c r="L38" t="s">
@@ -3431,20 +5273,21 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="39" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D39" s="33">
+    <row r="39" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C39" s="27"/>
+      <c r="D39" s="40">
         <v>9780670813261</v>
       </c>
-      <c r="E39" s="8">
-        <v>1</v>
-      </c>
-      <c r="I39" s="33">
+      <c r="E39" s="54">
+        <v>1</v>
+      </c>
+      <c r="I39" s="40">
         <v>9780670813261</v>
       </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="K39">
+      <c r="J39" s="44">
+        <v>1</v>
+      </c>
+      <c r="K39" s="46">
         <v>2</v>
       </c>
       <c r="L39" t="s">
@@ -3454,20 +5297,21 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="40" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D40" s="33">
+    <row r="40" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C40" s="27"/>
+      <c r="D40" s="40">
         <v>9780670813278</v>
       </c>
-      <c r="E40" s="8">
-        <v>1</v>
-      </c>
-      <c r="I40" s="33">
+      <c r="E40" s="54">
+        <v>1</v>
+      </c>
+      <c r="I40" s="40">
         <v>9780670813278</v>
       </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="K40">
+      <c r="J40" s="44">
+        <v>1</v>
+      </c>
+      <c r="K40" s="46">
         <v>2</v>
       </c>
       <c r="L40" s="1">
@@ -3477,20 +5321,21 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="41" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D41" s="33">
+    <row r="41" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C41" s="27"/>
+      <c r="D41" s="40">
         <v>9780670813285</v>
       </c>
-      <c r="E41" s="8">
-        <v>1</v>
-      </c>
-      <c r="I41" s="33">
+      <c r="E41" s="54">
+        <v>1</v>
+      </c>
+      <c r="I41" s="40">
         <v>9780670813285</v>
       </c>
-      <c r="J41">
-        <v>1</v>
-      </c>
-      <c r="K41">
+      <c r="J41" s="44">
+        <v>1</v>
+      </c>
+      <c r="K41" s="46">
         <v>2</v>
       </c>
       <c r="L41" t="s">
@@ -3500,20 +5345,21 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="42" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D42" s="33">
+    <row r="42" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C42" s="27"/>
+      <c r="D42" s="40">
         <v>9780670813292</v>
       </c>
-      <c r="E42" s="8">
-        <v>1</v>
-      </c>
-      <c r="I42" s="33">
+      <c r="E42" s="54">
+        <v>1</v>
+      </c>
+      <c r="I42" s="40">
         <v>9780670813292</v>
       </c>
-      <c r="J42">
-        <v>1</v>
-      </c>
-      <c r="K42">
+      <c r="J42" s="44">
+        <v>1</v>
+      </c>
+      <c r="K42" s="46">
         <v>2</v>
       </c>
       <c r="L42" t="s">
@@ -3523,20 +5369,21 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="43" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D43" s="33">
+    <row r="43" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C43" s="27"/>
+      <c r="D43" s="40">
         <v>9780670813308</v>
       </c>
-      <c r="E43" s="8">
-        <v>1</v>
-      </c>
-      <c r="I43" s="33">
+      <c r="E43" s="54">
+        <v>1</v>
+      </c>
+      <c r="I43" s="40">
         <v>9780670813308</v>
       </c>
-      <c r="J43">
-        <v>1</v>
-      </c>
-      <c r="K43">
+      <c r="J43" s="44">
+        <v>1</v>
+      </c>
+      <c r="K43" s="46">
         <v>2</v>
       </c>
       <c r="L43" t="s">
@@ -3546,20 +5393,21 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="44" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D44" s="33">
+    <row r="44" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C44" s="27"/>
+      <c r="D44" s="40">
         <v>9780670813315</v>
       </c>
-      <c r="E44" s="8">
-        <v>1</v>
-      </c>
-      <c r="I44" s="33">
+      <c r="E44" s="54">
+        <v>1</v>
+      </c>
+      <c r="I44" s="40">
         <v>9780670813315</v>
       </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="K44">
+      <c r="J44" s="44">
+        <v>1</v>
+      </c>
+      <c r="K44" s="46">
         <v>2</v>
       </c>
       <c r="L44" t="s">
@@ -3569,20 +5417,21 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="45" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D45" s="33">
+    <row r="45" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C45" s="27"/>
+      <c r="D45" s="40">
         <v>9780670813322</v>
       </c>
-      <c r="E45" s="8">
-        <v>1</v>
-      </c>
-      <c r="I45" s="33">
+      <c r="E45" s="54">
+        <v>1</v>
+      </c>
+      <c r="I45" s="40">
         <v>9780670813322</v>
       </c>
-      <c r="J45">
-        <v>1</v>
-      </c>
-      <c r="K45">
+      <c r="J45" s="44">
+        <v>1</v>
+      </c>
+      <c r="K45" s="46">
         <v>2</v>
       </c>
       <c r="L45" t="s">
@@ -3592,20 +5441,21 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="46" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D46" s="33">
+    <row r="46" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C46" s="27"/>
+      <c r="D46" s="40">
         <v>9780670813339</v>
       </c>
-      <c r="E46" s="8">
-        <v>1</v>
-      </c>
-      <c r="I46" s="33">
+      <c r="E46" s="54">
+        <v>1</v>
+      </c>
+      <c r="I46" s="40">
         <v>9780670813339</v>
       </c>
-      <c r="J46">
-        <v>1</v>
-      </c>
-      <c r="K46">
+      <c r="J46" s="44">
+        <v>1</v>
+      </c>
+      <c r="K46" s="46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
@@ -3614,24 +5464,22 @@
       <c r="M46">
         <v>2018</v>
       </c>
-      <c r="O46" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="47" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D47" s="33">
+    </row>
+    <row r="47" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C47" s="27"/>
+      <c r="D47" s="40">
         <v>9780670813346</v>
       </c>
-      <c r="E47" s="8">
-        <v>1</v>
-      </c>
-      <c r="I47" s="33">
+      <c r="E47" s="54">
+        <v>1</v>
+      </c>
+      <c r="I47" s="40">
         <v>9780670813346</v>
       </c>
-      <c r="J47">
-        <v>1</v>
-      </c>
-      <c r="K47">
+      <c r="J47" s="44">
+        <v>1</v>
+      </c>
+      <c r="K47" s="46">
         <v>2</v>
       </c>
       <c r="L47" t="s">
@@ -3640,27 +5488,22 @@
       <c r="M47">
         <v>2021</v>
       </c>
-      <c r="O47" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="P47" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="48" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D48" s="33">
+    </row>
+    <row r="48" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C48" s="27"/>
+      <c r="D48" s="40">
         <v>9780670813353</v>
       </c>
-      <c r="E48" s="8">
-        <v>1</v>
-      </c>
-      <c r="I48" s="33">
+      <c r="E48" s="54">
+        <v>1</v>
+      </c>
+      <c r="I48" s="40">
         <v>9780670813353</v>
       </c>
-      <c r="J48">
-        <v>1</v>
-      </c>
-      <c r="K48">
+      <c r="J48" s="44">
+        <v>1</v>
+      </c>
+      <c r="K48" s="46">
         <v>2</v>
       </c>
       <c r="L48" t="s">
@@ -3669,27 +5512,22 @@
       <c r="M48">
         <v>2021</v>
       </c>
-      <c r="O48">
-        <v>1</v>
-      </c>
-      <c r="P48" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="D49" s="33">
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C49" s="27"/>
+      <c r="D49" s="40">
         <v>9780670813360</v>
       </c>
-      <c r="E49" s="8">
-        <v>1</v>
-      </c>
-      <c r="I49" s="33">
+      <c r="E49" s="54">
+        <v>1</v>
+      </c>
+      <c r="I49" s="40">
         <v>9780670813360</v>
       </c>
-      <c r="J49">
-        <v>1</v>
-      </c>
-      <c r="K49">
+      <c r="J49" s="44">
+        <v>1</v>
+      </c>
+      <c r="K49" s="46">
         <v>2</v>
       </c>
       <c r="L49" t="s">
@@ -3699,20 +5537,21 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="D50" s="33">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C50" s="27"/>
+      <c r="D50" s="40">
         <v>9780670813377</v>
       </c>
-      <c r="E50" s="8">
-        <v>1</v>
-      </c>
-      <c r="I50" s="33">
+      <c r="E50" s="54">
+        <v>1</v>
+      </c>
+      <c r="I50" s="40">
         <v>9780670813377</v>
       </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
-      <c r="K50">
+      <c r="J50" s="44">
+        <v>1</v>
+      </c>
+      <c r="K50" s="46">
         <v>2</v>
       </c>
       <c r="L50" t="s">
@@ -3722,20 +5561,21 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="51" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D51" s="34">
+    <row r="51" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="27"/>
+      <c r="D51" s="41">
         <v>9780670813384</v>
       </c>
-      <c r="E51" s="9">
-        <v>1</v>
-      </c>
-      <c r="I51" s="34">
+      <c r="E51" s="51">
+        <v>1</v>
+      </c>
+      <c r="I51" s="41">
         <v>9780670813384</v>
       </c>
-      <c r="J51">
-        <v>1</v>
-      </c>
-      <c r="K51">
+      <c r="J51" s="48">
+        <v>1</v>
+      </c>
+      <c r="K51" s="47">
         <v>2</v>
       </c>
       <c r="L51" t="s">
@@ -3745,23 +5585,23 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="52" spans="2:17" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="55" spans="2:17" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="28" t="s">
+    <row r="55" spans="2:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="59" t="s">
         <v>78</v>
       </c>
       <c r="D55" t="s">
         <v>79</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="26" t="s">
         <v>6</v>
       </c>
       <c r="G55" t="s">
@@ -3771,1064 +5611,1082 @@
         <v>103</v>
       </c>
     </row>
-    <row r="56" spans="2:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" s="29">
+    <row r="56" spans="2:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="57">
+        <v>1</v>
+      </c>
+      <c r="C56" s="60">
         <v>6</v>
       </c>
       <c r="D56" t="b">
         <v>1</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="16">
         <v>9780385086952</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="H56" s="32" t="s">
+      <c r="H56" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="K56" s="5" t="s">
+      <c r="K56" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L56" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B57">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B57" s="57">
         <v>2</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="60">
         <v>6</v>
       </c>
       <c r="D57" t="b">
         <v>1</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="17">
         <v>9780307743657</v>
       </c>
-      <c r="G57">
-        <v>1</v>
-      </c>
-      <c r="H57" s="37">
+      <c r="G57" s="24">
+        <v>1</v>
+      </c>
+      <c r="H57" s="21">
         <v>9780385086952</v>
       </c>
-      <c r="K57">
+      <c r="K57" s="46">
         <v>1</v>
       </c>
       <c r="L57" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B58">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B58" s="57">
         <v>3</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="60">
         <v>6</v>
       </c>
       <c r="D58" t="b">
         <v>1</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="16">
         <v>9780307743664</v>
       </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-      <c r="H58" s="38">
+      <c r="G58" s="24">
+        <v>1</v>
+      </c>
+      <c r="H58" s="22">
         <v>9780307743657</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="46">
         <v>2</v>
       </c>
       <c r="L58" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B59">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B59" s="57">
         <v>4</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="60">
         <v>7</v>
       </c>
       <c r="D59" t="b">
         <v>1</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="17">
         <v>9780670813025</v>
       </c>
-      <c r="G59">
-        <v>1</v>
-      </c>
-      <c r="H59" s="37">
+      <c r="G59" s="24">
+        <v>1</v>
+      </c>
+      <c r="H59" s="21">
         <v>9780307743664</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="46">
         <v>3</v>
       </c>
       <c r="L59" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B60">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B60" s="57">
         <v>5</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="60">
         <v>7</v>
       </c>
       <c r="D60" t="b">
         <v>1</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="16">
         <v>9780345418864</v>
       </c>
-      <c r="G60">
-        <v>1</v>
-      </c>
-      <c r="H60" s="38">
+      <c r="G60" s="24">
+        <v>1</v>
+      </c>
+      <c r="H60" s="22">
         <v>9780670813025</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="46">
         <v>4</v>
       </c>
       <c r="L60" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B61">
+    <row r="61" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="57">
         <v>6</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="60">
         <v>6</v>
       </c>
       <c r="D61" t="b">
         <v>1</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="17">
         <v>9780670813032</v>
       </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-      <c r="H61" s="37">
+      <c r="G61" s="24">
+        <v>1</v>
+      </c>
+      <c r="H61" s="21">
         <v>9780345418864</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="47">
         <v>5</v>
       </c>
       <c r="L61" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B62">
+    <row r="62" spans="2:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="57">
         <v>7</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="60">
         <v>6</v>
       </c>
       <c r="D62" t="b">
         <v>1</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="16">
         <v>9780670813049</v>
       </c>
-      <c r="G62">
-        <v>1</v>
-      </c>
-      <c r="H62" s="38">
+      <c r="G62" s="24">
+        <v>1</v>
+      </c>
+      <c r="H62" s="22">
         <v>9780670813032</v>
       </c>
-      <c r="M62" t="s">
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B63" s="57">
+        <v>8</v>
+      </c>
+      <c r="C63" s="60">
+        <v>8</v>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="17">
+        <v>9780670813056</v>
+      </c>
+      <c r="G63" s="24">
+        <v>1</v>
+      </c>
+      <c r="H63" s="21">
+        <v>9780670813049</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B64" s="57">
+        <v>9</v>
+      </c>
+      <c r="C64" s="60">
+        <v>8</v>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="16">
+        <v>9780670813063</v>
+      </c>
+      <c r="G64" s="24">
+        <v>1</v>
+      </c>
+      <c r="H64" s="22">
+        <v>9780670813056</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B65" s="57">
+        <v>10</v>
+      </c>
+      <c r="C65" s="60">
+        <v>8</v>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="17">
+        <v>9780670813070</v>
+      </c>
+      <c r="G65" s="24">
+        <v>1</v>
+      </c>
+      <c r="H65" s="21">
+        <v>9780670813063</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B66" s="57">
+        <v>11</v>
+      </c>
+      <c r="C66" s="60">
+        <v>8</v>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="16">
+        <v>9780670813087</v>
+      </c>
+      <c r="G66" s="24">
+        <v>1</v>
+      </c>
+      <c r="H66" s="22">
+        <v>9780670813070</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B67" s="57">
+        <v>12</v>
+      </c>
+      <c r="C67" s="60">
+        <v>6</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="17">
+        <v>9780670813094</v>
+      </c>
+      <c r="G67" s="24">
+        <v>1</v>
+      </c>
+      <c r="H67" s="21">
+        <v>9780670813087</v>
+      </c>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B68" s="57">
+        <v>13</v>
+      </c>
+      <c r="C68" s="60">
+        <v>6</v>
+      </c>
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="16">
+        <v>9780670813100</v>
+      </c>
+      <c r="G68" s="24">
+        <v>1</v>
+      </c>
+      <c r="H68" s="22">
+        <v>9780670813094</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B69" s="57">
+        <v>14</v>
+      </c>
+      <c r="C69" s="60">
+        <v>6</v>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="17">
+        <v>9780670813117</v>
+      </c>
+      <c r="G69" s="24">
+        <v>1</v>
+      </c>
+      <c r="H69" s="21">
+        <v>9780670813100</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B70" s="57">
+        <v>15</v>
+      </c>
+      <c r="C70" s="60">
+        <v>6</v>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="16">
+        <v>9780670813124</v>
+      </c>
+      <c r="G70" s="24">
+        <v>1</v>
+      </c>
+      <c r="H70" s="22">
+        <v>9780670813117</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B71" s="57">
+        <v>16</v>
+      </c>
+      <c r="C71" s="60">
+        <v>6</v>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="17">
+        <v>9780670813131</v>
+      </c>
+      <c r="G71" s="24">
+        <v>1</v>
+      </c>
+      <c r="H71" s="21">
+        <v>9780670813124</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B72" s="57">
+        <v>17</v>
+      </c>
+      <c r="C72" s="60">
+        <v>6</v>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="16">
+        <v>9780670813148</v>
+      </c>
+      <c r="G72" s="24">
+        <v>1</v>
+      </c>
+      <c r="H72" s="22">
+        <v>9780670813131</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="57">
+        <v>18</v>
+      </c>
+      <c r="C73" s="60">
+        <v>6</v>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="17">
+        <v>9780670813155</v>
+      </c>
+      <c r="G73" s="24">
+        <v>1</v>
+      </c>
+      <c r="H73" s="21">
+        <v>9780670813148</v>
+      </c>
+      <c r="O73" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="57">
+        <v>19</v>
+      </c>
+      <c r="C74" s="60">
+        <v>6</v>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="16">
+        <v>9780670813162</v>
+      </c>
+      <c r="G74" s="24">
+        <v>1</v>
+      </c>
+      <c r="H74" s="22">
+        <v>9780670813155</v>
+      </c>
+      <c r="O74" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="P74" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B75" s="57">
+        <v>20</v>
+      </c>
+      <c r="C75" s="60">
+        <v>6</v>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="17">
+        <v>9780670813179</v>
+      </c>
+      <c r="G75" s="24">
+        <v>1</v>
+      </c>
+      <c r="H75" s="21">
+        <v>9780670813162</v>
+      </c>
+      <c r="O75" s="24">
+        <v>1</v>
+      </c>
+      <c r="P75" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="57">
+        <v>21</v>
+      </c>
+      <c r="C76" s="60">
+        <v>6</v>
+      </c>
+      <c r="D76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" s="16">
+        <v>9780670813186</v>
+      </c>
+      <c r="G76" s="24">
+        <v>1</v>
+      </c>
+      <c r="H76" s="22">
+        <v>9780670813179</v>
+      </c>
+      <c r="J76" t="s">
+        <v>98</v>
+      </c>
+      <c r="O76" s="24">
+        <v>2</v>
+      </c>
+      <c r="P76" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="57">
+        <v>22</v>
+      </c>
+      <c r="C77" s="60">
+        <v>6</v>
+      </c>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="17">
+        <v>9780670813193</v>
+      </c>
+      <c r="G77" s="24">
+        <v>1</v>
+      </c>
+      <c r="H77" s="21">
+        <v>9780670813186</v>
+      </c>
+      <c r="J77" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="K77" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="O77" s="25">
+        <v>3</v>
+      </c>
+      <c r="P77" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="78" spans="2:16" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="57">
+        <v>23</v>
+      </c>
+      <c r="C78" s="60">
+        <v>6</v>
+      </c>
+      <c r="D78" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="16">
+        <v>9780670813209</v>
+      </c>
+      <c r="G78" s="24">
+        <v>1</v>
+      </c>
+      <c r="H78" s="22">
+        <v>9780670813193</v>
+      </c>
+      <c r="J78" s="86">
+        <v>1</v>
+      </c>
+      <c r="K78" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="57">
+        <v>24</v>
+      </c>
+      <c r="C79" s="60">
+        <v>6</v>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="17">
+        <v>9780670813216</v>
+      </c>
+      <c r="G79" s="24">
+        <v>1</v>
+      </c>
+      <c r="H79" s="21">
+        <v>9780670813209</v>
+      </c>
+      <c r="M79" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B63">
-        <v>8</v>
-      </c>
-      <c r="C63" s="29">
-        <v>8</v>
-      </c>
-      <c r="D63" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="3">
-        <v>9780670813056</v>
-      </c>
-      <c r="G63">
-        <v>1</v>
-      </c>
-      <c r="H63" s="37">
-        <v>9780670813049</v>
-      </c>
-      <c r="M63" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N63" t="s">
+    <row r="80" spans="2:16" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="57">
+        <v>25</v>
+      </c>
+      <c r="C80" s="60">
+        <v>6</v>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" s="16">
+        <v>9780670813223</v>
+      </c>
+      <c r="G80" s="24">
+        <v>1</v>
+      </c>
+      <c r="H80" s="22">
+        <v>9780670813216</v>
+      </c>
+      <c r="M80" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="N80" t="s">
         <v>97</v>
       </c>
-      <c r="P63" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B64">
-        <v>9</v>
-      </c>
-      <c r="C64" s="29">
-        <v>8</v>
-      </c>
-      <c r="D64" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="2">
-        <v>9780670813063</v>
-      </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64" s="38">
-        <v>9780670813056</v>
-      </c>
-      <c r="M64">
-        <v>1</v>
-      </c>
-      <c r="N64">
+      <c r="P80" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="81" spans="2:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="57">
+        <v>26</v>
+      </c>
+      <c r="C81" s="60">
+        <v>6</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="17">
+        <v>9780670813230</v>
+      </c>
+      <c r="G81" s="24">
+        <v>1</v>
+      </c>
+      <c r="H81" s="21">
+        <v>9780670813223</v>
+      </c>
+      <c r="M81" s="70">
+        <v>1</v>
+      </c>
+      <c r="N81">
         <v>1010</v>
       </c>
-      <c r="P64" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q64" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B65">
-        <v>10</v>
-      </c>
-      <c r="C65" s="29">
-        <v>8</v>
-      </c>
-      <c r="D65" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="3">
-        <v>9780670813070</v>
-      </c>
-      <c r="G65">
-        <v>1</v>
-      </c>
-      <c r="H65" s="37">
-        <v>9780670813063</v>
-      </c>
-      <c r="M65">
+      <c r="P81" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="82" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B82" s="57">
+        <v>27</v>
+      </c>
+      <c r="C82" s="60">
+        <v>6</v>
+      </c>
+      <c r="D82" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="16">
+        <v>9780670813247</v>
+      </c>
+      <c r="G82" s="24">
+        <v>1</v>
+      </c>
+      <c r="H82" s="22">
+        <v>9780670813230</v>
+      </c>
+      <c r="M82" s="70">
         <v>2</v>
       </c>
-      <c r="N65">
+      <c r="N82">
         <v>8010</v>
       </c>
-      <c r="P65">
-        <v>1</v>
-      </c>
-      <c r="Q65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B66">
-        <v>11</v>
-      </c>
-      <c r="C66" s="29">
-        <v>8</v>
-      </c>
-      <c r="D66" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="2">
-        <v>9780670813087</v>
-      </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
-      <c r="H66" s="38">
-        <v>9780670813070</v>
-      </c>
-      <c r="M66">
+      <c r="P82" s="79">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="83" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="57">
+        <v>28</v>
+      </c>
+      <c r="C83" s="60">
+        <v>6</v>
+      </c>
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="17">
+        <v>9780670813254</v>
+      </c>
+      <c r="G83" s="24">
+        <v>1</v>
+      </c>
+      <c r="H83" s="21">
+        <v>9780670813247</v>
+      </c>
+      <c r="M83" s="71">
         <v>3</v>
       </c>
-      <c r="N66">
+      <c r="N83">
         <v>8263</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B67">
-        <v>12</v>
-      </c>
-      <c r="C67" s="29">
+      <c r="P83" s="79">
+        <v>2</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="84" spans="2:17" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="57">
+        <v>29</v>
+      </c>
+      <c r="C84" s="60">
         <v>6</v>
       </c>
-      <c r="D67" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="3">
-        <v>9780670813094</v>
-      </c>
-      <c r="G67">
-        <v>1</v>
-      </c>
-      <c r="H67" s="37">
-        <v>9780670813087</v>
-      </c>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B68">
-        <v>13</v>
-      </c>
-      <c r="C68" s="29">
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="16">
+        <v>9780670813261</v>
+      </c>
+      <c r="G84" s="24">
+        <v>1</v>
+      </c>
+      <c r="H84" s="22">
+        <v>9780670813254</v>
+      </c>
+      <c r="P84" s="80">
+        <v>3</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="85" spans="2:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="57">
+        <v>30</v>
+      </c>
+      <c r="C85" s="60">
         <v>6</v>
       </c>
-      <c r="D68" t="b">
-        <v>1</v>
-      </c>
-      <c r="E68" s="2">
-        <v>9780670813100</v>
-      </c>
-      <c r="G68">
-        <v>1</v>
-      </c>
-      <c r="H68" s="38">
-        <v>9780670813094</v>
-      </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B69">
-        <v>14</v>
-      </c>
-      <c r="C69" s="29">
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="17">
+        <v>9780670813278</v>
+      </c>
+      <c r="G85" s="24">
+        <v>1</v>
+      </c>
+      <c r="H85" s="21">
+        <v>9780670813261</v>
+      </c>
+    </row>
+    <row r="86" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B86" s="57">
+        <v>31</v>
+      </c>
+      <c r="C86" s="60">
         <v>6</v>
       </c>
-      <c r="D69" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" s="3">
-        <v>9780670813117</v>
-      </c>
-      <c r="G69">
-        <v>1</v>
-      </c>
-      <c r="H69" s="37">
-        <v>9780670813100</v>
-      </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B70">
-        <v>15</v>
-      </c>
-      <c r="C70" s="29">
+      <c r="D86" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="16">
+        <v>9780670813285</v>
+      </c>
+      <c r="G86" s="24">
+        <v>1</v>
+      </c>
+      <c r="H86" s="22">
+        <v>9780670813278</v>
+      </c>
+    </row>
+    <row r="87" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="57">
+        <v>32</v>
+      </c>
+      <c r="C87" s="60">
         <v>6</v>
       </c>
-      <c r="D70" t="b">
-        <v>1</v>
-      </c>
-      <c r="E70" s="2">
-        <v>9780670813124</v>
-      </c>
-      <c r="G70">
-        <v>1</v>
-      </c>
-      <c r="H70" s="38">
-        <v>9780670813117</v>
-      </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B71">
-        <v>16</v>
-      </c>
-      <c r="C71" s="29">
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="17">
+        <v>9780670813292</v>
+      </c>
+      <c r="G87" s="24">
+        <v>1</v>
+      </c>
+      <c r="H87" s="21">
+        <v>9780670813285</v>
+      </c>
+      <c r="J87" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" spans="2:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="57">
+        <v>33</v>
+      </c>
+      <c r="C88" s="60">
         <v>6</v>
       </c>
-      <c r="D71" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="3">
-        <v>9780670813131</v>
-      </c>
-      <c r="G71">
-        <v>1</v>
-      </c>
-      <c r="H71" s="37">
-        <v>9780670813124</v>
-      </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B72">
-        <v>17</v>
-      </c>
-      <c r="C72" s="29">
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="16">
+        <v>9780670813308</v>
+      </c>
+      <c r="G88" s="24">
+        <v>1</v>
+      </c>
+      <c r="H88" s="22">
+        <v>9780670813292</v>
+      </c>
+      <c r="J88" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="K88" t="s">
+        <v>80</v>
+      </c>
+      <c r="L88" t="s">
+        <v>81</v>
+      </c>
+      <c r="M88" s="72" t="s">
+        <v>82</v>
+      </c>
+      <c r="N88" s="75" t="s">
+        <v>83</v>
+      </c>
+      <c r="O88" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="P88" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B89" s="57">
+        <v>34</v>
+      </c>
+      <c r="C89" s="60">
         <v>6</v>
       </c>
-      <c r="D72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="2">
-        <v>9780670813148</v>
-      </c>
-      <c r="G72">
-        <v>1</v>
-      </c>
-      <c r="H72" s="38">
-        <v>9780670813131</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B73">
-        <v>18</v>
-      </c>
-      <c r="C73" s="29">
+      <c r="D89" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="17">
+        <v>9780670813315</v>
+      </c>
+      <c r="G89" s="24">
+        <v>1</v>
+      </c>
+      <c r="H89" s="21">
+        <v>9780670813308</v>
+      </c>
+      <c r="J89" s="67">
+        <v>1</v>
+      </c>
+      <c r="K89" t="s">
+        <v>87</v>
+      </c>
+      <c r="L89" t="s">
+        <v>88</v>
+      </c>
+      <c r="M89" s="73">
+        <v>1</v>
+      </c>
+      <c r="N89" s="76">
+        <v>3</v>
+      </c>
+      <c r="O89" s="82">
+        <v>3</v>
+      </c>
+      <c r="P89" s="79">
+        <v>1</v>
+      </c>
+      <c r="Q89">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="90" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="57">
+        <v>35</v>
+      </c>
+      <c r="C90" s="60">
         <v>6</v>
       </c>
-      <c r="D73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" s="3">
-        <v>9780670813155</v>
-      </c>
-      <c r="G73">
-        <v>1</v>
-      </c>
-      <c r="H73" s="37">
-        <v>9780670813148</v>
-      </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B74">
-        <v>19</v>
-      </c>
-      <c r="C74" s="29">
+      <c r="D90" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="16">
+        <v>9780670813322</v>
+      </c>
+      <c r="G90" s="24">
+        <v>1</v>
+      </c>
+      <c r="H90" s="22">
+        <v>9780670813315</v>
+      </c>
+      <c r="J90" s="68">
+        <v>2</v>
+      </c>
+      <c r="K90" t="s">
+        <v>89</v>
+      </c>
+      <c r="L90" t="s">
+        <v>90</v>
+      </c>
+      <c r="M90" s="74">
+        <v>1</v>
+      </c>
+      <c r="N90" s="77">
+        <v>3</v>
+      </c>
+      <c r="O90" s="83">
+        <v>3</v>
+      </c>
+      <c r="P90" s="80">
+        <v>1</v>
+      </c>
+      <c r="Q90">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="91" spans="2:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="57">
+        <v>36</v>
+      </c>
+      <c r="C91" s="60">
         <v>6</v>
       </c>
-      <c r="D74" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" s="2">
-        <v>9780670813162</v>
-      </c>
-      <c r="G74">
-        <v>1</v>
-      </c>
-      <c r="H74" s="38">
-        <v>9780670813155</v>
-      </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B75">
-        <v>20</v>
-      </c>
-      <c r="C75" s="29">
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="17">
+        <v>9780670813339</v>
+      </c>
+      <c r="G91" s="24">
+        <v>1</v>
+      </c>
+      <c r="H91" s="21">
+        <v>9780670813322</v>
+      </c>
+    </row>
+    <row r="92" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B92" s="57">
+        <v>37</v>
+      </c>
+      <c r="C92" s="60">
         <v>6</v>
       </c>
-      <c r="D75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" s="3">
-        <v>9780670813179</v>
-      </c>
-      <c r="G75">
-        <v>1</v>
-      </c>
-      <c r="H75" s="37">
-        <v>9780670813162</v>
-      </c>
-      <c r="M75" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B76">
-        <v>21</v>
-      </c>
-      <c r="C76" s="29">
+      <c r="D92" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="16">
+        <v>9780670813346</v>
+      </c>
+      <c r="G92" s="24">
+        <v>1</v>
+      </c>
+      <c r="H92" s="22">
+        <v>9780670813339</v>
+      </c>
+    </row>
+    <row r="93" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="57">
+        <v>38</v>
+      </c>
+      <c r="C93" s="60">
         <v>6</v>
       </c>
-      <c r="D76" t="b">
-        <v>1</v>
-      </c>
-      <c r="E76" s="2">
-        <v>9780670813186</v>
-      </c>
-      <c r="G76">
-        <v>1</v>
-      </c>
-      <c r="H76" s="38">
-        <v>9780670813179</v>
-      </c>
-      <c r="J76" t="s">
-        <v>110</v>
-      </c>
-      <c r="M76" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N76" t="s">
-        <v>80</v>
-      </c>
-      <c r="O76" t="s">
-        <v>81</v>
-      </c>
-      <c r="P76" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>83</v>
-      </c>
-      <c r="R76" t="s">
-        <v>84</v>
-      </c>
-      <c r="S76" t="s">
-        <v>85</v>
-      </c>
-      <c r="T76" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B77">
-        <v>22</v>
-      </c>
-      <c r="C77" s="29">
+      <c r="D93" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="17">
+        <v>9780670813353</v>
+      </c>
+      <c r="G93" s="24">
+        <v>1</v>
+      </c>
+      <c r="H93" s="21">
+        <v>9780670813346</v>
+      </c>
+      <c r="M93" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="94" spans="2:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="57">
+        <v>39</v>
+      </c>
+      <c r="C94" s="60">
         <v>6</v>
       </c>
-      <c r="D77" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" s="3">
-        <v>9780670813193</v>
-      </c>
-      <c r="G77">
-        <v>1</v>
-      </c>
-      <c r="H77" s="37">
-        <v>9780670813186</v>
-      </c>
-      <c r="J77" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K77" t="s">
-        <v>110</v>
-      </c>
-      <c r="M77">
-        <v>1</v>
-      </c>
-      <c r="N77" t="s">
-        <v>87</v>
-      </c>
-      <c r="O77" t="s">
-        <v>88</v>
-      </c>
-      <c r="P77">
-        <v>1</v>
-      </c>
-      <c r="Q77">
-        <v>3</v>
-      </c>
-      <c r="R77">
-        <v>3</v>
-      </c>
-      <c r="S77">
-        <v>1</v>
-      </c>
-      <c r="T77">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="78" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B78">
-        <v>23</v>
-      </c>
-      <c r="C78" s="29">
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="16">
+        <v>9780670813360</v>
+      </c>
+      <c r="G94" s="24">
+        <v>1</v>
+      </c>
+      <c r="H94" s="22">
+        <v>9780670813353</v>
+      </c>
+      <c r="M94" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="N94" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="57">
+        <v>40</v>
+      </c>
+      <c r="C95" s="60">
         <v>6</v>
       </c>
-      <c r="D78" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" s="2">
-        <v>9780670813209</v>
-      </c>
-      <c r="G78">
-        <v>1</v>
-      </c>
-      <c r="H78" s="38">
-        <v>9780670813193</v>
-      </c>
-      <c r="J78">
-        <v>1</v>
-      </c>
-      <c r="K78" t="s">
-        <v>111</v>
-      </c>
-      <c r="M78">
-        <v>2</v>
-      </c>
-      <c r="N78" t="s">
-        <v>89</v>
-      </c>
-      <c r="O78" t="s">
-        <v>90</v>
-      </c>
-      <c r="P78">
-        <v>1</v>
-      </c>
-      <c r="Q78">
-        <v>3</v>
-      </c>
-      <c r="R78">
-        <v>3</v>
-      </c>
-      <c r="S78">
-        <v>1</v>
-      </c>
-      <c r="T78">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B79">
-        <v>24</v>
-      </c>
-      <c r="C79" s="29">
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="17">
+        <v>9780670813377</v>
+      </c>
+      <c r="G95" s="24">
+        <v>1</v>
+      </c>
+      <c r="H95" s="21">
+        <v>9780670813360</v>
+      </c>
+      <c r="M95" s="47">
+        <v>1</v>
+      </c>
+      <c r="N95" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="96" spans="2:17" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="58">
+        <v>41</v>
+      </c>
+      <c r="C96" s="61">
         <v>6</v>
       </c>
-      <c r="D79" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="3">
-        <v>9780670813216</v>
-      </c>
-      <c r="G79">
-        <v>1</v>
-      </c>
-      <c r="H79" s="37">
-        <v>9780670813209</v>
-      </c>
-      <c r="J79">
-        <v>2</v>
-      </c>
-      <c r="K79" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B80">
-        <v>25</v>
-      </c>
-      <c r="C80" s="29">
-        <v>6</v>
-      </c>
-      <c r="D80" t="b">
-        <v>1</v>
-      </c>
-      <c r="E80" s="2">
-        <v>9780670813223</v>
-      </c>
-      <c r="G80">
-        <v>1</v>
-      </c>
-      <c r="H80" s="38">
-        <v>9780670813216</v>
-      </c>
-      <c r="J80">
-        <v>3</v>
-      </c>
-      <c r="K80" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B81">
-        <v>26</v>
-      </c>
-      <c r="C81" s="29">
-        <v>6</v>
-      </c>
-      <c r="D81" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" s="3">
-        <v>9780670813230</v>
-      </c>
-      <c r="G81">
-        <v>1</v>
-      </c>
-      <c r="H81" s="37">
-        <v>9780670813223</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B82">
-        <v>27</v>
-      </c>
-      <c r="C82" s="29">
-        <v>6</v>
-      </c>
-      <c r="D82" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" s="2">
-        <v>9780670813247</v>
-      </c>
-      <c r="G82">
-        <v>1</v>
-      </c>
-      <c r="H82" s="38">
-        <v>9780670813230</v>
-      </c>
-      <c r="J82" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B83">
-        <v>28</v>
-      </c>
-      <c r="C83" s="29">
-        <v>6</v>
-      </c>
-      <c r="D83" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="3">
-        <v>9780670813254</v>
-      </c>
-      <c r="G83">
-        <v>1</v>
-      </c>
-      <c r="H83" s="37">
-        <v>9780670813247</v>
-      </c>
-      <c r="J83" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K83" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B84">
-        <v>29</v>
-      </c>
-      <c r="C84" s="29">
-        <v>6</v>
-      </c>
-      <c r="D84" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" s="2">
-        <v>9780670813261</v>
-      </c>
-      <c r="G84">
-        <v>1</v>
-      </c>
-      <c r="H84" s="38">
-        <v>9780670813254</v>
-      </c>
-      <c r="J84">
-        <v>1</v>
-      </c>
-      <c r="K84" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B85">
-        <v>30</v>
-      </c>
-      <c r="C85" s="29">
-        <v>6</v>
-      </c>
-      <c r="D85" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" s="3">
-        <v>9780670813278</v>
-      </c>
-      <c r="G85">
-        <v>1</v>
-      </c>
-      <c r="H85" s="37">
-        <v>9780670813261</v>
-      </c>
-      <c r="J85">
-        <v>2</v>
-      </c>
-      <c r="K85" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B86">
-        <v>31</v>
-      </c>
-      <c r="C86" s="29">
-        <v>6</v>
-      </c>
-      <c r="D86" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" s="2">
-        <v>9780670813285</v>
-      </c>
-      <c r="G86">
-        <v>1</v>
-      </c>
-      <c r="H86" s="38">
-        <v>9780670813278</v>
-      </c>
-      <c r="J86">
-        <v>3</v>
-      </c>
-      <c r="K86" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B87">
-        <v>32</v>
-      </c>
-      <c r="C87" s="29">
-        <v>6</v>
-      </c>
-      <c r="D87" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="3">
-        <v>9780670813292</v>
-      </c>
-      <c r="G87">
-        <v>1</v>
-      </c>
-      <c r="H87" s="37">
-        <v>9780670813285</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B88">
-        <v>33</v>
-      </c>
-      <c r="C88" s="29">
-        <v>6</v>
-      </c>
-      <c r="D88" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="2">
-        <v>9780670813308</v>
-      </c>
-      <c r="G88">
-        <v>1</v>
-      </c>
-      <c r="H88" s="38">
-        <v>9780670813292</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B89">
-        <v>34</v>
-      </c>
-      <c r="C89" s="29">
-        <v>6</v>
-      </c>
-      <c r="D89" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" s="3">
-        <v>9780670813315</v>
-      </c>
-      <c r="G89">
-        <v>1</v>
-      </c>
-      <c r="H89" s="37">
-        <v>9780670813308</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B90">
-        <v>35</v>
-      </c>
-      <c r="C90" s="29">
-        <v>6</v>
-      </c>
-      <c r="D90" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" s="2">
-        <v>9780670813322</v>
-      </c>
-      <c r="G90">
-        <v>1</v>
-      </c>
-      <c r="H90" s="38">
-        <v>9780670813315</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B91">
-        <v>36</v>
-      </c>
-      <c r="C91" s="29">
-        <v>6</v>
-      </c>
-      <c r="D91" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" s="3">
-        <v>9780670813339</v>
-      </c>
-      <c r="G91">
-        <v>1</v>
-      </c>
-      <c r="H91" s="37">
-        <v>9780670813322</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B92">
-        <v>37</v>
-      </c>
-      <c r="C92" s="29">
-        <v>6</v>
-      </c>
-      <c r="D92" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="2">
-        <v>9780670813346</v>
-      </c>
-      <c r="G92">
-        <v>1</v>
-      </c>
-      <c r="H92" s="38">
-        <v>9780670813339</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B93">
-        <v>38</v>
-      </c>
-      <c r="C93" s="29">
-        <v>6</v>
-      </c>
-      <c r="D93" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="3">
-        <v>9780670813353</v>
-      </c>
-      <c r="G93">
-        <v>1</v>
-      </c>
-      <c r="H93" s="37">
-        <v>9780670813346</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B94">
-        <v>39</v>
-      </c>
-      <c r="C94" s="29">
-        <v>6</v>
-      </c>
-      <c r="D94" t="b">
-        <v>1</v>
-      </c>
-      <c r="E94" s="2">
-        <v>9780670813360</v>
-      </c>
-      <c r="G94">
-        <v>1</v>
-      </c>
-      <c r="H94" s="38">
-        <v>9780670813353</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B95">
-        <v>40</v>
-      </c>
-      <c r="C95" s="29">
-        <v>6</v>
-      </c>
-      <c r="D95" t="b">
-        <v>1</v>
-      </c>
-      <c r="E95" s="3">
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" s="18">
+        <v>9780670813384</v>
+      </c>
+      <c r="G96" s="24">
+        <v>1</v>
+      </c>
+      <c r="H96" s="22">
         <v>9780670813377</v>
       </c>
-      <c r="G95">
-        <v>1</v>
-      </c>
-      <c r="H95" s="37">
-        <v>9780670813360</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B96">
-        <v>41</v>
-      </c>
-      <c r="C96" s="30">
-        <v>6</v>
-      </c>
-      <c r="D96" t="b">
-        <v>1</v>
-      </c>
-      <c r="E96" s="2">
+    </row>
+    <row r="97" spans="3:17" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G97" s="25">
+        <v>1</v>
+      </c>
+      <c r="H97" s="23">
         <v>9780670813384</v>
       </c>
-      <c r="G96">
-        <v>1</v>
-      </c>
-      <c r="H96" s="38">
-        <v>9780670813377</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G97">
-        <v>1</v>
-      </c>
-      <c r="H97" s="39">
-        <v>9780670813384</v>
-      </c>
-    </row>
-    <row r="98" spans="3:13" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="100" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="3:17" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="100" spans="3:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D100" t="s">
         <v>41</v>
       </c>
       <c r="G100" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C101" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D101" s="25" t="s">
+      <c r="L100" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C101" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D101" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E101" s="15" t="s">
+      <c r="E101" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G101" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="H101" t="s">
+      <c r="G101" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H101" s="28" t="s">
         <v>92</v>
       </c>
       <c r="I101" t="s">
@@ -4837,178 +6695,226 @@
       <c r="J101" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C102" s="29">
+      <c r="L101" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M101" t="s">
+        <v>15</v>
+      </c>
+      <c r="N101" t="s">
+        <v>16</v>
+      </c>
+      <c r="O101" t="s">
+        <v>17</v>
+      </c>
+      <c r="P101" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q101" s="63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C102" s="12">
         <v>6</v>
       </c>
-      <c r="D102" s="26">
-        <v>1</v>
-      </c>
-      <c r="E102" s="16">
-        <v>1</v>
-      </c>
-      <c r="G102" s="5">
-        <v>1</v>
-      </c>
-      <c r="H102">
-        <v>1</v>
-      </c>
-      <c r="I102" s="4" t="s">
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102" s="29">
+        <v>1</v>
+      </c>
+      <c r="G102" s="35">
+        <v>1</v>
+      </c>
+      <c r="H102" s="30">
+        <v>1</v>
+      </c>
+      <c r="I102" s="2" t="s">
         <v>119</v>
       </c>
       <c r="J102" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="103" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C103" s="29">
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102" s="1">
+        <v>46082</v>
+      </c>
+      <c r="N102" s="1">
+        <v>46090</v>
+      </c>
+      <c r="P102" s="67">
+        <v>1</v>
+      </c>
+      <c r="Q102" s="64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="3:17" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="12">
         <v>7</v>
       </c>
-      <c r="D103" s="26">
-        <v>1</v>
-      </c>
-      <c r="E103" s="16">
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103" s="29">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C104" s="29">
+      <c r="L103">
+        <v>2</v>
+      </c>
+      <c r="M103" s="1">
+        <v>46082</v>
+      </c>
+      <c r="N103" s="1">
+        <v>46090</v>
+      </c>
+      <c r="P103" s="68">
+        <v>1</v>
+      </c>
+      <c r="Q103" s="65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="3:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C104" s="12">
         <v>8</v>
       </c>
-      <c r="D104" s="26">
-        <v>1</v>
-      </c>
-      <c r="E104" s="16">
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104" s="29">
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C105" s="29">
+    <row r="105" spans="3:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C105" s="12">
         <v>9</v>
       </c>
-      <c r="D105" s="26">
+      <c r="D105">
         <v>2</v>
       </c>
-      <c r="E105" s="16">
-        <v>1</v>
-      </c>
-      <c r="L105" t="s">
+      <c r="E105" s="29">
+        <v>1</v>
+      </c>
+      <c r="H105" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="106" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C106" s="29">
+    <row r="106" spans="3:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C106" s="12">
         <v>10</v>
       </c>
-      <c r="D106" s="26">
+      <c r="D106">
         <v>2</v>
       </c>
-      <c r="E106" s="16">
+      <c r="E106" s="29">
         <v>2</v>
       </c>
-      <c r="L106" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M106" t="s">
+      <c r="H106" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I106" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C107" s="30">
+    <row r="107" spans="3:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C107" s="13">
         <v>11</v>
       </c>
-      <c r="D107" s="27">
+      <c r="D107" s="11">
         <v>2</v>
       </c>
-      <c r="E107" s="17">
+      <c r="E107" s="30">
         <v>3</v>
       </c>
-      <c r="L107">
-        <v>1</v>
-      </c>
-      <c r="M107" t="s">
+      <c r="H107" s="29">
+        <v>1</v>
+      </c>
+      <c r="I107" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="108" spans="3:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="L108">
+    <row r="108" spans="3:17" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H108" s="30">
         <v>2</v>
       </c>
-      <c r="M108" t="s">
+      <c r="I108" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="110" spans="3:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:17" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="110" spans="3:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D110" t="s">
         <v>53</v>
       </c>
-      <c r="E110" s="18"/>
       <c r="G110" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="111" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C111" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D111" s="10" t="s">
+    <row r="111" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C111" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F111" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="G111" s="10" t="s">
+      <c r="F111" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="G111" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="112" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C112" s="23">
-        <v>1</v>
-      </c>
-      <c r="D112" s="11">
-        <v>1</v>
-      </c>
-      <c r="F112" s="20">
-        <v>1</v>
-      </c>
-      <c r="G112" s="11">
+    <row r="112" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C112" s="8">
+        <v>1</v>
+      </c>
+      <c r="D112" s="5">
+        <v>1</v>
+      </c>
+      <c r="F112" s="32">
+        <v>1</v>
+      </c>
+      <c r="G112" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="113" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C113" s="23">
+      <c r="C113" s="8">
         <v>2</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="5">
         <v>0</v>
       </c>
-      <c r="F113" s="20">
+      <c r="F113" s="32">
         <v>2</v>
       </c>
-      <c r="G113" s="11">
+      <c r="G113" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="114" spans="3:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C114" s="23">
+      <c r="C114" s="8">
         <v>3</v>
       </c>
-      <c r="D114" s="11">
+      <c r="D114" s="5">
         <v>2</v>
       </c>
-      <c r="F114" s="21">
+      <c r="F114" s="33">
         <v>3</v>
       </c>
-      <c r="G114" s="12">
+      <c r="G114" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="115" spans="3:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C115" s="24">
+      <c r="C115" s="9">
         <v>4</v>
       </c>
-      <c r="D115" s="12">
+      <c r="D115" s="6">
         <v>3</v>
       </c>
     </row>

--- a/requirements/rm_diagram/db_rm_testdaten.xlsx
+++ b/requirements/rm_diagram/db_rm_testdaten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philippreisinger/Documents/Hochschule/S02/FOGL/fh-sem2-db-project/requirements/rm_diagram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9D0912-C239-194A-ACAB-46279A6E7B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF9A54B-A94E-134A-803F-E8F374939344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="50040" windowHeight="28200" xr2:uid="{F1193D4A-DC4B-D649-9F00-C53722C965C8}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="50040" windowHeight="21460" xr2:uid="{F1193D4A-DC4B-D649-9F00-C53722C965C8}"/>
   </bookViews>
   <sheets>
     <sheet name="abgabe_groesser" sheetId="7" r:id="rId1"/>
@@ -1300,7 +1300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1386,8 +1386,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
@@ -1398,25 +1396,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="192">
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thick">
-          <color theme="5"/>
+          <color theme="8" tint="0.39997558519241921"/>
         </left>
         <right style="thick">
-          <color theme="5"/>
+          <color theme="8" tint="0.39997558519241921"/>
         </right>
         <top/>
         <bottom/>
@@ -1427,10 +1447,10 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thick">
-          <color rgb="FF00B0F0"/>
+          <color rgb="FFFFFF00"/>
         </left>
         <right style="thick">
-          <color rgb="FF00B0F0"/>
+          <color rgb="FFFFFF00"/>
         </right>
         <top/>
         <bottom/>
@@ -1451,6 +1471,290 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="29" formatCode="mm:ss.0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFFFF00"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFFFF00"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </left>
+        <right style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="6" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="6" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="medium">
+          <color theme="4"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </left>
+        <right style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5" tint="0.59999389629810485"/>
+        </left>
+        <right style="thick">
+          <color theme="5" tint="0.59999389629810485"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1496,6 +1800,48 @@
         </left>
         <right style="thick">
           <color rgb="FFFFFF00"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FF00B0F0"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF00B0F0"/>
         </right>
         <top/>
         <bottom/>
@@ -1824,12 +2170,15 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="3" tint="0.249977111117893"/>
+          <color theme="3"/>
         </left>
         <right style="medium">
-          <color theme="4"/>
+          <color theme="3"/>
         </right>
+        <top/>
+        <bottom/>
         <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1849,10 +2198,10 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color theme="3" tint="0.249977111117893"/>
+          <color theme="3"/>
         </left>
         <right style="medium">
-          <color theme="3" tint="0.249977111117893"/>
+          <color theme="3"/>
         </right>
         <top/>
         <bottom/>
@@ -1862,13 +2211,16 @@
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
+        <left style="medium">
+          <color theme="6"/>
         </left>
-        <right style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
+        <right style="medium">
+          <color theme="6"/>
         </right>
+        <top/>
+        <bottom/>
         <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2060,128 +2412,6 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thick">
-          <color rgb="FFFFFF00"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFFFF00"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5"/>
-        </left>
-        <right style="thick">
-          <color theme="5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="29" formatCode="mm:ss.0"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5"/>
-        </left>
-        <right style="thick">
-          <color theme="5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFFFF00"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFFFF00"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="00000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
           <color theme="9" tint="-0.249977111117893"/>
         </left>
         <right style="thick">
@@ -2200,849 +2430,6 @@
         </left>
         <right style="thick">
           <color theme="6" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="5"/>
-        </left>
-        <right style="thick">
-          <color theme="5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="3" tint="0.249977111117893"/>
-        </left>
-        <right style="medium">
-          <color theme="4"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5"/>
-        </left>
-        <right style="thick">
-          <color theme="5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="3" tint="0.249977111117893"/>
-        </left>
-        <right style="medium">
-          <color theme="3" tint="0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
-        </left>
-        <right style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8"/>
-        </left>
-        <right style="thick">
-          <color theme="8"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="00000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
-        </left>
-        <right style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="6" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="6" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="00000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8"/>
-        </left>
-        <right style="thick">
-          <color theme="8"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFF0000"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFF0000"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5" tint="0.59999389629810485"/>
-        </left>
-        <right style="thick">
-          <color theme="5" tint="0.59999389629810485"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFF0000"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFF0000"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="00000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="3"/>
-        </left>
-        <right style="medium">
-          <color theme="3"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="3"/>
-        </left>
-        <right style="medium">
-          <color theme="3"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="6"/>
-        </left>
-        <right style="medium">
-          <color theme="6"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5"/>
-        </left>
-        <right style="thick">
-          <color theme="5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FF00B0F0"/>
-        </left>
-        <right style="thick">
-          <color rgb="FF00B0F0"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="00000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFFFF00"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFFFF00"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFFFF00"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFFFF00"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="5" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFF0000"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFF0000"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5"/>
-        </left>
-        <right style="thick">
-          <color theme="5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="29" formatCode="mm:ss.0"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5"/>
-        </left>
-        <right style="thick">
-          <color theme="5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFFFF00"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFFFF00"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="5" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFFFF00"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFFFF00"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFF0000"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFF0000"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FF00B0F0"/>
-        </left>
-        <right style="thick">
-          <color rgb="FF00B0F0"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFF0000"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFF0000"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="00000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
-        </left>
-        <right style="thick">
-          <color theme="9" tint="-0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="6" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="6" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="5"/>
-        </left>
-        <right style="thick">
-          <color theme="5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="1"/>
-        </left>
-        <right style="medium">
-          <color theme="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5"/>
-        </left>
-        <right style="thick">
-          <color theme="5"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="5" tint="0.59999389629810485"/>
-        </left>
-        <right style="thick">
-          <color theme="5" tint="0.59999389629810485"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="6" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="6" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FF00B0F0"/>
-        </left>
-        <right style="thick">
-          <color rgb="FF00B0F0"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yy"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color rgb="FFFF0000"/>
-        </left>
-        <right style="thick">
-          <color rgb="FFFF0000"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="00000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
-        </left>
-        <right style="thick">
-          <color theme="8" tint="0.39997558519241921"/>
         </right>
         <top/>
         <bottom/>
@@ -4329,6 +3716,616 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FF00B0F0"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF00B0F0"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFFFF00"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFFFF00"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFFFF00"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFFFF00"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="5" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="29" formatCode="mm:ss.0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFFFF00"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFFFF00"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="5" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFFFF00"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFFFF00"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FF00B0F0"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF00B0F0"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </left>
+        <right style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="6" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="6" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="1"/>
+        </left>
+        <right style="medium">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="medium">
+          <color theme="4"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5"/>
+        </left>
+        <right style="thick">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="medium">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </left>
+        <right style="thick">
+          <color theme="9" tint="-0.249977111117893"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="5" tint="0.59999389629810485"/>
+        </left>
+        <right style="thick">
+          <color theme="5" tint="0.59999389629810485"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="6" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="6" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FF00B0F0"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF00B0F0"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yy"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="thick">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8"/>
+        </left>
+        <right style="thick">
+          <color theme="8"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="00000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </left>
+        <right style="thick">
+          <color theme="8" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thick">
+          <color theme="8"/>
+        </left>
+        <right style="thick">
+          <color theme="8"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -14064,7 +14061,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="71" xr:uid="{4882A83E-A12D-D74A-9121-0C523387AE80}" name="Table172" displayName="Table172" ref="E5:F6" totalsRowShown="0">
   <autoFilter ref="E5:F6" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C948F8FC-AAB7-5C4F-9469-6702F4236CE2}" name="id" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{C948F8FC-AAB7-5C4F-9469-6702F4236CE2}" name="id" dataDxfId="191"/>
     <tableColumn id="2" xr3:uid="{EA21FC1F-D7F0-C84B-872A-01E90D95E223}" name="author_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14075,7 +14072,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="80" xr:uid="{DB07E07B-B16C-E748-AFD8-CAF481564B41}" name="Table1181" displayName="Table1181" ref="N94:O95" totalsRowShown="0">
   <autoFilter ref="N94:O95" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D3952B12-C26A-B645-AD31-25ECD29F003A}" name="country_id" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{D3952B12-C26A-B645-AD31-25ECD29F003A}" name="country_id" dataDxfId="170"/>
     <tableColumn id="2" xr3:uid="{3C51E746-1712-724F-8957-66FF7537EB02}" name="country_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14086,13 +14083,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="81" xr:uid="{FC428B44-810B-A345-9BB5-B1C559CA4BA6}" name="Table1282" displayName="Table1282" ref="K88:R90" totalsRowShown="0">
   <autoFilter ref="K88:R90" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{DB1F79F9-E3FD-C045-A8CF-9BCC9C08834A}" name="customer_id" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{DB1F79F9-E3FD-C045-A8CF-9BCC9C08834A}" name="customer_id" dataDxfId="169"/>
     <tableColumn id="2" xr3:uid="{D2F2E24A-8AEE-414F-A230-B084B5B37F50}" name="first_name"/>
     <tableColumn id="3" xr3:uid="{ADA19224-BC9B-6448-AD6A-90900789E541}" name="last_name"/>
-    <tableColumn id="4" xr3:uid="{EF488524-F18C-8641-8F7E-A71D97602067}" name="country_id" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{BA8DADC1-98CF-AD48-B081-9F0739EC76C2}" name="zip_id" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{82F8681A-7988-4649-A3D3-0A36AB9B2AF8}" name="town_id" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{79C38DB9-DDD0-9A48-A9A0-02CF3F867489}" name="street_id" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{EF488524-F18C-8641-8F7E-A71D97602067}" name="country_id" dataDxfId="168"/>
+    <tableColumn id="5" xr3:uid="{BA8DADC1-98CF-AD48-B081-9F0739EC76C2}" name="zip_id" dataDxfId="167"/>
+    <tableColumn id="6" xr3:uid="{82F8681A-7988-4649-A3D3-0A36AB9B2AF8}" name="town_id" dataDxfId="166"/>
+    <tableColumn id="7" xr3:uid="{79C38DB9-DDD0-9A48-A9A0-02CF3F867489}" name="street_id" dataDxfId="165"/>
     <tableColumn id="8" xr3:uid="{64209262-D7FB-CC4E-9877-4AF3DBE2C032}" name="streetnumber"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14103,9 +14100,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="82" xr:uid="{109783FA-3F71-0448-8EE6-5258D2D5A96E}" name="Table1383" displayName="Table1383" ref="G101:J102" totalsRowShown="0">
   <autoFilter ref="G101:J102" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2D1A7E35-113E-D54A-A88F-B5C1F74DC357}" name="event_id" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{26B88FBC-7CA6-8744-A38B-8DCA2D873ECC}" name="event_type_id" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{708C60E8-DA62-C043-AFA4-41C53E1427DE}" name="event_start_at_dt" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{2D1A7E35-113E-D54A-A88F-B5C1F74DC357}" name="event_id" dataDxfId="164"/>
+    <tableColumn id="2" xr3:uid="{26B88FBC-7CA6-8744-A38B-8DCA2D873ECC}" name="event_type_id" dataDxfId="163"/>
+    <tableColumn id="3" xr3:uid="{708C60E8-DA62-C043-AFA4-41C53E1427DE}" name="event_start_at_dt" dataDxfId="162"/>
     <tableColumn id="4" xr3:uid="{2E67C737-DC6F-8845-9B51-A5D4A97FF27A}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14116,7 +14113,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="83" xr:uid="{F8BE8759-FE75-944B-A2A2-8A5BDA18E242}" name="Table1484" displayName="Table1484" ref="H106:I108" totalsRowShown="0">
   <autoFilter ref="H106:I108" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1ED4EB8D-0AA9-C943-A5E7-09B65D53C377}" name="event_type_id" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{1ED4EB8D-0AA9-C943-A5E7-09B65D53C377}" name="event_type_id" dataDxfId="161"/>
     <tableColumn id="2" xr3:uid="{F4942877-A164-F943-97A5-E3E5E4F24A04}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14127,7 +14124,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="84" xr:uid="{77D19D1E-9B0E-7E4A-9A83-9D7EADF420AD}" name="Table1585" displayName="Table1585" ref="K56:L61" totalsRowShown="0">
   <autoFilter ref="K56:L61" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D0D31D73-6D2F-D54E-84F3-1CB5ECDF1B71}" name="publisher_id" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{D0D31D73-6D2F-D54E-84F3-1CB5ECDF1B71}" name="publisher_id" dataDxfId="160"/>
     <tableColumn id="2" xr3:uid="{F21F264A-3065-E54A-A4BD-6F7FB70E8CBA}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14138,7 +14135,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="85" xr:uid="{B6F3A547-ABE4-F040-A231-F50F95769E82}" name="Table1686" displayName="Table1686" ref="Q81:R84" totalsRowShown="0">
   <autoFilter ref="Q81:R84" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{145775E6-3EA4-1F43-90E7-49F575C02448}" name="street_id" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{145775E6-3EA4-1F43-90E7-49F575C02448}" name="street_id" dataDxfId="159"/>
     <tableColumn id="2" xr3:uid="{F84EC384-91AD-B74C-94C7-E0C2E1A40ABA}" name="street"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14149,7 +14146,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="86" xr:uid="{B4C4D809-9D4D-854C-AB50-D9BDA9DA6489}" name="Table1787" displayName="Table1787" ref="P74:Q77" totalsRowShown="0">
   <autoFilter ref="P74:Q77" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3B524549-4F32-7F49-BC51-2895BF16CEEE}" name="town_id" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{3B524549-4F32-7F49-BC51-2895BF16CEEE}" name="town_id" dataDxfId="158"/>
     <tableColumn id="2" xr3:uid="{F7D48148-D20D-1242-A8A9-4E58AF806DAF}" name="town_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14160,7 +14157,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="87" xr:uid="{8541A3BA-1229-BE44-91EC-DF0DC45E8878}" name="Table1888" displayName="Table1888" ref="N80:O83" totalsRowShown="0">
   <autoFilter ref="N80:O83" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1870AB00-6E87-ED42-9D4C-C1B35B05523E}" name="zip_id" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{1870AB00-6E87-ED42-9D4C-C1B35B05523E}" name="zip_id" dataDxfId="157"/>
     <tableColumn id="2" xr3:uid="{764C5B1A-F44C-E24A-883A-947F861B4607}" name="zip_code"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14168,33 +14165,33 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="88" xr:uid="{DF2AAE64-0C47-754B-A713-6365A605AA1A}" name="Table1989" displayName="Table1989" ref="G56:H97" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="88" xr:uid="{DF2AAE64-0C47-754B-A713-6365A605AA1A}" name="Table1989" displayName="Table1989" ref="G56:H97" totalsRowShown="0" headerRowDxfId="156">
   <autoFilter ref="G56:H97" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{136A7CD5-A8C6-8D4E-A23F-AC0E9F69F97E}" name="event_id" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{A7E34A93-EB78-634F-9090-AA309047E1D2}" name="book_isbn" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{136A7CD5-A8C6-8D4E-A23F-AC0E9F69F97E}" name="event_id" dataDxfId="155"/>
+    <tableColumn id="2" xr3:uid="{A7E34A93-EB78-634F-9090-AA309047E1D2}" name="book_isbn" dataDxfId="154"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="89" xr:uid="{17D0171D-E676-954C-81E3-566FDDD473DC}" name="Table2090" displayName="Table2090" ref="K77:L78" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="89" xr:uid="{17D0171D-E676-954C-81E3-566FDDD473DC}" name="Table2090" displayName="Table2090" ref="K77:L78" totalsRowShown="0" headerRowDxfId="153">
   <autoFilter ref="K77:L78" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7CA7417D-F816-ED4A-8BAE-05348CD11929}" name="customer_id" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{73206A65-6C57-6B45-8B4C-04F604B9160A}" name="event_id" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{7CA7417D-F816-ED4A-8BAE-05348CD11929}" name="customer_id" dataDxfId="152"/>
+    <tableColumn id="2" xr3:uid="{73206A65-6C57-6B45-8B4C-04F604B9160A}" name="event_id" dataDxfId="151"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="72" xr:uid="{358C2326-156C-E846-BA80-94C11050AB34}" name="Table273" displayName="Table273" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="72" xr:uid="{358C2326-156C-E846-BA80-94C11050AB34}" name="Table273" displayName="Table273" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="190">
   <autoFilter ref="D10:E51" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A89AFF32-232F-2248-9E8E-53009D611655}" name="isbn" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{8CB6679F-E1F7-9742-A46B-BF646C51E759}" name="author_id" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{A89AFF32-232F-2248-9E8E-53009D611655}" name="isbn" dataDxfId="189"/>
+    <tableColumn id="2" xr3:uid="{8CB6679F-E1F7-9742-A46B-BF646C51E759}" name="author_id" dataDxfId="188"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14204,7 +14201,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}" name="Table1" displayName="Table1" ref="E5:F6" totalsRowShown="0">
   <autoFilter ref="E5:F6" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4CA8222C-E02B-3947-87F8-83F881B4CD46}" name="id" dataDxfId="191"/>
+    <tableColumn id="1" xr3:uid="{4CA8222C-E02B-3947-87F8-83F881B4CD46}" name="id" dataDxfId="150"/>
     <tableColumn id="2" xr3:uid="{E0E55DC1-F22B-7F48-A870-6CF35C2E7C76}" name="author_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14212,11 +14209,11 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}" name="Table2" displayName="Table2" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="190">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}" name="Table2" displayName="Table2" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="149">
   <autoFilter ref="D10:E51" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1B46E4BC-5557-7848-A9B7-5BB850BF8539}" name="isbn" dataDxfId="189"/>
-    <tableColumn id="2" xr3:uid="{A9C101D5-0497-2F45-A36B-EA046D7840FD}" name="author_id" dataDxfId="188"/>
+    <tableColumn id="1" xr3:uid="{1B46E4BC-5557-7848-A9B7-5BB850BF8539}" name="isbn" dataDxfId="148"/>
+    <tableColumn id="2" xr3:uid="{A9C101D5-0497-2F45-A36B-EA046D7840FD}" name="author_id" dataDxfId="147"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14226,9 +14223,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}" name="Table3" displayName="Table3" ref="I10:M51" totalsRowShown="0">
   <autoFilter ref="I10:M51" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{38CAD5D1-EBB5-C247-B45E-AEE98024CD77}" name="isbn" dataDxfId="187"/>
+    <tableColumn id="1" xr3:uid="{38CAD5D1-EBB5-C247-B45E-AEE98024CD77}" name="isbn" dataDxfId="146"/>
     <tableColumn id="2" xr3:uid="{60F11968-00C8-6F4A-9CC4-55D26BA9ED3D}" name="book_genre_id"/>
-    <tableColumn id="3" xr3:uid="{9E8F79E7-43C5-AF41-B8EF-1A9332BF14EA}" name="publisher_id" dataDxfId="186"/>
+    <tableColumn id="3" xr3:uid="{9E8F79E7-43C5-AF41-B8EF-1A9332BF14EA}" name="publisher_id" dataDxfId="145"/>
     <tableColumn id="4" xr3:uid="{1053F528-7EBD-174A-871B-D0618032220F}" name="title"/>
     <tableColumn id="5" xr3:uid="{864CACD1-75A9-024C-BE64-135C41FF4E7C}" name="year"/>
   </tableColumns>
@@ -14241,11 +14238,11 @@
   <autoFilter ref="L101:Q103" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CE43687C-859D-1F40-BDA4-99499EB16E72}" name="book_circulation_log_id"/>
-    <tableColumn id="2" xr3:uid="{6970F839-29D6-AF48-9ED9-F80AEA8EBDB8}" name="loan_starts_at_date" dataDxfId="185"/>
-    <tableColumn id="3" xr3:uid="{2A5A1D14-65E8-8741-9C1C-5D6CEC0EAC51}" name="loan_ends_at_date" dataDxfId="184"/>
+    <tableColumn id="2" xr3:uid="{6970F839-29D6-AF48-9ED9-F80AEA8EBDB8}" name="loan_starts_at_date" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{2A5A1D14-65E8-8741-9C1C-5D6CEC0EAC51}" name="loan_ends_at_date" dataDxfId="143"/>
     <tableColumn id="4" xr3:uid="{97CCF238-494E-9D41-8539-ABC80CEB0F33}" name="book_returned_at_date"/>
-    <tableColumn id="5" xr3:uid="{DAFFE0E3-462C-F744-A240-14A8F0635450}" name="customerid" dataDxfId="183"/>
-    <tableColumn id="6" xr3:uid="{EB8E3328-793F-564A-877C-326817474CA3}" name="book_stock_log_id" dataDxfId="182"/>
+    <tableColumn id="5" xr3:uid="{DAFFE0E3-462C-F744-A240-14A8F0635450}" name="customerid" dataDxfId="142"/>
+    <tableColumn id="6" xr3:uid="{EB8E3328-793F-564A-877C-326817474CA3}" name="book_stock_log_id" dataDxfId="141"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14255,7 +14252,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}" name="Table6" displayName="Table6" ref="J2:K8" totalsRowShown="0">
   <autoFilter ref="J2:K8" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{38EBFB47-42CE-4249-A9CD-4AEC31A85951}" name="book_genre_id" dataDxfId="181"/>
+    <tableColumn id="1" xr3:uid="{38EBFB47-42CE-4249-A9CD-4AEC31A85951}" name="book_genre_id" dataDxfId="140"/>
     <tableColumn id="2" xr3:uid="{D7B8AC5E-2E4C-E944-A81B-AAECE5723F44}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14266,9 +14263,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}" name="Table7" displayName="Table7" ref="C101:E107" totalsRowShown="0">
   <autoFilter ref="C101:E107" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C98E57F8-CF5A-B04C-9AE6-4326E12BF111}" name="book_location_id" dataDxfId="180"/>
-    <tableColumn id="2" xr3:uid="{2B878DF3-03FC-7E45-8203-B9092C488BC3}" name="book_location_floor_id" dataDxfId="179"/>
-    <tableColumn id="3" xr3:uid="{7E6E67C0-8A4A-4348-B9CE-17C91B56993F}" name="book_location_shelf_id" dataDxfId="178"/>
+    <tableColumn id="1" xr3:uid="{C98E57F8-CF5A-B04C-9AE6-4326E12BF111}" name="book_location_id" dataDxfId="139"/>
+    <tableColumn id="2" xr3:uid="{2B878DF3-03FC-7E45-8203-B9092C488BC3}" name="book_location_floor_id" dataDxfId="138"/>
+    <tableColumn id="3" xr3:uid="{7E6E67C0-8A4A-4348-B9CE-17C91B56993F}" name="book_location_shelf_id" dataDxfId="137"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14278,8 +14275,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}" name="Table8" displayName="Table8" ref="C111:D115" totalsRowShown="0">
   <autoFilter ref="C111:D115" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{ED3B7FB1-4AD6-3148-A8C5-AD0D54AB86D5}" name="book_location_floor_id" dataDxfId="177"/>
-    <tableColumn id="2" xr3:uid="{5CFA8D92-95F5-D848-ACFF-964046FA5E4A}" name="number" dataDxfId="176"/>
+    <tableColumn id="1" xr3:uid="{ED3B7FB1-4AD6-3148-A8C5-AD0D54AB86D5}" name="book_location_floor_id" dataDxfId="136"/>
+    <tableColumn id="2" xr3:uid="{5CFA8D92-95F5-D848-ACFF-964046FA5E4A}" name="number" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14289,8 +14286,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}" name="Table9" displayName="Table9" ref="F111:G114" totalsRowShown="0">
   <autoFilter ref="F111:G114" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{34593F39-F4A6-074E-A6EC-EC7E7E8422BE}" name="book_location_shelf_id" dataDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{E3B4CF1C-A9B2-1C4A-A8F1-45940E10B2C5}" name="number" dataDxfId="174"/>
+    <tableColumn id="1" xr3:uid="{34593F39-F4A6-074E-A6EC-EC7E7E8422BE}" name="book_location_shelf_id" dataDxfId="134"/>
+    <tableColumn id="2" xr3:uid="{E3B4CF1C-A9B2-1C4A-A8F1-45940E10B2C5}" name="number" dataDxfId="133"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14300,10 +14297,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}" name="Table10" displayName="Table10" ref="B55:E96" totalsRowShown="0">
   <autoFilter ref="B55:E96" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0E733531-21AD-F946-9111-F766797F96D0}" name="book_stock_log_id" dataDxfId="173"/>
-    <tableColumn id="2" xr3:uid="{85903ED5-BC1F-D147-A8EA-8491727CFFC9}" name="book_location_id" dataDxfId="172"/>
+    <tableColumn id="1" xr3:uid="{0E733531-21AD-F946-9111-F766797F96D0}" name="book_stock_log_id" dataDxfId="132"/>
+    <tableColumn id="2" xr3:uid="{85903ED5-BC1F-D147-A8EA-8491727CFFC9}" name="book_location_id" dataDxfId="131"/>
     <tableColumn id="3" xr3:uid="{0A1011E6-FFDE-254C-9381-CF62A47EE8F3}" name="is_in_stock"/>
-    <tableColumn id="4" xr3:uid="{260DA1AD-9E16-104E-A144-7275FF29087D}" name="isbn" dataDxfId="171"/>
+    <tableColumn id="4" xr3:uid="{260DA1AD-9E16-104E-A144-7275FF29087D}" name="isbn" dataDxfId="130"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14313,7 +14310,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}" name="Table11" displayName="Table11" ref="N94:O95" totalsRowShown="0">
   <autoFilter ref="N94:O95" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6EC00463-AD68-3A4E-88D2-79816B3C1B9D}" name="country_id" dataDxfId="170"/>
+    <tableColumn id="1" xr3:uid="{6EC00463-AD68-3A4E-88D2-79816B3C1B9D}" name="country_id" dataDxfId="129"/>
     <tableColumn id="2" xr3:uid="{E086A4A2-2C9C-A84B-9AC0-52176BF11D98}" name="country_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14324,9 +14321,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="73" xr:uid="{6340C3CF-02FE-6C42-AD7A-41D0A9CF89C7}" name="Table374" displayName="Table374" ref="I10:M51" totalsRowShown="0">
   <autoFilter ref="I10:M51" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F656600B-27E6-C342-AE80-A0D2EA283369}" name="isbn" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{F656600B-27E6-C342-AE80-A0D2EA283369}" name="isbn" dataDxfId="187"/>
     <tableColumn id="2" xr3:uid="{564A24BE-EA80-EE42-B5DE-FAD0B64FC072}" name="book_genre_id"/>
-    <tableColumn id="3" xr3:uid="{D8B126B3-A0E5-694E-9905-D01927C186C5}" name="publisher_id" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{D8B126B3-A0E5-694E-9905-D01927C186C5}" name="publisher_id" dataDxfId="186"/>
     <tableColumn id="4" xr3:uid="{0F2D7473-CBEC-5A45-B442-C781C40CE503}" name="title"/>
     <tableColumn id="5" xr3:uid="{F4BAE610-7536-8843-AE67-BACF11F5C82D}" name="year"/>
   </tableColumns>
@@ -14338,13 +14335,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}" name="Table12" displayName="Table12" ref="K88:R90" totalsRowShown="0">
   <autoFilter ref="K88:R90" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E73135F5-C2F6-4D4B-884D-4470E95AC0A9}" name="customer_id" dataDxfId="169"/>
+    <tableColumn id="1" xr3:uid="{E73135F5-C2F6-4D4B-884D-4470E95AC0A9}" name="customer_id" dataDxfId="128"/>
     <tableColumn id="2" xr3:uid="{89AD4D6A-6E80-F84D-BC1C-F0BC9AB56A2A}" name="first_name"/>
     <tableColumn id="3" xr3:uid="{D5B6CC10-DD47-CF4F-97FC-CF3CB26AC93D}" name="last_name"/>
-    <tableColumn id="4" xr3:uid="{228DB8C2-005E-F44A-9144-29D84EA1CDCD}" name="country_id" dataDxfId="168"/>
-    <tableColumn id="5" xr3:uid="{F311F8A6-D073-364D-AB8C-3D81F088519F}" name="zip_id" dataDxfId="167"/>
-    <tableColumn id="6" xr3:uid="{B085B83B-E563-5747-92AE-F02F325D2365}" name="town_id" dataDxfId="166"/>
-    <tableColumn id="7" xr3:uid="{469FF72E-F569-5149-AAA6-FAE3DFD7884E}" name="street_id" dataDxfId="165"/>
+    <tableColumn id="4" xr3:uid="{228DB8C2-005E-F44A-9144-29D84EA1CDCD}" name="country_id" dataDxfId="127"/>
+    <tableColumn id="5" xr3:uid="{F311F8A6-D073-364D-AB8C-3D81F088519F}" name="zip_id" dataDxfId="126"/>
+    <tableColumn id="6" xr3:uid="{B085B83B-E563-5747-92AE-F02F325D2365}" name="town_id" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{469FF72E-F569-5149-AAA6-FAE3DFD7884E}" name="street_id" dataDxfId="124"/>
     <tableColumn id="8" xr3:uid="{E9A49622-D15A-F048-A7F1-ED4F84228EE8}" name="streetnumber"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14355,9 +14352,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}" name="Table13" displayName="Table13" ref="G101:J102" totalsRowShown="0">
   <autoFilter ref="G101:J102" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{47A5031E-499A-004E-B300-55435FDF6C2C}" name="event_id" dataDxfId="164"/>
-    <tableColumn id="2" xr3:uid="{9FADB436-039C-5246-BE80-643E467F92EE}" name="event_type_id" dataDxfId="163"/>
-    <tableColumn id="3" xr3:uid="{5C025943-87BA-0A4A-9FBA-C1B0DF57EB85}" name="event_start_at_dt" dataDxfId="162"/>
+    <tableColumn id="1" xr3:uid="{47A5031E-499A-004E-B300-55435FDF6C2C}" name="event_id" dataDxfId="123"/>
+    <tableColumn id="2" xr3:uid="{9FADB436-039C-5246-BE80-643E467F92EE}" name="event_type_id" dataDxfId="122"/>
+    <tableColumn id="3" xr3:uid="{5C025943-87BA-0A4A-9FBA-C1B0DF57EB85}" name="event_start_at_dt" dataDxfId="121"/>
     <tableColumn id="4" xr3:uid="{5457FAB7-6DE8-8A44-884C-825D5762F6B4}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14368,7 +14365,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}" name="Table14" displayName="Table14" ref="H106:I108" totalsRowShown="0">
   <autoFilter ref="H106:I108" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C4630465-2BEF-F04C-9706-9ECAD5A63900}" name="event_type_id" dataDxfId="161"/>
+    <tableColumn id="1" xr3:uid="{C4630465-2BEF-F04C-9706-9ECAD5A63900}" name="event_type_id" dataDxfId="120"/>
     <tableColumn id="2" xr3:uid="{3DED103F-D0D6-FB4A-BF71-8281276D9E61}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14379,7 +14376,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}" name="Table15" displayName="Table15" ref="K56:L61" totalsRowShown="0">
   <autoFilter ref="K56:L61" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7F823BF2-5D4F-5646-A492-44D3E4F6B911}" name="publisher_id" dataDxfId="160"/>
+    <tableColumn id="1" xr3:uid="{7F823BF2-5D4F-5646-A492-44D3E4F6B911}" name="publisher_id" dataDxfId="119"/>
     <tableColumn id="2" xr3:uid="{DF0F7948-576E-8649-8C5A-04EB28891E87}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14390,7 +14387,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}" name="Table16" displayName="Table16" ref="Q81:R84" totalsRowShown="0">
   <autoFilter ref="Q81:R84" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{61F45889-5DB7-B84F-B548-EC91EF25CFE0}" name="street_id" dataDxfId="159"/>
+    <tableColumn id="1" xr3:uid="{61F45889-5DB7-B84F-B548-EC91EF25CFE0}" name="street_id" dataDxfId="118"/>
     <tableColumn id="2" xr3:uid="{26F1151E-3796-634A-A382-F1364220BD49}" name="street"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14401,7 +14398,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}" name="Table17" displayName="Table17" ref="P74:Q77" totalsRowShown="0">
   <autoFilter ref="P74:Q77" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{98617ACD-5B89-6942-9465-1BB31F03AED3}" name="town_id" dataDxfId="158"/>
+    <tableColumn id="1" xr3:uid="{98617ACD-5B89-6942-9465-1BB31F03AED3}" name="town_id" dataDxfId="117"/>
     <tableColumn id="2" xr3:uid="{AEE42774-BADF-C948-B5B5-784A9108FA3C}" name="town_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14412,7 +14409,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}" name="Table18" displayName="Table18" ref="N80:O83" totalsRowShown="0">
   <autoFilter ref="N80:O83" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{07F9A468-865E-0A43-9EE2-245F124FBEFF}" name="zip_id" dataDxfId="157"/>
+    <tableColumn id="1" xr3:uid="{07F9A468-865E-0A43-9EE2-245F124FBEFF}" name="zip_id" dataDxfId="116"/>
     <tableColumn id="2" xr3:uid="{A7D14D91-1CDA-FB45-A260-0E20E6DC29BE}" name="zip_code"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14420,22 +14417,22 @@
 </file>
 
 <file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}" name="Table19" displayName="Table19" ref="G56:H97" totalsRowShown="0" headerRowDxfId="156">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}" name="Table19" displayName="Table19" ref="G56:H97" totalsRowShown="0" headerRowDxfId="115">
   <autoFilter ref="G56:H97" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8E911F00-E0AD-E241-B46F-392E2B46174D}" name="event_id" dataDxfId="155"/>
-    <tableColumn id="2" xr3:uid="{0B1666A1-D5FB-6648-AEFB-95B5325AE797}" name="book_isbn" dataDxfId="154"/>
+    <tableColumn id="1" xr3:uid="{8E911F00-E0AD-E241-B46F-392E2B46174D}" name="event_id" dataDxfId="114"/>
+    <tableColumn id="2" xr3:uid="{0B1666A1-D5FB-6648-AEFB-95B5325AE797}" name="book_isbn" dataDxfId="113"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}" name="Table20" displayName="Table20" ref="K77:L78" totalsRowShown="0" headerRowDxfId="153">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}" name="Table20" displayName="Table20" ref="K77:L78" totalsRowShown="0" headerRowDxfId="112">
   <autoFilter ref="K77:L78" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DE2D07D2-ADAE-264C-8DCD-F0CBE007E888}" name="customer_id" dataDxfId="152"/>
-    <tableColumn id="2" xr3:uid="{A21AA7ED-F1FA-D540-B965-8F8EEC8690D4}" name="event_id" dataDxfId="151"/>
+    <tableColumn id="1" xr3:uid="{DE2D07D2-ADAE-264C-8DCD-F0CBE007E888}" name="customer_id" dataDxfId="111"/>
+    <tableColumn id="2" xr3:uid="{A21AA7ED-F1FA-D540-B965-8F8EEC8690D4}" name="event_id" dataDxfId="110"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14445,7 +14442,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{7394F16C-F9D7-7D44-B5A5-640FA545A1BF}" name="Table121" displayName="Table121" ref="E5:F6" totalsRowShown="0">
   <autoFilter ref="E5:F6" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{203B0D74-4524-5A4E-812B-D5D6A799DD30}" name="id" dataDxfId="150"/>
+    <tableColumn id="1" xr3:uid="{203B0D74-4524-5A4E-812B-D5D6A799DD30}" name="id" dataDxfId="109"/>
     <tableColumn id="2" xr3:uid="{5504C138-2ABE-D344-A63C-AD6753855CF0}" name="author_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14457,22 +14454,22 @@
   <autoFilter ref="L101:Q103" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{ECB55CA3-C754-764F-9E38-2CB17D485D56}" name="book_circulation_log_id"/>
-    <tableColumn id="2" xr3:uid="{1C6AD9D0-E59B-644E-B504-637CFBA3AD30}" name="loan_starts_at_date" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{3605814B-1B14-7347-99A6-C62699CEEF39}" name="loan_ends_at_date" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{1C6AD9D0-E59B-644E-B504-637CFBA3AD30}" name="loan_starts_at_date" dataDxfId="185"/>
+    <tableColumn id="3" xr3:uid="{3605814B-1B14-7347-99A6-C62699CEEF39}" name="loan_ends_at_date" dataDxfId="184"/>
     <tableColumn id="4" xr3:uid="{C83CC057-17FB-DB4D-BFBB-DFF06E3DD37B}" name="book_returned_at_date"/>
-    <tableColumn id="5" xr3:uid="{93AE7DAC-085F-7145-BEF3-54DDFA1A8016}" name="customerid" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{00929280-8669-284E-B89D-677708E2AEB0}" name="book_stock_log_id" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{93AE7DAC-085F-7145-BEF3-54DDFA1A8016}" name="customerid" dataDxfId="183"/>
+    <tableColumn id="6" xr3:uid="{00929280-8669-284E-B89D-677708E2AEB0}" name="book_stock_log_id" dataDxfId="182"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table40.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{F6A32824-40B2-A44B-AD32-D2E5A96F45F3}" name="Table222" displayName="Table222" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="149">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{F6A32824-40B2-A44B-AD32-D2E5A96F45F3}" name="Table222" displayName="Table222" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="108">
   <autoFilter ref="D10:E51" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C2C17FED-001F-6149-ACF8-D55F29E17C9D}" name="isbn" dataDxfId="148"/>
-    <tableColumn id="2" xr3:uid="{AE3A0C87-4489-BD40-8CF4-E6A209D05BF9}" name="author_id" dataDxfId="147"/>
+    <tableColumn id="1" xr3:uid="{C2C17FED-001F-6149-ACF8-D55F29E17C9D}" name="isbn" dataDxfId="107"/>
+    <tableColumn id="2" xr3:uid="{AE3A0C87-4489-BD40-8CF4-E6A209D05BF9}" name="author_id" dataDxfId="106"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14482,9 +14479,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{F0C19DBB-6A40-8749-BFBF-5838FEA6867B}" name="Table323" displayName="Table323" ref="I10:M51" totalsRowShown="0">
   <autoFilter ref="I10:M51" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3C5A7293-518B-2D47-99EC-50E82DABD5A1}" name="isbn" dataDxfId="146"/>
+    <tableColumn id="1" xr3:uid="{3C5A7293-518B-2D47-99EC-50E82DABD5A1}" name="isbn" dataDxfId="105"/>
     <tableColumn id="2" xr3:uid="{A8C6BA1F-A7CD-334F-ACA7-204642516285}" name="book_genre_id"/>
-    <tableColumn id="3" xr3:uid="{453BE3A3-796C-DA43-A622-2CC05491C026}" name="publisher_id" dataDxfId="145"/>
+    <tableColumn id="3" xr3:uid="{453BE3A3-796C-DA43-A622-2CC05491C026}" name="publisher_id" dataDxfId="104"/>
     <tableColumn id="4" xr3:uid="{C5A89EBE-A074-E64C-B7F3-0A5ED947A4F6}" name="title"/>
     <tableColumn id="5" xr3:uid="{713184CA-B48F-204F-9CC9-61ADCA74570D}" name="year"/>
   </tableColumns>
@@ -14497,11 +14494,11 @@
   <autoFilter ref="L101:Q103" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{FC95F8F4-E985-EC40-ADF2-A95C5D0D05D2}" name="book_circulation_log_id"/>
-    <tableColumn id="2" xr3:uid="{F9F80B1F-301D-A54F-883E-EF315B18196C}" name="loan_starts_at_date" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{5530BAE8-FC68-0440-8A7A-F7484DB93E21}" name="loan_ends_at_date" dataDxfId="143"/>
+    <tableColumn id="2" xr3:uid="{F9F80B1F-301D-A54F-883E-EF315B18196C}" name="loan_starts_at_date" dataDxfId="103"/>
+    <tableColumn id="3" xr3:uid="{5530BAE8-FC68-0440-8A7A-F7484DB93E21}" name="loan_ends_at_date" dataDxfId="102"/>
     <tableColumn id="4" xr3:uid="{77CDB291-FCA8-864B-9A06-04C88949E711}" name="book_returned_at_date"/>
-    <tableColumn id="5" xr3:uid="{FE336F67-AE4D-2448-A010-6507FFE6BFC9}" name="customerid" dataDxfId="142"/>
-    <tableColumn id="6" xr3:uid="{97B3AE9B-4833-EA43-96CF-1AD56C15235E}" name="book_stock_log_id" dataDxfId="141"/>
+    <tableColumn id="5" xr3:uid="{FE336F67-AE4D-2448-A010-6507FFE6BFC9}" name="customerid" dataDxfId="101"/>
+    <tableColumn id="6" xr3:uid="{97B3AE9B-4833-EA43-96CF-1AD56C15235E}" name="book_stock_log_id" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14511,7 +14508,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{0CD2AFB7-FA26-A94C-9DFF-124E4AE64FAE}" name="Table625" displayName="Table625" ref="J2:K8" totalsRowShown="0">
   <autoFilter ref="J2:K8" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DBFB8796-3B74-E24A-969C-1A18D2347C61}" name="book_genre_id" dataDxfId="140"/>
+    <tableColumn id="1" xr3:uid="{DBFB8796-3B74-E24A-969C-1A18D2347C61}" name="book_genre_id" dataDxfId="99"/>
     <tableColumn id="2" xr3:uid="{0CFD3F1C-A716-7C4B-912B-9B4FC6C11F81}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14522,9 +14519,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{3542A85D-5C1E-B344-86AB-EAB0A1A9B9AE}" name="Table726" displayName="Table726" ref="C101:E107" totalsRowShown="0">
   <autoFilter ref="C101:E107" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3BE6D8C0-8858-B04C-9C1C-2A73C046B5C2}" name="book_location_id" dataDxfId="139"/>
-    <tableColumn id="2" xr3:uid="{DA7B0004-F7E3-3642-8768-6C71D38A4976}" name="book_location_floor_id" dataDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{C62F293D-71B9-9C44-BA44-A3BAD9960AE4}" name="book_location_shelf_id" dataDxfId="137"/>
+    <tableColumn id="1" xr3:uid="{3BE6D8C0-8858-B04C-9C1C-2A73C046B5C2}" name="book_location_id" dataDxfId="98"/>
+    <tableColumn id="2" xr3:uid="{DA7B0004-F7E3-3642-8768-6C71D38A4976}" name="book_location_floor_id" dataDxfId="97"/>
+    <tableColumn id="3" xr3:uid="{C62F293D-71B9-9C44-BA44-A3BAD9960AE4}" name="book_location_shelf_id" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14534,8 +14531,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{64108BEC-CEFC-6545-A5DD-BC755D5C6C0E}" name="Table827" displayName="Table827" ref="C111:D115" totalsRowShown="0">
   <autoFilter ref="C111:D115" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{60EB19C2-7920-624E-A6F7-62C0EEEDDD60}" name="book_location_floor_id" dataDxfId="136"/>
-    <tableColumn id="2" xr3:uid="{2A2F0890-22C6-2D44-BDD7-1BF0B722E3A6}" name="number" dataDxfId="135"/>
+    <tableColumn id="1" xr3:uid="{60EB19C2-7920-624E-A6F7-62C0EEEDDD60}" name="book_location_floor_id" dataDxfId="95"/>
+    <tableColumn id="2" xr3:uid="{2A2F0890-22C6-2D44-BDD7-1BF0B722E3A6}" name="number" dataDxfId="94"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14545,8 +14542,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{51507A35-D333-3343-95A5-F8F07A4F1EB6}" name="Table928" displayName="Table928" ref="F111:G114" totalsRowShown="0">
   <autoFilter ref="F111:G114" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D5ADA5C2-53E2-A341-B1ED-89B9CF9978A8}" name="book_location_shelf_id" dataDxfId="134"/>
-    <tableColumn id="2" xr3:uid="{E939F894-CA16-7E4B-B8CD-5B5C8821C43D}" name="number" dataDxfId="133"/>
+    <tableColumn id="1" xr3:uid="{D5ADA5C2-53E2-A341-B1ED-89B9CF9978A8}" name="book_location_shelf_id" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{E939F894-CA16-7E4B-B8CD-5B5C8821C43D}" name="number" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14556,10 +14553,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{E7762716-BC5F-444B-A5BD-35ABC67CC121}" name="Table1029" displayName="Table1029" ref="B55:E96" totalsRowShown="0">
   <autoFilter ref="B55:E96" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5B0F4B2E-DB87-B045-9175-0240CCFD1E45}" name="book_stock_log_id" dataDxfId="132"/>
-    <tableColumn id="2" xr3:uid="{E3EDF090-9D45-574B-A9C3-FF8FBCE6C613}" name="book_location_id" dataDxfId="131"/>
+    <tableColumn id="1" xr3:uid="{5B0F4B2E-DB87-B045-9175-0240CCFD1E45}" name="book_stock_log_id" dataDxfId="91"/>
+    <tableColumn id="2" xr3:uid="{E3EDF090-9D45-574B-A9C3-FF8FBCE6C613}" name="book_location_id" dataDxfId="90"/>
     <tableColumn id="3" xr3:uid="{4929255E-22B9-0B4A-89E5-98EC20FD6D38}" name="is_in_stock"/>
-    <tableColumn id="4" xr3:uid="{183F3EBE-D906-9442-83F4-C0D76A437497}" name="isbn" dataDxfId="130"/>
+    <tableColumn id="4" xr3:uid="{183F3EBE-D906-9442-83F4-C0D76A437497}" name="isbn" dataDxfId="89"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14569,7 +14566,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{4AC7A0B4-5A29-CC48-9255-545F57FF7516}" name="Table1130" displayName="Table1130" ref="N94:O95" totalsRowShown="0">
   <autoFilter ref="N94:O95" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DDD4E8D2-86BA-7644-8801-7435E84DA19A}" name="country_id" dataDxfId="129"/>
+    <tableColumn id="1" xr3:uid="{DDD4E8D2-86BA-7644-8801-7435E84DA19A}" name="country_id" dataDxfId="88"/>
     <tableColumn id="2" xr3:uid="{AEACE3BE-491C-1F40-A19B-1712380069A1}" name="country_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14580,13 +14577,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{449B9EBE-4F54-1648-A43C-51F35AE5C676}" name="Table1231" displayName="Table1231" ref="K88:R90" totalsRowShown="0">
   <autoFilter ref="K88:R90" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{CE324B06-2675-1B40-A5D5-08CD806415E9}" name="customer_id" dataDxfId="128"/>
+    <tableColumn id="1" xr3:uid="{CE324B06-2675-1B40-A5D5-08CD806415E9}" name="customer_id" dataDxfId="87"/>
     <tableColumn id="2" xr3:uid="{EAA6D2B1-35C7-CA4D-8DA8-0BEC8CD9AD0D}" name="first_name"/>
     <tableColumn id="3" xr3:uid="{D0606A88-3E0B-C542-8588-3033AE3F776E}" name="last_name"/>
-    <tableColumn id="4" xr3:uid="{3F3499B4-567F-C14A-B911-57CECCDE0935}" name="country_id" dataDxfId="127"/>
-    <tableColumn id="5" xr3:uid="{983183F8-7F90-134C-8E95-163F989969C7}" name="zip_id" dataDxfId="126"/>
-    <tableColumn id="6" xr3:uid="{1E52FE30-C9A0-A146-BE92-F87FA727B8A9}" name="town_id" dataDxfId="125"/>
-    <tableColumn id="7" xr3:uid="{83DFCCEF-9FF1-9F46-8349-46BA57BA8215}" name="street_id" dataDxfId="124"/>
+    <tableColumn id="4" xr3:uid="{3F3499B4-567F-C14A-B911-57CECCDE0935}" name="country_id" dataDxfId="86"/>
+    <tableColumn id="5" xr3:uid="{983183F8-7F90-134C-8E95-163F989969C7}" name="zip_id" dataDxfId="85"/>
+    <tableColumn id="6" xr3:uid="{1E52FE30-C9A0-A146-BE92-F87FA727B8A9}" name="town_id" dataDxfId="84"/>
+    <tableColumn id="7" xr3:uid="{83DFCCEF-9FF1-9F46-8349-46BA57BA8215}" name="street_id" dataDxfId="83"/>
     <tableColumn id="8" xr3:uid="{03B6BC18-DE7B-C348-A47E-C247CC8957B8}" name="streetnumber"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14597,7 +14594,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="75" xr:uid="{509CB013-FB08-5346-999D-D30E763466EC}" name="Table676" displayName="Table676" ref="J2:K8" totalsRowShown="0">
   <autoFilter ref="J2:K8" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3A48FCA8-F216-FF41-ADE8-0AF958164799}" name="book_genre_id" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{3A48FCA8-F216-FF41-ADE8-0AF958164799}" name="book_genre_id" dataDxfId="181"/>
     <tableColumn id="2" xr3:uid="{BFB9F10D-0ADB-7E40-9484-0159B8CB54C2}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14608,9 +14605,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{D5AB7E34-DE44-8841-9B47-004B9E30BD46}" name="Table1332" displayName="Table1332" ref="G101:J102" totalsRowShown="0">
   <autoFilter ref="G101:J102" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6C0E4B3B-05F6-5E44-963E-F3F0BB8890E4}" name="event_id" dataDxfId="123"/>
-    <tableColumn id="2" xr3:uid="{079E936E-8720-CE46-90FB-3BD33C9C7CE6}" name="event_type_id" dataDxfId="122"/>
-    <tableColumn id="3" xr3:uid="{0C550EE6-0F91-864B-9BA5-4F6FB240688D}" name="event_start_at_dt" dataDxfId="121"/>
+    <tableColumn id="1" xr3:uid="{6C0E4B3B-05F6-5E44-963E-F3F0BB8890E4}" name="event_id" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{079E936E-8720-CE46-90FB-3BD33C9C7CE6}" name="event_type_id" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{0C550EE6-0F91-864B-9BA5-4F6FB240688D}" name="event_start_at_dt" dataDxfId="80"/>
     <tableColumn id="4" xr3:uid="{EC0008FD-CB8B-E94B-BB92-33938D539D5D}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14621,7 +14618,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A21DB05C-B17F-0A41-8B97-143654B6D194}" name="Table1433" displayName="Table1433" ref="H106:I108" totalsRowShown="0">
   <autoFilter ref="H106:I108" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{834FB93E-8E55-1A46-B8A0-98B1E1B66907}" name="event_type_id" dataDxfId="120"/>
+    <tableColumn id="1" xr3:uid="{834FB93E-8E55-1A46-B8A0-98B1E1B66907}" name="event_type_id" dataDxfId="79"/>
     <tableColumn id="2" xr3:uid="{3A5CB433-D461-4645-8F96-ACD898E52908}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14632,7 +14629,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{0EEDD44C-BE4C-6945-96DD-130B07FEE796}" name="Table1534" displayName="Table1534" ref="K56:L61" totalsRowShown="0">
   <autoFilter ref="K56:L61" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C2A361FD-74E9-294A-9FCF-562FDD573F77}" name="publisher_id" dataDxfId="119"/>
+    <tableColumn id="1" xr3:uid="{C2A361FD-74E9-294A-9FCF-562FDD573F77}" name="publisher_id" dataDxfId="78"/>
     <tableColumn id="2" xr3:uid="{CA65A0AC-198D-E24E-A0A5-B527F0910956}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14643,7 +14640,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{1A446E31-D5A0-9843-B77E-5CB0BD27B713}" name="Table1635" displayName="Table1635" ref="Q81:R84" totalsRowShown="0">
   <autoFilter ref="Q81:R84" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E39B5614-F5F9-0F4E-ABC0-7795652D2544}" name="street_id" dataDxfId="118"/>
+    <tableColumn id="1" xr3:uid="{E39B5614-F5F9-0F4E-ABC0-7795652D2544}" name="street_id" dataDxfId="77"/>
     <tableColumn id="2" xr3:uid="{DBC0E9AE-D975-D142-8A0E-957D259CF176}" name="street"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14654,7 +14651,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{3760C90F-E72B-704F-B0CE-38C07A8319CE}" name="Table1736" displayName="Table1736" ref="P74:Q77" totalsRowShown="0">
   <autoFilter ref="P74:Q77" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{24FCBA63-27C3-184D-8317-012FDF8AEC8E}" name="town_id" dataDxfId="117"/>
+    <tableColumn id="1" xr3:uid="{24FCBA63-27C3-184D-8317-012FDF8AEC8E}" name="town_id" dataDxfId="76"/>
     <tableColumn id="2" xr3:uid="{F533B120-897F-E24E-8C75-A2072ADC49BD}" name="town_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14665,7 +14662,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{E78245C7-561B-C642-AB11-CFD17A84E734}" name="Table1837" displayName="Table1837" ref="N80:O83" totalsRowShown="0">
   <autoFilter ref="N80:O83" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{653F96A2-D4A9-8B40-BAA2-4F3750853953}" name="zip_id" dataDxfId="116"/>
+    <tableColumn id="1" xr3:uid="{653F96A2-D4A9-8B40-BAA2-4F3750853953}" name="zip_id" dataDxfId="75"/>
     <tableColumn id="2" xr3:uid="{24A90A27-4302-8445-9682-40E1A5F0A153}" name="zip_code"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14673,22 +14670,22 @@
 </file>
 
 <file path=xl/tables/table56.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{2E579FF7-6392-D945-9BAA-0128CFCC2D49}" name="Table1938" displayName="Table1938" ref="G56:H97" totalsRowShown="0" headerRowDxfId="115">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{2E579FF7-6392-D945-9BAA-0128CFCC2D49}" name="Table1938" displayName="Table1938" ref="G56:H97" totalsRowShown="0" headerRowDxfId="74">
   <autoFilter ref="G56:H97" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{86E5651A-D245-E342-8873-FE28E7AFDC85}" name="event_id" dataDxfId="114"/>
-    <tableColumn id="2" xr3:uid="{DCD6236F-AEAF-164D-B50E-D196EC1E6D7A}" name="book_isbn" dataDxfId="113"/>
+    <tableColumn id="1" xr3:uid="{86E5651A-D245-E342-8873-FE28E7AFDC85}" name="event_id" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{DCD6236F-AEAF-164D-B50E-D196EC1E6D7A}" name="book_isbn" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table57.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{3937C1E4-A445-6A49-B493-389869348432}" name="Table2039" displayName="Table2039" ref="K77:L78" totalsRowShown="0" headerRowDxfId="112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{3937C1E4-A445-6A49-B493-389869348432}" name="Table2039" displayName="Table2039" ref="K77:L78" totalsRowShown="0" headerRowDxfId="71">
   <autoFilter ref="K77:L78" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{75D46311-4BB8-E342-B6E6-DFAB45FED088}" name="customer_id" dataDxfId="111"/>
-    <tableColumn id="2" xr3:uid="{BF46FAA8-C6A9-4D4C-8A1F-D5099D9ADD6D}" name="event_id" dataDxfId="110"/>
+    <tableColumn id="1" xr3:uid="{75D46311-4BB8-E342-B6E6-DFAB45FED088}" name="customer_id" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{BF46FAA8-C6A9-4D4C-8A1F-D5099D9ADD6D}" name="event_id" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14698,7 +14695,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="61" xr:uid="{90AE1EAC-7046-A542-BB35-2ADE52FD985E}" name="Table12162" displayName="Table12162" ref="I6:J7" totalsRowShown="0">
   <autoFilter ref="I6:J7" xr:uid="{90AE1EAC-7046-A542-BB35-2ADE52FD985E}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{85823B2C-F546-334B-A401-B3FEA6FB343C}" name="id" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{85823B2C-F546-334B-A401-B3FEA6FB343C}" name="id" dataDxfId="68"/>
     <tableColumn id="2" xr3:uid="{75322719-F7EC-5745-A048-9141EA2D72EB}" name="author_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14706,11 +14703,11 @@
 </file>
 
 <file path=xl/tables/table59.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="62" xr:uid="{9812DB5F-489B-AA4D-8680-3103BDE1BA65}" name="Table22263" displayName="Table22263" ref="H11:I33" totalsRowShown="0" tableBorderDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="62" xr:uid="{9812DB5F-489B-AA4D-8680-3103BDE1BA65}" name="Table22263" displayName="Table22263" ref="H11:I33" totalsRowShown="0" tableBorderDxfId="67">
   <autoFilter ref="H11:I33" xr:uid="{9812DB5F-489B-AA4D-8680-3103BDE1BA65}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2DB454B3-3A63-4B46-ACAC-79A455B58678}" name="isbn" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{567D742E-0188-6C4F-99FF-9949826B48C5}" name="author_id" dataDxfId="58"/>
+    <tableColumn id="1" xr3:uid="{2DB454B3-3A63-4B46-ACAC-79A455B58678}" name="isbn" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{567D742E-0188-6C4F-99FF-9949826B48C5}" name="author_id" dataDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14720,9 +14717,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="76" xr:uid="{F0600F3B-B018-214E-9C5A-91989BC5B712}" name="Table777" displayName="Table777" ref="C101:E107" totalsRowShown="0">
   <autoFilter ref="C101:E107" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2D270AD2-D5BB-4442-81A7-928D13382234}" name="book_location_id" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{DBE81402-1489-F344-A1EF-66C484D6F086}" name="book_location_floor_id" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{E6B5A3C1-5E97-2D43-8FFC-7761E0AEC67D}" name="book_location_shelf_id" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{2D270AD2-D5BB-4442-81A7-928D13382234}" name="book_location_id" dataDxfId="180"/>
+    <tableColumn id="2" xr3:uid="{DBE81402-1489-F344-A1EF-66C484D6F086}" name="book_location_floor_id" dataDxfId="179"/>
+    <tableColumn id="3" xr3:uid="{E6B5A3C1-5E97-2D43-8FFC-7761E0AEC67D}" name="book_location_shelf_id" dataDxfId="178"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14732,10 +14729,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="63" xr:uid="{61A35EC9-5066-894E-BB5F-0FDE245EF3F4}" name="Table102964" displayName="Table102964" ref="F37:I56" totalsRowShown="0">
   <autoFilter ref="F37:I56" xr:uid="{61A35EC9-5066-894E-BB5F-0FDE245EF3F4}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{16969B8C-10C4-E24E-BD95-97FCDCE5A252}" name="book_stock_log_id" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{DAE84566-08EB-0C46-8DA3-F896C2A87D27}" name="book_location_id" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{16969B8C-10C4-E24E-BD95-97FCDCE5A252}" name="book_stock_log_id" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{DAE84566-08EB-0C46-8DA3-F896C2A87D27}" name="book_location_id" dataDxfId="63"/>
     <tableColumn id="3" xr3:uid="{F48FA60F-99C1-D040-9BE4-7E1575E1CACB}" name="is_in_stock"/>
-    <tableColumn id="4" xr3:uid="{F650390B-F9A5-604E-8286-3615D7471B40}" name="isbn" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{F650390B-F9A5-604E-8286-3615D7471B40}" name="isbn" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14745,7 +14742,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{CAEB586A-E20D-7C4E-B9ED-9EF2A547773F}" name="Table140" displayName="Table140" ref="E5:F6" totalsRowShown="0">
   <autoFilter ref="E5:F6" xr:uid="{A18C76F2-3AB3-5E48-90CA-4724130A5284}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6E1B2AC6-A6A2-B347-8238-BA7122DD03A3}" name="id" dataDxfId="109"/>
+    <tableColumn id="1" xr3:uid="{6E1B2AC6-A6A2-B347-8238-BA7122DD03A3}" name="id" dataDxfId="61"/>
     <tableColumn id="2" xr3:uid="{03A658A4-D3FC-CF40-850D-E58F3675EF97}" name="author_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14753,11 +14750,11 @@
 </file>
 
 <file path=xl/tables/table62.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{78944676-ABF5-6E4D-851C-9F8236CCEF72}" name="Table241" displayName="Table241" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{78944676-ABF5-6E4D-851C-9F8236CCEF72}" name="Table241" displayName="Table241" ref="D10:E51" totalsRowShown="0" tableBorderDxfId="60">
   <autoFilter ref="D10:E51" xr:uid="{47E5A2F3-9585-E84E-9A49-8C17C38E4C8D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E443EAFE-41C4-B34B-B532-58372E5F36B0}" name="isbn" dataDxfId="107"/>
-    <tableColumn id="2" xr3:uid="{FD0286D3-783C-1345-8F71-D667894C68F5}" name="author_id" dataDxfId="106"/>
+    <tableColumn id="1" xr3:uid="{E443EAFE-41C4-B34B-B532-58372E5F36B0}" name="isbn" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{FD0286D3-783C-1345-8F71-D667894C68F5}" name="author_id" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14767,9 +14764,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{5F8AAE0B-83A2-504D-9037-6A0378671BFA}" name="Table342" displayName="Table342" ref="I10:M51" totalsRowShown="0">
   <autoFilter ref="I10:M51" xr:uid="{DDAF566F-FD81-C548-9A5B-6F4665EEA2D5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F05FA232-5004-5148-BCC5-85CDC747C514}" name="isbn" dataDxfId="105"/>
+    <tableColumn id="1" xr3:uid="{F05FA232-5004-5148-BCC5-85CDC747C514}" name="isbn" dataDxfId="57"/>
     <tableColumn id="2" xr3:uid="{BD6AFE82-D2E3-7247-94D9-05FBA1ECAD45}" name="book_genre_id"/>
-    <tableColumn id="3" xr3:uid="{FB163672-B1E0-1E4D-831E-9422477E7127}" name="publisher_id" dataDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{FB163672-B1E0-1E4D-831E-9422477E7127}" name="publisher_id" dataDxfId="56"/>
     <tableColumn id="4" xr3:uid="{1F9FC730-551F-8143-AB5F-848B0462E105}" name="title"/>
     <tableColumn id="5" xr3:uid="{4047B33C-6D7E-A947-9CC3-521E5C4F10CA}" name="year"/>
   </tableColumns>
@@ -14782,11 +14779,11 @@
   <autoFilter ref="M101:R103" xr:uid="{0234A537-B095-774D-BBFF-33837A065154}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{36EC2467-303D-AE48-ADE2-347E06483929}" name="book_circulation_log_id"/>
-    <tableColumn id="2" xr3:uid="{0321A503-5B66-2E47-BAC4-7C6BD1062EDA}" name="loan_starts_at_date" dataDxfId="103"/>
-    <tableColumn id="3" xr3:uid="{B74FEF28-D2B2-D849-B91A-093F769C5AF5}" name="loan_ends_at_date" dataDxfId="102"/>
+    <tableColumn id="2" xr3:uid="{0321A503-5B66-2E47-BAC4-7C6BD1062EDA}" name="loan_starts_at_date" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{B74FEF28-D2B2-D849-B91A-093F769C5AF5}" name="loan_ends_at_date" dataDxfId="54"/>
     <tableColumn id="4" xr3:uid="{52D4B296-73F2-EA4A-8168-8236E9B26214}" name="book_returned_at_date"/>
-    <tableColumn id="5" xr3:uid="{5FFEAA47-F1AB-DB4F-AB0B-7E051E4CFFB7}" name="customerid" dataDxfId="101"/>
-    <tableColumn id="6" xr3:uid="{F2ECD4B5-497C-0D4C-A455-17FB87DA8FDA}" name="book_stock_log_id" dataDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{5FFEAA47-F1AB-DB4F-AB0B-7E051E4CFFB7}" name="customerid" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{F2ECD4B5-497C-0D4C-A455-17FB87DA8FDA}" name="book_stock_log_id" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14796,7 +14793,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{40CF05A5-E370-244F-BC6D-411D1A4052AC}" name="Table644" displayName="Table644" ref="J2:K8" totalsRowShown="0">
   <autoFilter ref="J2:K8" xr:uid="{8894ECEA-DBC1-B141-8753-FD4F756C1719}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{78831784-5468-BE46-B6BD-609974B5A426}" name="book_genre_id" dataDxfId="99"/>
+    <tableColumn id="1" xr3:uid="{78831784-5468-BE46-B6BD-609974B5A426}" name="book_genre_id" dataDxfId="51"/>
     <tableColumn id="2" xr3:uid="{2DDFA6EC-FF28-F24D-B3D1-163978E11C57}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14807,9 +14804,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{E992677D-FC2E-6B48-9DF8-3A0740C6473B}" name="Table745" displayName="Table745" ref="C84:E90" totalsRowShown="0">
   <autoFilter ref="C84:E90" xr:uid="{1DF3B3F5-B548-584D-B434-22242AEAC2F4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5156DC7F-619B-4E44-91C3-33803EA6694C}" name="book_location_id" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{344E96D0-0C06-7645-A4BE-3CF72548878B}" name="book_location_floor_id" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{9392BED2-5FC8-C647-AF44-D32A4DFF9412}" name="book_location_shelf_id" dataDxfId="98"/>
+    <tableColumn id="1" xr3:uid="{5156DC7F-619B-4E44-91C3-33803EA6694C}" name="book_location_id" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{344E96D0-0C06-7645-A4BE-3CF72548878B}" name="book_location_floor_id" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{9392BED2-5FC8-C647-AF44-D32A4DFF9412}" name="book_location_shelf_id" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14819,8 +14816,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{BFC10B61-9CB0-8342-AE70-445793BB802B}" name="Table846" displayName="Table846" ref="C94:D98" totalsRowShown="0">
   <autoFilter ref="C94:D98" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F6066D7A-716F-884B-89F8-8BF48733B319}" name="book_location_floor_id" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{FC7FF7A9-2D39-634B-98A0-6035CEEC3334}" name="number" dataDxfId="97"/>
+    <tableColumn id="1" xr3:uid="{F6066D7A-716F-884B-89F8-8BF48733B319}" name="book_location_floor_id" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{FC7FF7A9-2D39-634B-98A0-6035CEEC3334}" name="number" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14830,8 +14827,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{FAAB849D-5243-1944-AFC9-F5E58FE132AC}" name="Table947" displayName="Table947" ref="F119:G122" totalsRowShown="0">
   <autoFilter ref="F119:G122" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C77CE851-8F40-BC4E-AEB7-6FAA45F8A2BD}" name="book_location_shelf_id" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{59733FC4-77AB-8C41-903C-C49D0AEE6AC4}" name="number" dataDxfId="95"/>
+    <tableColumn id="1" xr3:uid="{C77CE851-8F40-BC4E-AEB7-6FAA45F8A2BD}" name="book_location_shelf_id" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{59733FC4-77AB-8C41-903C-C49D0AEE6AC4}" name="number" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14841,10 +14838,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="47" xr:uid="{798127F1-2FA5-8E40-B39D-BA3893821E7B}" name="Table1048" displayName="Table1048" ref="B55:E72" totalsRowShown="0">
   <autoFilter ref="B55:E72" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{10F257B9-BB33-3B49-8C92-7BC57A0B44C3}" name="book_stock_log_id" dataDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{1CB4C0D5-7B21-7440-9467-F97BA77103D9}" name="book_location_id" dataDxfId="93"/>
+    <tableColumn id="1" xr3:uid="{10F257B9-BB33-3B49-8C92-7BC57A0B44C3}" name="book_stock_log_id" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{1CB4C0D5-7B21-7440-9467-F97BA77103D9}" name="book_location_id" dataDxfId="42"/>
     <tableColumn id="3" xr3:uid="{9D6240A0-5E4E-9846-A99F-9DC6E10216E5}" name="is_in_stock"/>
-    <tableColumn id="4" xr3:uid="{3A4B4135-BC2A-0149-8D6A-A95D8D48AD78}" name="isbn" dataDxfId="92"/>
+    <tableColumn id="4" xr3:uid="{3A4B4135-BC2A-0149-8D6A-A95D8D48AD78}" name="isbn" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14854,8 +14851,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="77" xr:uid="{97446123-D0FB-554E-AF52-475A7D1C3292}" name="Table878" displayName="Table878" ref="C111:D115" totalsRowShown="0">
   <autoFilter ref="C111:D115" xr:uid="{DDAA8026-B91E-D84F-8433-739D35DDAA3D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A1841798-EEA4-594A-9877-37240E8215AB}" name="book_location_floor_id" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{46D6B8F5-3188-6C4C-B9FA-D98128F630E0}" name="number" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{A1841798-EEA4-594A-9877-37240E8215AB}" name="book_location_floor_id" dataDxfId="177"/>
+    <tableColumn id="2" xr3:uid="{46D6B8F5-3188-6C4C-B9FA-D98128F630E0}" name="number" dataDxfId="176"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14865,7 +14862,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="48" xr:uid="{881B0A9B-D49C-C544-AC5B-2CD695A623F5}" name="Table1149" displayName="Table1149" ref="O94:P95" totalsRowShown="0">
   <autoFilter ref="O94:P95" xr:uid="{28467CD7-2EFD-174A-9FC6-6965D645C908}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{379B17D4-00B5-A642-9C14-3D780000D8EF}" name="country_id" dataDxfId="91"/>
+    <tableColumn id="1" xr3:uid="{379B17D4-00B5-A642-9C14-3D780000D8EF}" name="country_id" dataDxfId="40"/>
     <tableColumn id="2" xr3:uid="{76ED51DD-15CC-B647-BEF1-C7396B4936C9}" name="country_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14876,13 +14873,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="49" xr:uid="{DFAB782A-D099-4148-B27C-C7038CCCCEA0}" name="Table1250" displayName="Table1250" ref="L88:S90" totalsRowShown="0">
   <autoFilter ref="L88:S90" xr:uid="{98C0CD45-8D4E-7E46-982F-330E3905CC8C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{54EE8D92-72D3-424F-AC8B-2F799B3A45E0}" name="customer_id" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{54EE8D92-72D3-424F-AC8B-2F799B3A45E0}" name="customer_id" dataDxfId="39"/>
     <tableColumn id="2" xr3:uid="{3E8AFE0E-3170-5D4E-97E6-FF9D1CECA7F7}" name="first_name"/>
     <tableColumn id="3" xr3:uid="{4A0E1280-EFAB-FA4C-A053-819BE838F617}" name="last_name"/>
-    <tableColumn id="4" xr3:uid="{5055143A-0D50-6A4B-868D-22F097F1FE38}" name="country_id" dataDxfId="89"/>
-    <tableColumn id="5" xr3:uid="{024374AE-AF92-E548-A0B7-2E6BB5D4B3D8}" name="zip_id" dataDxfId="88"/>
-    <tableColumn id="6" xr3:uid="{96DFA4DA-3830-D44A-86D6-E1128FB3624A}" name="town_id" dataDxfId="87"/>
-    <tableColumn id="7" xr3:uid="{44A553B9-C2FA-AF43-8E90-568C49E489EB}" name="street_id" dataDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{5055143A-0D50-6A4B-868D-22F097F1FE38}" name="country_id" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{024374AE-AF92-E548-A0B7-2E6BB5D4B3D8}" name="zip_id" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{96DFA4DA-3830-D44A-86D6-E1128FB3624A}" name="town_id" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{44A553B9-C2FA-AF43-8E90-568C49E489EB}" name="street_id" dataDxfId="35"/>
     <tableColumn id="8" xr3:uid="{62F3971F-212F-3740-9BC1-8BF485DD78FC}" name="streetnumber"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14893,9 +14890,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="50" xr:uid="{CAC9D4E9-EDC3-BF4F-B0D5-F79336DEBF2E}" name="Table1351" displayName="Table1351" ref="G101:J102" totalsRowShown="0">
   <autoFilter ref="G101:J102" xr:uid="{410B0B2D-025F-1248-83A2-5C84793D0A9E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E803FA14-46D1-D843-A0A9-2EF056AA11F7}" name="event_id" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{FE6B6ABA-C144-014B-B13D-782B5BC18276}" name="event_type_id" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{D3790129-FFF2-0F4E-AB18-8A22BD9EC9F1}" name="event_start_at_dt" dataDxfId="83"/>
+    <tableColumn id="1" xr3:uid="{E803FA14-46D1-D843-A0A9-2EF056AA11F7}" name="event_id" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{FE6B6ABA-C144-014B-B13D-782B5BC18276}" name="event_type_id" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{D3790129-FFF2-0F4E-AB18-8A22BD9EC9F1}" name="event_start_at_dt" dataDxfId="32"/>
     <tableColumn id="4" xr3:uid="{94CCB889-3B3E-2349-B24C-73784A876975}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14906,7 +14903,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="51" xr:uid="{F199A474-A665-E043-AF2D-63084B6F43A6}" name="Table1452" displayName="Table1452" ref="H107:I109" totalsRowShown="0">
   <autoFilter ref="H107:I109" xr:uid="{F77AC24A-6244-7D48-8E2F-6993D1197385}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{62FD7681-3E5F-B941-B067-8AF42F71A32F}" name="event_type_id" dataDxfId="82"/>
+    <tableColumn id="1" xr3:uid="{62FD7681-3E5F-B941-B067-8AF42F71A32F}" name="event_type_id" dataDxfId="31"/>
     <tableColumn id="2" xr3:uid="{6F514240-4E31-6540-93E6-5E97DB15ADF8}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14917,7 +14914,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="52" xr:uid="{96B0B19A-D986-5944-AA67-5B1C850E6DBA}" name="Table1553" displayName="Table1553" ref="K56:L61" totalsRowShown="0">
   <autoFilter ref="K56:L61" xr:uid="{9B023D2B-13C5-E642-8500-1027D57A480A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{759718CD-30F0-2C43-A1F7-41ACB8648056}" name="publisher_id" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{759718CD-30F0-2C43-A1F7-41ACB8648056}" name="publisher_id" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{B8DD4859-E5F1-3748-992E-93439F1F8D9B}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14928,7 +14925,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="53" xr:uid="{B66181E3-B396-9B4C-8375-9B4D2CD344CD}" name="Table1654" displayName="Table1654" ref="R81:S84" totalsRowShown="0">
   <autoFilter ref="R81:S84" xr:uid="{392EB08F-BB0A-C74F-9DAD-AD4640E30454}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A475BD0D-3CFD-EB49-AD7D-E767AC89434E}" name="street_id" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{A475BD0D-3CFD-EB49-AD7D-E767AC89434E}" name="street_id" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{B9758413-FE10-0F4A-93EE-D1CF954CEB98}" name="street"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14939,7 +14936,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="54" xr:uid="{D66CD126-CE27-CA40-99C0-61E49C0A7108}" name="Table1755" displayName="Table1755" ref="Q74:R77" totalsRowShown="0">
   <autoFilter ref="Q74:R77" xr:uid="{985AB320-4B0B-E546-8BE4-FE79B7D1445D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B44D967D-988F-F145-9D43-0F78D0C0E992}" name="town_id" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{B44D967D-988F-F145-9D43-0F78D0C0E992}" name="town_id" dataDxfId="28"/>
     <tableColumn id="2" xr3:uid="{ADC1F4DD-FDD2-E947-ADE3-6A760F7A76F7}" name="town_name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14950,7 +14947,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="55" xr:uid="{4A9829BB-AAF8-0047-BB64-415E258F9B61}" name="Table1856" displayName="Table1856" ref="O80:P83" totalsRowShown="0">
   <autoFilter ref="O80:P83" xr:uid="{0949F84C-2BA6-764E-924F-E5135155D478}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DC4543DE-935D-D143-B8DE-A7A59FD7F6D1}" name="zip_id" dataDxfId="78"/>
+    <tableColumn id="1" xr3:uid="{DC4543DE-935D-D143-B8DE-A7A59FD7F6D1}" name="zip_id" dataDxfId="27"/>
     <tableColumn id="2" xr3:uid="{461B2082-6545-5B44-A154-37C90C506457}" name="zip_code"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -14958,22 +14955,22 @@
 </file>
 
 <file path=xl/tables/table78.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="57" xr:uid="{D43CD728-018C-A34E-8E87-2DBA61D28280}" name="Table2058" displayName="Table2058" ref="L77:M78" totalsRowShown="0" headerRowDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="57" xr:uid="{D43CD728-018C-A34E-8E87-2DBA61D28280}" name="Table2058" displayName="Table2058" ref="L77:M78" totalsRowShown="0" headerRowDxfId="26">
   <autoFilter ref="L77:M78" xr:uid="{24080707-42B4-8944-9D1A-7CD6BDA12940}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A851ED35-4D02-004C-910D-0090F5CCACAE}" name="customer_id" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{1FEDD235-1425-864B-8D38-8F9F9FDC9847}" name="event_id" dataDxfId="72"/>
+    <tableColumn id="1" xr3:uid="{A851ED35-4D02-004C-910D-0090F5CCACAE}" name="customer_id" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{1FEDD235-1425-864B-8D38-8F9F9FDC9847}" name="event_id" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table79.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="56" xr:uid="{0759EA37-826F-3843-8E5B-112F7007EAE3}" name="Table1957" displayName="Table1957" ref="G56:H97" totalsRowShown="0" headerRowDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="56" xr:uid="{0759EA37-826F-3843-8E5B-112F7007EAE3}" name="Table1957" displayName="Table1957" ref="G56:H97" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="G56:H97" xr:uid="{C5C412B0-23B0-5E49-84F6-5E6A55E09BE2}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BEDBB925-D06C-D94C-8C3F-EF117DBF8E94}" name="event_id" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{1502B464-4BA5-1747-85F6-BE1A2D332AC3}" name="book_isbn" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{BEDBB925-D06C-D94C-8C3F-EF117DBF8E94}" name="event_id" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{1502B464-4BA5-1747-85F6-BE1A2D332AC3}" name="book_isbn" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14983,8 +14980,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="78" xr:uid="{06FA7E47-EA99-5F43-B48F-0ABDA06A6A8C}" name="Table979" displayName="Table979" ref="F111:G114" totalsRowShown="0">
   <autoFilter ref="F111:G114" xr:uid="{7AF64A5D-8383-FE44-AFB9-3BF4F11C07D0}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{94496EC9-A19F-2E4B-9E6B-C960DCFE04B7}" name="book_location_shelf_id" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{43C21897-418A-6D47-8643-3B6CE260815A}" name="number" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{94496EC9-A19F-2E4B-9E6B-C960DCFE04B7}" name="book_location_shelf_id" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{43C21897-418A-6D47-8643-3B6CE260815A}" name="number" dataDxfId="174"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14994,9 +14991,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{EA0CFF22-C043-B348-AEB5-639E0FF45B0A}" name="Table34259" displayName="Table34259" ref="I16:M41" totalsRowShown="0">
   <autoFilter ref="I16:M41" xr:uid="{EA0CFF22-C043-B348-AEB5-639E0FF45B0A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{AC7F5DE7-368A-1F4C-8E50-9D3123BC2C7C}" name="isbn" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{AC7F5DE7-368A-1F4C-8E50-9D3123BC2C7C}" name="isbn" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{8BCB37CD-DDB9-4B46-89DF-481E43496B51}" name="book_genre_id"/>
-    <tableColumn id="3" xr3:uid="{933BB685-EEF9-7547-AC18-3D7F5637E09D}" name="publisher_id" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{933BB685-EEF9-7547-AC18-3D7F5637E09D}" name="publisher_id" dataDxfId="19"/>
     <tableColumn id="4" xr3:uid="{412F4D26-3E51-084A-8F6F-89FFC0CB0746}" name="title"/>
     <tableColumn id="5" xr3:uid="{5003E292-401D-EF47-A812-C84780FFE78B}" name="year"/>
   </tableColumns>
@@ -15008,7 +15005,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{BBF6523A-1362-0346-A43B-4B42105A125D}" name="Table64460" displayName="Table64460" ref="J8:K14" totalsRowShown="0">
   <autoFilter ref="J8:K14" xr:uid="{BBF6523A-1362-0346-A43B-4B42105A125D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C841E8E7-A24B-F742-BCCF-B8F7D811A050}" name="book_genre_id" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{C841E8E7-A24B-F742-BCCF-B8F7D811A050}" name="book_genre_id" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{567C1954-5C8B-EA47-8DBF-417CB099ADE1}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -15019,7 +15016,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="60" xr:uid="{F8DF6FCE-B9D5-1840-90B1-ABABEEC7A4DB}" name="Table155361" displayName="Table155361" ref="K46:L51" totalsRowShown="0">
   <autoFilter ref="K46:L51" xr:uid="{F8DF6FCE-B9D5-1840-90B1-ABABEEC7A4DB}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{99189128-2DCF-EF4C-A6C1-FF9E05DCA7EA}" name="publisher_id" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{99189128-2DCF-EF4C-A6C1-FF9E05DCA7EA}" name="publisher_id" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{4C630777-3AAF-554D-9414-03BA601A5246}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -15030,9 +15027,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="64" xr:uid="{D413BF7C-A885-2042-811D-6D8E25ACD7CC}" name="Table765" displayName="Table765" ref="G54:I60" totalsRowShown="0">
   <autoFilter ref="G54:I60" xr:uid="{D413BF7C-A885-2042-811D-6D8E25ACD7CC}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C6B739FB-3776-6A42-96D9-7E657D726515}" name="book_location_id" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{42438FAC-5C29-5B47-A289-C89641D45AD8}" name="book_location_floor_id" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{75FA8663-36A0-294E-B601-44255574A2D4}" name="book_location_shelf_id" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{C6B739FB-3776-6A42-96D9-7E657D726515}" name="book_location_id" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{42438FAC-5C29-5B47-A289-C89641D45AD8}" name="book_location_floor_id" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{75FA8663-36A0-294E-B601-44255574A2D4}" name="book_location_shelf_id" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15042,8 +15039,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="65" xr:uid="{14C30350-54BB-BA4F-81D9-F0146CDE0038}" name="Table866" displayName="Table866" ref="G64:H68" totalsRowShown="0">
   <autoFilter ref="G64:H68" xr:uid="{14C30350-54BB-BA4F-81D9-F0146CDE0038}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5CC5E555-FBF5-DD4D-A826-16CCE1B19B00}" name="book_location_floor_id" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{91A0DFA2-3BCA-504A-B12D-27D929D542AC}" name="number" dataDxfId="53"/>
+    <tableColumn id="1" xr3:uid="{5CC5E555-FBF5-DD4D-A826-16CCE1B19B00}" name="book_location_floor_id" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{91A0DFA2-3BCA-504A-B12D-27D929D542AC}" name="number" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15053,8 +15050,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="66" xr:uid="{3EDD4C36-0AAA-1A41-8901-4626FE21F207}" name="Table967" displayName="Table967" ref="J64:K67" totalsRowShown="0">
   <autoFilter ref="J64:K67" xr:uid="{3EDD4C36-0AAA-1A41-8901-4626FE21F207}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{98959CD0-4D23-7748-8BD3-7245F0E73B5E}" name="book_location_shelf_id" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{428E7CE6-3628-5D44-BB07-DE00FE5C74AC}" name="number" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{98959CD0-4D23-7748-8BD3-7245F0E73B5E}" name="book_location_shelf_id" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{428E7CE6-3628-5D44-BB07-DE00FE5C74AC}" name="number" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15064,10 +15061,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="67" xr:uid="{BF9C218D-8B19-D743-8AEA-BFA2E2FA75FD}" name="Table1068" displayName="Table1068" ref="F8:I49" totalsRowShown="0">
   <autoFilter ref="F8:I49" xr:uid="{BF9C218D-8B19-D743-8AEA-BFA2E2FA75FD}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{82EC27A9-9F34-D24A-8AE9-AE2FA577368A}" name="book_stock_log_id" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{A404EF74-2F8F-D048-9DB3-92594CAA96AC}" name="book_location_id" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{82EC27A9-9F34-D24A-8AE9-AE2FA577368A}" name="book_stock_log_id" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{A404EF74-2F8F-D048-9DB3-92594CAA96AC}" name="book_location_id" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{C5180CFC-836D-DC46-A78B-9414106702FA}" name="is_in_stock"/>
-    <tableColumn id="4" xr3:uid="{3D67D0AA-D26F-AB44-ACD8-C1B8DDD46BC2}" name="isbn" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{3D67D0AA-D26F-AB44-ACD8-C1B8DDD46BC2}" name="isbn" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15077,9 +15074,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="68" xr:uid="{343D6659-19F9-9F4C-BD3E-B851E8126C75}" name="Table1369" displayName="Table1369" ref="K54:N55" totalsRowShown="0">
   <autoFilter ref="K54:N55" xr:uid="{343D6659-19F9-9F4C-BD3E-B851E8126C75}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{9B18E576-2983-DD4E-B6FD-E6E4EF79A297}" name="event_id" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{B6977D5F-FB0C-4C44-ACC8-FBB5976566C6}" name="event_type_id" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{B99D957D-05CD-9045-8D72-74C62579474B}" name="event_start_at_dt" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{9B18E576-2983-DD4E-B6FD-E6E4EF79A297}" name="event_id" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{B6977D5F-FB0C-4C44-ACC8-FBB5976566C6}" name="event_type_id" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{B99D957D-05CD-9045-8D72-74C62579474B}" name="event_start_at_dt" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{364E2808-8D29-D74A-8918-99DCEAF156B1}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -15090,7 +15087,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="69" xr:uid="{9998F81C-C2BC-6F48-AA39-8C03C2F9C08D}" name="Table1470" displayName="Table1470" ref="L59:M61" totalsRowShown="0">
   <autoFilter ref="L59:M61" xr:uid="{9998F81C-C2BC-6F48-AA39-8C03C2F9C08D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F01E0EEE-C546-0A4E-BB52-BF7991F4A39B}" name="event_type_id" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{F01E0EEE-C546-0A4E-BB52-BF7991F4A39B}" name="event_type_id" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{B50AC879-D0FA-1945-9B51-9374ED895385}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -15098,11 +15095,11 @@
 </file>
 
 <file path=xl/tables/table89.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="70" xr:uid="{69BBF4AF-7DE7-9E42-90FD-4A8C0797870B}" name="Table1971" displayName="Table1971" ref="K9:L50" totalsRowShown="0" headerRowDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="70" xr:uid="{69BBF4AF-7DE7-9E42-90FD-4A8C0797870B}" name="Table1971" displayName="Table1971" ref="K9:L50" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="K9:L50" xr:uid="{69BBF4AF-7DE7-9E42-90FD-4A8C0797870B}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CE3D4B93-FB12-E94C-A807-D5D16D809F05}" name="event_id" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{B992D097-7096-CF47-97B3-D49C3A11E6A7}" name="book_isbn" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{CE3D4B93-FB12-E94C-A807-D5D16D809F05}" name="event_id" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{B992D097-7096-CF47-97B3-D49C3A11E6A7}" name="book_isbn" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15112,10 +15109,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="79" xr:uid="{F34D05D5-DA19-E741-80E0-76360098A1F0}" name="Table1080" displayName="Table1080" ref="B55:E96" totalsRowShown="0">
   <autoFilter ref="B55:E96" xr:uid="{693A829E-6BAE-D240-BB4E-D963A5D545EF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4A0BEFD3-F815-6646-BC17-779039FB97F8}" name="book_stock_log_id" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{2B472FD2-8FBD-A84D-B15C-2CC8B93007A5}" name="book_location_id" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{4A0BEFD3-F815-6646-BC17-779039FB97F8}" name="book_stock_log_id" dataDxfId="173"/>
+    <tableColumn id="2" xr3:uid="{2B472FD2-8FBD-A84D-B15C-2CC8B93007A5}" name="book_location_id" dataDxfId="172"/>
     <tableColumn id="3" xr3:uid="{357BD8DB-B83E-2D49-9FBA-99C7064E2986}" name="is_in_stock"/>
-    <tableColumn id="4" xr3:uid="{09F190B9-0D66-DB4A-9FBF-5598FE83E998}" name="isbn" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{09F190B9-0D66-DB4A-9FBF-5598FE83E998}" name="isbn" dataDxfId="171"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -22885,7 +22882,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F6308E5-111F-4C4F-A8E5-4D378FE91EB2}">
-  <dimension ref="F5:K57"/>
+  <dimension ref="F5:J57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
@@ -22893,12 +22890,12 @@
     <col min="10" max="10" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="7:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="8:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="I5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="7:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="8:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="I6" s="46" t="s">
         <v>1</v>
       </c>
@@ -22906,7 +22903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="7:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="8:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="I7" s="47">
         <v>1</v>
       </c>
@@ -22914,293 +22911,203 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="7:11" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-    </row>
-    <row r="10" spans="7:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H10" s="86" t="s">
+    <row r="8" spans="8:10" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="8:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="86"/>
-      <c r="J10" s="86"/>
-      <c r="K10" s="86"/>
-    </row>
-    <row r="11" spans="7:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="H11" s="101" t="s">
+    </row>
+    <row r="11" spans="8:10" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="H11" s="98" t="s">
         <v>8</v>
       </c>
       <c r="I11" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
-    </row>
-    <row r="12" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G12" s="86"/>
-      <c r="H12" s="100">
+    </row>
+    <row r="12" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H12" s="97">
         <v>9780385086952</v>
       </c>
       <c r="I12" s="50">
         <v>1</v>
       </c>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-    </row>
-    <row r="13" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G13" s="86"/>
-      <c r="H13" s="100">
+    </row>
+    <row r="13" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H13" s="97">
         <v>9780307743657</v>
       </c>
       <c r="I13" s="50">
         <v>1</v>
       </c>
-      <c r="J13" s="86"/>
-      <c r="K13" s="86"/>
-    </row>
-    <row r="14" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G14" s="86"/>
-      <c r="H14" s="100">
+    </row>
+    <row r="14" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H14" s="97">
         <v>9780307743664</v>
       </c>
       <c r="I14" s="50">
         <v>1</v>
       </c>
-      <c r="J14" s="86"/>
-      <c r="K14" s="86"/>
-    </row>
-    <row r="15" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G15" s="86"/>
-      <c r="H15" s="100">
+    </row>
+    <row r="15" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H15" s="97">
         <v>9780670813025</v>
       </c>
       <c r="I15" s="50">
         <v>1</v>
       </c>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
-    </row>
-    <row r="16" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G16" s="86"/>
-      <c r="H16" s="100">
+    </row>
+    <row r="16" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H16" s="97">
         <v>9780345418864</v>
       </c>
       <c r="I16" s="50">
         <v>1</v>
       </c>
-      <c r="J16" s="86"/>
-      <c r="K16" s="86"/>
-    </row>
-    <row r="17" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G17" s="86"/>
-      <c r="H17" s="100">
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H17" s="97">
         <v>9780670813032</v>
       </c>
       <c r="I17" s="50">
         <v>1</v>
       </c>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-    </row>
-    <row r="18" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G18" s="86"/>
-      <c r="H18" s="100">
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H18" s="97">
         <v>9780670813049</v>
       </c>
       <c r="I18" s="50">
         <v>1</v>
       </c>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-    </row>
-    <row r="19" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G19" s="86"/>
-      <c r="H19" s="100">
+    </row>
+    <row r="19" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H19" s="97">
         <v>9780670813056</v>
       </c>
       <c r="I19" s="50">
         <v>1</v>
       </c>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-    </row>
-    <row r="20" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G20" s="86"/>
-      <c r="H20" s="100">
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H20" s="97">
         <v>9780670813063</v>
       </c>
       <c r="I20" s="50">
         <v>1</v>
       </c>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-    </row>
-    <row r="21" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G21" s="86"/>
-      <c r="H21" s="100">
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H21" s="97">
         <v>9780670813070</v>
       </c>
       <c r="I21" s="50">
         <v>1</v>
       </c>
-      <c r="J21" s="86"/>
-      <c r="K21" s="86"/>
-    </row>
-    <row r="22" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G22" s="86"/>
-      <c r="H22" s="100" t="s">
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H22" s="97" t="s">
         <v>124</v>
       </c>
       <c r="I22" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="J22" s="86"/>
-      <c r="K22" s="86"/>
-    </row>
-    <row r="23" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G23" s="86"/>
-      <c r="H23" s="100">
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H23" s="97">
         <v>9780670813285</v>
       </c>
       <c r="I23" s="50">
         <v>1</v>
       </c>
-      <c r="J23" s="86"/>
-      <c r="K23" s="86"/>
-    </row>
-    <row r="24" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G24" s="86"/>
-      <c r="H24" s="100">
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H24" s="97">
         <v>9780670813292</v>
       </c>
       <c r="I24" s="50">
         <v>1</v>
       </c>
-      <c r="J24" s="86"/>
-      <c r="K24" s="86"/>
-    </row>
-    <row r="25" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G25" s="86"/>
-      <c r="H25" s="100">
+    </row>
+    <row r="25" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H25" s="97">
         <v>9780670813308</v>
       </c>
       <c r="I25" s="50">
         <v>1</v>
       </c>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-    </row>
-    <row r="26" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G26" s="86"/>
-      <c r="H26" s="100">
+    </row>
+    <row r="26" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H26" s="97">
         <v>9780670813315</v>
       </c>
       <c r="I26" s="50">
         <v>1</v>
       </c>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-    </row>
-    <row r="27" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G27" s="86"/>
-      <c r="H27" s="100">
+    </row>
+    <row r="27" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H27" s="97">
         <v>9780670813322</v>
       </c>
       <c r="I27" s="50">
         <v>1</v>
       </c>
-      <c r="J27" s="86"/>
-      <c r="K27" s="86"/>
-    </row>
-    <row r="28" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G28" s="86"/>
-      <c r="H28" s="100">
+    </row>
+    <row r="28" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H28" s="97">
         <v>9780670813339</v>
       </c>
       <c r="I28" s="50">
         <v>1</v>
       </c>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-    </row>
-    <row r="29" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G29" s="86"/>
-      <c r="H29" s="100">
+    </row>
+    <row r="29" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H29" s="97">
         <v>9780670813346</v>
       </c>
       <c r="I29" s="50">
         <v>1</v>
       </c>
-      <c r="J29" s="86"/>
-      <c r="K29" s="86"/>
-    </row>
-    <row r="30" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G30" s="86"/>
-      <c r="H30" s="100">
+    </row>
+    <row r="30" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H30" s="97">
         <v>9780670813353</v>
       </c>
       <c r="I30" s="50">
         <v>1</v>
       </c>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-    </row>
-    <row r="31" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G31" s="86"/>
-      <c r="H31" s="100">
+    </row>
+    <row r="31" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H31" s="97">
         <v>9780670813360</v>
       </c>
       <c r="I31" s="50">
         <v>1</v>
       </c>
-      <c r="J31" s="86"/>
-      <c r="K31" s="86"/>
-    </row>
-    <row r="32" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G32" s="86"/>
-      <c r="H32" s="100">
+    </row>
+    <row r="32" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H32" s="97">
         <v>9780670813377</v>
       </c>
       <c r="I32" s="50">
         <v>1</v>
       </c>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-    </row>
-    <row r="33" spans="6:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G33" s="86"/>
-      <c r="H33" s="100">
+    </row>
+    <row r="33" spans="6:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H33" s="97">
         <v>9780670813384</v>
       </c>
       <c r="I33" s="47">
         <v>1</v>
       </c>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
-    </row>
-    <row r="34" spans="6:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="H34" s="86"/>
-      <c r="I34" s="86"/>
-      <c r="J34" s="86"/>
-      <c r="K34" s="86"/>
-    </row>
-    <row r="35" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H35" s="86"/>
-      <c r="I35" s="86"/>
-      <c r="K35" s="86"/>
-    </row>
-    <row r="36" spans="6:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="6:9" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="6:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
         <v>75</v>
       </c>
-      <c r="H36" s="86"/>
-      <c r="I36" s="86"/>
-      <c r="K36" s="86"/>
-    </row>
-    <row r="37" spans="6:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="6:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="F37" t="s">
         <v>121</v>
       </c>
@@ -23214,7 +23121,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F38" s="53">
         <v>1</v>
       </c>
@@ -23228,7 +23135,7 @@
         <v>9780385086952</v>
       </c>
     </row>
-    <row r="39" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F39" s="53">
         <v>2</v>
       </c>
@@ -23242,7 +23149,7 @@
         <v>9780307743657</v>
       </c>
     </row>
-    <row r="40" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F40" s="53">
         <v>3</v>
       </c>
@@ -23256,7 +23163,7 @@
         <v>9780307743664</v>
       </c>
     </row>
-    <row r="41" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F41" s="53">
         <v>4</v>
       </c>
@@ -23270,7 +23177,7 @@
         <v>9780670813025</v>
       </c>
     </row>
-    <row r="42" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F42" s="53">
         <v>5</v>
       </c>
@@ -23284,7 +23191,7 @@
         <v>9780345418864</v>
       </c>
     </row>
-    <row r="43" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F43" s="53">
         <v>6</v>
       </c>
@@ -23298,7 +23205,7 @@
         <v>9780670813032</v>
       </c>
     </row>
-    <row r="44" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F44" s="53">
         <v>7</v>
       </c>
@@ -23312,7 +23219,7 @@
         <v>9780670813049</v>
       </c>
     </row>
-    <row r="45" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F45" s="53" t="s">
         <v>123</v>
       </c>
@@ -23322,11 +23229,11 @@
       <c r="H45" t="s">
         <v>123</v>
       </c>
-      <c r="I45" s="97" t="s">
+      <c r="I45" s="14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F46" s="53">
         <v>31</v>
       </c>
@@ -23340,7 +23247,7 @@
         <v>9780670813285</v>
       </c>
     </row>
-    <row r="47" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F47" s="53">
         <v>32</v>
       </c>
@@ -23354,7 +23261,7 @@
         <v>9780670813292</v>
       </c>
     </row>
-    <row r="48" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F48" s="53">
         <v>33</v>
       </c>
@@ -24776,7 +24683,7 @@
       <c r="D61" t="s">
         <v>123</v>
       </c>
-      <c r="E61" s="97" t="s">
+      <c r="E61" s="14" t="s">
         <v>124</v>
       </c>
       <c r="G61" s="22">
@@ -25071,9 +24978,8 @@
       </c>
     </row>
     <row r="77" spans="2:18" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="86"/>
-      <c r="D77" s="85"/>
-      <c r="E77" s="85"/>
+      <c r="D77" s="84"/>
+      <c r="E77" s="84"/>
       <c r="G77" s="22">
         <v>1</v>
       </c>
@@ -25094,7 +25000,6 @@
       </c>
     </row>
     <row r="78" spans="2:18" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="86"/>
       <c r="D78" s="84"/>
       <c r="E78" s="84"/>
       <c r="G78" s="22">
@@ -25111,7 +25016,6 @@
       </c>
     </row>
     <row r="79" spans="2:18" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="86"/>
       <c r="D79" s="83"/>
       <c r="E79" s="83"/>
       <c r="G79" s="22">
@@ -25125,7 +25029,6 @@
       </c>
     </row>
     <row r="80" spans="2:18" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="86"/>
       <c r="G80" s="22">
         <v>1</v>
       </c>
@@ -25142,8 +25045,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="81" spans="2:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="86"/>
+    <row r="81" spans="3:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="G81" s="22">
         <v>1</v>
       </c>
@@ -25163,8 +25065,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="82" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B82" s="86"/>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="G82" s="22">
         <v>1</v>
       </c>
@@ -25184,8 +25085,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="83" spans="2:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="86"/>
+    <row r="83" spans="3:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D83" t="s">
         <v>40</v>
       </c>
@@ -25208,15 +25108,14 @@
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="2:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="86"/>
-      <c r="C84" s="90" t="s">
+    <row r="84" spans="3:19" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C84" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="D84" s="87" t="s">
+      <c r="D84" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="E84" s="94" t="s">
+      <c r="E84" s="92" t="s">
         <v>43</v>
       </c>
       <c r="G84" s="22">
@@ -25232,15 +25131,14 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="2:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="86"/>
-      <c r="C85" s="91">
+    <row r="85" spans="3:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C85" s="89">
         <v>6</v>
       </c>
-      <c r="D85" s="88">
-        <v>1</v>
-      </c>
-      <c r="E85" s="95">
+      <c r="D85" s="86">
+        <v>1</v>
+      </c>
+      <c r="E85" s="93">
         <v>1</v>
       </c>
       <c r="G85" s="22">
@@ -25250,15 +25148,14 @@
         <v>9780670813261</v>
       </c>
     </row>
-    <row r="86" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B86" s="86"/>
-      <c r="C86" s="92">
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C86" s="90">
         <v>7</v>
       </c>
-      <c r="D86" s="88">
-        <v>1</v>
-      </c>
-      <c r="E86" s="95">
+      <c r="D86" s="86">
+        <v>1</v>
+      </c>
+      <c r="E86" s="93">
         <v>2</v>
       </c>
       <c r="G86" s="22">
@@ -25268,15 +25165,14 @@
         <v>9780670813278</v>
       </c>
     </row>
-    <row r="87" spans="2:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="86"/>
-      <c r="C87" s="92">
+    <row r="87" spans="3:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C87" s="90">
         <v>8</v>
       </c>
-      <c r="D87" s="88">
-        <v>1</v>
-      </c>
-      <c r="E87" s="95">
+      <c r="D87" s="86">
+        <v>1</v>
+      </c>
+      <c r="E87" s="93">
         <v>3</v>
       </c>
       <c r="G87" s="22">
@@ -25289,15 +25185,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="88" spans="2:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="86"/>
-      <c r="C88" s="92">
+    <row r="88" spans="3:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C88" s="90">
         <v>9</v>
       </c>
-      <c r="D88" s="88">
+      <c r="D88" s="86">
         <v>2</v>
       </c>
-      <c r="E88" s="95">
+      <c r="E88" s="93">
         <v>1</v>
       </c>
       <c r="G88" s="22">
@@ -25331,15 +25226,14 @@
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B89" s="86"/>
-      <c r="C89" s="92">
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C89" s="90">
         <v>10</v>
       </c>
-      <c r="D89" s="88">
+      <c r="D89" s="86">
         <v>2</v>
       </c>
-      <c r="E89" s="95">
+      <c r="E89" s="93">
         <v>2</v>
       </c>
       <c r="G89" s="22">
@@ -25373,15 +25267,14 @@
         <v>188</v>
       </c>
     </row>
-    <row r="90" spans="2:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="86"/>
-      <c r="C90" s="93">
+    <row r="90" spans="3:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C90" s="91">
         <v>11</v>
       </c>
-      <c r="D90" s="89">
+      <c r="D90" s="87">
         <v>2</v>
       </c>
-      <c r="E90" s="96">
+      <c r="E90" s="94">
         <v>3</v>
       </c>
       <c r="G90" s="22">
@@ -25415,8 +25308,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="91" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B91" s="86"/>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="G91" s="22">
         <v>1</v>
       </c>
@@ -25424,8 +25316,7 @@
         <v>9780670813322</v>
       </c>
     </row>
-    <row r="92" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B92" s="86"/>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="G92" s="22">
         <v>1</v>
       </c>
@@ -25433,8 +25324,7 @@
         <v>9780670813339</v>
       </c>
     </row>
-    <row r="93" spans="2:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="86"/>
+    <row r="93" spans="3:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D93" t="s">
         <v>52</v>
       </c>
@@ -25448,9 +25338,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="2:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B94" s="86"/>
-      <c r="C94" s="87" t="s">
+    <row r="94" spans="3:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C94" s="85" t="s">
         <v>42</v>
       </c>
       <c r="D94" s="4" t="s">
@@ -25469,9 +25358,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="95" spans="2:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="86"/>
-      <c r="C95" s="88">
+    <row r="95" spans="3:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C95" s="86">
         <v>1</v>
       </c>
       <c r="D95" s="5">
@@ -25490,9 +25378,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="96" spans="2:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B96" s="86"/>
-      <c r="C96" s="88">
+    <row r="96" spans="3:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C96" s="86">
         <v>2</v>
       </c>
       <c r="D96" s="5">
@@ -25505,9 +25392,8 @@
         <v>9780670813377</v>
       </c>
     </row>
-    <row r="97" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="86"/>
-      <c r="C97" s="88">
+    <row r="97" spans="3:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C97" s="86">
         <v>3</v>
       </c>
       <c r="D97" s="5">
@@ -25520,23 +25406,15 @@
         <v>9780670813384</v>
       </c>
     </row>
-    <row r="98" spans="2:18" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="86"/>
-      <c r="C98" s="89">
+    <row r="98" spans="3:18" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="87">
         <v>4</v>
       </c>
       <c r="D98" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B99" s="86"/>
-    </row>
-    <row r="100" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="86"/>
-      <c r="C100" s="86"/>
-      <c r="D100" s="86"/>
-      <c r="E100" s="86"/>
+    <row r="100" spans="3:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G100" t="s">
         <v>90</v>
       </c>
@@ -25544,11 +25422,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="2:18" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B101" s="86"/>
-      <c r="C101" s="86"/>
-      <c r="D101" s="86"/>
-      <c r="E101" s="86"/>
+    <row r="101" spans="3:18" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="G101" s="17" t="s">
         <v>100</v>
       </c>
@@ -25580,11 +25454,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="102" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="86"/>
-      <c r="C102" s="86"/>
-      <c r="D102" s="86"/>
-      <c r="E102" s="86"/>
+    <row r="102" spans="3:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G102" s="31">
         <v>1</v>
       </c>
@@ -25613,11 +25483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="2:18" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="86"/>
-      <c r="C103" s="86"/>
-      <c r="D103" s="86"/>
-      <c r="E103" s="86"/>
+    <row r="103" spans="3:18" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="M103">
         <v>2</v>
       </c>
@@ -25634,32 +25500,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="2:18" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B104" s="86"/>
-      <c r="C104" s="86"/>
-      <c r="D104" s="86"/>
-      <c r="E104" s="86"/>
-    </row>
-    <row r="105" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B105" s="86"/>
-      <c r="C105" s="86"/>
-      <c r="D105" s="86"/>
-      <c r="E105" s="86"/>
-    </row>
-    <row r="106" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B106" s="86"/>
-      <c r="C106" s="86"/>
-      <c r="D106" s="86"/>
-      <c r="E106" s="86"/>
+    <row r="104" spans="3:18" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="106" spans="3:18" x14ac:dyDescent="0.2">
       <c r="H106" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="107" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B107" s="86"/>
-      <c r="C107" s="86"/>
-      <c r="D107" s="86"/>
-      <c r="E107" s="86"/>
+    <row r="107" spans="3:18" x14ac:dyDescent="0.2">
       <c r="H107" s="3" t="s">
         <v>91</v>
       </c>
@@ -25667,7 +25514,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="108" spans="3:18" x14ac:dyDescent="0.2">
       <c r="H108" s="27">
         <v>1</v>
       </c>
@@ -25675,7 +25522,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="2:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="H109" s="28">
         <v>2</v>
       </c>
@@ -25683,7 +25530,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="110" spans="2:18" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="110" spans="3:18" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="118" spans="6:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G118" t="s">
         <v>60</v>
@@ -26024,7 +25871,7 @@
       </c>
     </row>
     <row r="27" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I27" s="98" t="s">
+      <c r="I27" s="95" t="s">
         <v>123</v>
       </c>
       <c r="J27" s="40" t="s">
@@ -26084,7 +25931,7 @@
       <c r="K30" s="42">
         <v>2</v>
       </c>
-      <c r="L30" s="99">
+      <c r="L30" s="96">
         <v>23337</v>
       </c>
       <c r="M30">
